--- a/scripts/gbrt_standard_l2/performance.xlsx
+++ b/scripts/gbrt_standard_l2/performance.xlsx
@@ -9,13 +9,18 @@
   <sheets>
     <sheet name="Models" sheetId="1" r:id="rId1"/>
     <sheet name="Ensemble" sheetId="2" r:id="rId2"/>
+    <sheet name="Ensemble optspreads" sheetId="3" r:id="rId3"/>
+    <sheet name="Ensemble opt-undspreads" sheetId="4" r:id="rId4"/>
+    <sheet name="Returns Long-Short 30-min" sheetId="5" r:id="rId5"/>
+    <sheet name="Returns Long-Short Daily" sheetId="6" r:id="rId6"/>
+    <sheet name="Returns Long-Short Weekly" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="490">
   <si>
     <t>Model</t>
   </si>
@@ -238,7 +243,1288 @@
     <t>H-L 10 portfolios, 0 turnover</t>
   </si>
   <si>
-    <t>[nan, nan]</t>
+    <t>[np.float64(0.0005966067841540283), np.float64(1.5094986015810147e-60)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.000751129112884685), np.float64(0.7148584413678503)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7758611810777926), np.float64(0.43805548322052495)]</t>
+  </si>
+  <si>
+    <t>delta_change_mean</t>
+  </si>
+  <si>
+    <t>delta_change_std</t>
+  </si>
+  <si>
+    <t>turnover_mean</t>
+  </si>
+  <si>
+    <t>turnover_std</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>inf</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0028162057974499676), np.float64(0.070924297179464)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.003266868880633331), np.float64(0.11597358282902684)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0011535513667106508), np.float64(0.32343548187925336)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.001142785599711901), np.float64(0.6243498200974134)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0035348635551434877), np.float64(0.00013269370992636495)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.007014610235562138), np.float64(0.0001540665201293044)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.017100652260765088), np.float64(0.0002198112653963872)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.03360892645439551), np.float64(0.0002793608893359501)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.08374903354853755), np.float64(0.0003657307704847486)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.16291309125914488), np.float64(0.00018590864799652833)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-8.28888245634647e-05), np.float64(0.8426411433991179)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00047045614310678923), np.float64(0.38655834591631705)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0011334497779965196), np.float64(0.07844773339978137)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0029984041431047044), np.float64(0.020039201984430544)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.006397490922870002), np.float64(0.013006546599627451)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01258128034046294), np.float64(0.014200006247363227)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.03081386687262116), np.float64(0.016618249566071577)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.060267088594400844), np.float64(0.01690873653041901)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.15011190018249865), np.float64(0.019345662482576378)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.28893060768073564), np.float64(0.014892087483175864)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00023772309743334653), np.float64(0.020716981950193288)]</t>
+  </si>
+  <si>
+    <t>[np.float64(6.0808571174751753e-05), np.float64(0.6440420904148869)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0003016878389911809), np.float64(0.06381316303264853)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00113662351724837), np.float64(0.00040700604664990623)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0023312087870178784), np.float64(0.0002742997362202519)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004464528504794493), np.float64(0.0005038967963338852)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.010403813818298064), np.float64(0.0011232064544469415)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.02078665375141961), np.float64(0.0013498835641360025)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.050171225129093285), np.float64(0.0015552530007793093)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.1021877644813394), np.float64(0.0032522475353289537)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-6.059393170838167e-05), np.float64(0.5952338003173745)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0001742354681297095), np.float64(0.2414320335648951)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.000370314009304781), np.float64(0.04476258271360885)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0010538067185106804), np.float64(0.003926506612778915)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.002163895357598554), np.float64(0.0027218112909684657)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.003990268585137713), np.float64(0.005655857463600422)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00914149241317354), np.float64(0.011150194843233362)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.017533479579444212), np.float64(0.014959441509050408)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04143012743172772), np.float64(0.01834674706605495)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0863152553663986), np.float64(0.025810581278353204)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.1309759943377921e-05), np.float64(0.830160566546656)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00014017116507387096), np.float64(1.7774036602139478e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0002354719894860386), np.float64(1.4511084516087727e-10)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005081979012403171), np.float64(2.8290946982946317e-21)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0007957473246386775), np.float64(1.8780573082064976e-18)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0011463137655511452), np.float64(2.638241207425903e-12)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.001856107812572834), np.float64(1.5167434538404072e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.002861478478979055), np.float64(0.00012599269795938978)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005664775219229519), np.float64(0.0030036809934296423)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009841714989951783), np.float64(0.0057215666358933085)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00030687789747672287), np.float64(8.508288301197459e-34)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0003711753007025523), np.float64(5.577480030778414e-41)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0004233202057447511), np.float64(8.799642615588339e-47)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005966036352170899), np.float64(1.5112288075508086e-60)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0007833978240482108), np.float64(3.4122659721702813e-66)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0009645248712676694), np.float64(4.0501731962091896e-60)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0011636152494390918), np.float64(1.1983716267403962e-39)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0013343457761587469), np.float64(2.553107698730245e-27)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.001578703862074444), np.float64(8.644130634501984e-16)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0017960698491377301), np.float64(1.1860593755065391e-11)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.2312477329205147), np.float64(0.017270330336031058)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.3210746281745712), np.float64(0.013120633702104732)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.20829318664998572), np.float64(0.004209172984936713)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.4238322907346407), np.float64(0.0033888687215819072)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.07478191084761669), np.float64(0.18287324578305797)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.11937315981485003), np.float64(0.28591811744493206)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.2437757469249956), np.float64(0.38322236161205)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.5427537852063885), np.float64(0.32572962081433815)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.1191305924771389), np.float64(0.41877795964853554)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.3487485073251486), np.float64(0.3521479569232886)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.001171218753287731), np.float64(0.964059670828844)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.007100550689504995), np.float64(0.83345136858673)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.007455484270737814), np.float64(0.8521718970072131)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.016624092662837504), np.float64(0.834506161224268)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04157337317498216), np.float64(0.7913410930568794)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0930763905867519), np.float64(0.7645753128808328)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.2809482410921735), np.float64(0.7182676313284616)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.7295895523638039), np.float64(0.6297077183050661)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.2592757653114246), np.float64(0.5517662973872021)]</t>
+  </si>
+  <si>
+    <t>[np.float64(6.965906669504774), np.float64(0.3130405515878802)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0017855473763106404), np.float64(0.7797886970057802)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0023004278646215274), np.float64(0.7788258791451367)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005443037323075893), np.float64(0.5902073131811574)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.008647290648457595), np.float64(0.6619412927069814)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.020125134967916347), np.float64(0.6061532192876841)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04147327001081325), np.float64(0.5929275798824547)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.11353486139797521), np.float64(0.5571998833736203)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.17141489180672656), np.float64(0.6595174235923426)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.5027751071220564), np.float64(0.5921240053158223)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.4189737835726455), np.float64(0.8352306375767947)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00010301437528493742), np.float64(0.9884332654620449)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0005711842460851939), np.float64(0.950787394845516)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0016353626406862595), np.float64(0.8865313391109254)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0010487367518915533), np.float64(0.9628079259551134)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.01456839090582541), np.float64(0.7409957297123758)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.027399021026721964), np.float64(0.7536143783560372)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.07009727272903397), np.float64(0.7484552915530441)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.13689983232018046), np.float64(0.751356552987009)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.024832648306591036), np.float64(0.9809825808826541)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.4746678634510211), np.float64(0.8341185053614857)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.006724138333473226), np.float64(0.040472162169198585)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0017514741548272288), np.float64(0.38487371296876804)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0012729880308726665), np.float64(0.5709015753458984)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0013878965230323928), np.float64(0.6661744220873279)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0002054821900602634), np.float64(0.9697478541939181)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0016182640870380275), np.float64(0.8689978525783164)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.006294050646831069), np.float64(0.787366273814896)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.009141751836930325), np.float64(0.8379480618464152)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.006469159107001144), np.float64(0.9541499522621174)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.005591148891175217), np.float64(0.9785990789992663)]</t>
+  </si>
+  <si>
+    <t>[np.float64(8.763143386469306e-05), np.float64(0.9533764132011106)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0001497366110442147), np.float64(0.9264453470684935)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-3.0251588918542102e-05), np.float64(0.9858899108454271)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0007544545124547531), np.float64(0.7136514857963487)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0017850340285623274), np.float64(0.48167927057171156)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0044060659357164226), np.float64(0.1828756924885572)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.009190855902900169), np.float64(0.07136466136113723)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.012358186054222295), np.float64(0.0825552201690581)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.01589574293042106), np.float64(0.1624524329318956)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.016403147305368192), np.float64(0.2779100369097691)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.283101970845629), np.float64(0.02268039308050331)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.9151388311279705), np.float64(0.055823681296901226)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.6188135733820004), np.float64(0.10587332179275318)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7379080627364927), np.float64(0.4607822074533067)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.4554899966476644), np.float64(0.014276568594810113)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.2181488050747746), np.float64(0.001341086858654185)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.539990782560693), np.float64(0.0004227634594350974)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.6089803796807405), np.float64(0.00032611386781354525)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.5918862360421513), np.float64(0.000347915558319636)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.7995989513761668), np.float64(0.0001556880292749932)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.7388098424940714), np.float64(0.08244490134944153)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.8536744673165545), np.float64(0.39353560321341663)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.03160386886463727), np.float64(0.9747956767989582)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.418426908848776), np.float64(0.1564474928526217)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.064524897687894), np.float64(0.03928307741080173)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.270347977295954), np.float64(0.023446113416034343)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.3478047365050254), np.float64(0.01912208522085051)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.3885967328712123), np.float64(0.017138951967094335)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.3689538663260827), np.float64(0.018070140879247285)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.5088252232634196), np.float64(0.012305940424550056)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.3757693808985376), np.float64(0.017742134087197797)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.8480437348214531), np.float64(0.06495725981605875)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3740643477452135), np.float64(0.16979854281149873)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.13477525193224274), np.float64(0.8928227685069393)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.5407676341666778), np.float64(0.12376055567456085)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.4862451258053913), np.float64(0.013108686658338201)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.9565567519982), np.float64(0.0032005158483338248)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.0777960728653815), np.float64(0.0021550228641081)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.149136378624914), np.float64(0.00169709082772125)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.940264360972197), np.float64(0.0033718382090004006)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.0424972314843632), np.float64(0.04142276809534282)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.5999810296742902), np.float64(0.1099893910129016)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.2026062674550884), np.float64(0.22947713035514816)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.022499377314019804), np.float64(0.9820551024935322)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.1754426096476278), np.float64(0.24016011543603769)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.8504663735040154), np.float64(0.06460719308983484)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.214510128559083), np.float64(0.027068986443951414)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.2668266011902665), np.float64(0.023661449264282812)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.3072064381137416), np.float64(0.021292513388199166)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.1932477745215406), np.float64(0.028570687200548096)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.9397431213021177), np.float64(0.05275478093167362)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.7130559073021718), np.float64(0.08708164104419215)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.5043296439234723), np.float64(0.13288297349803915)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.9975304080576861), np.float64(0.31880246872233053)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.5129160209989977), np.float64(0.6081487177384943)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.09864799296386041), np.float64(0.9214419605397908)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.0735945566626013), np.float64(0.2833214235753118)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.8735624075468742), np.float64(0.061347542566493794)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.2252068061898838), np.float64(0.026339662533940905)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.401511745293448), np.float64(0.016549930781519173)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3592123703993173), np.float64(0.1744543603370996)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.2711387703795312), np.float64(0.20404106743658224)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.1845733374827259), np.float64(0.23653066515368984)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7776463315143731), np.float64(0.4370026610751663)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.48557538414993917), np.float64(0.6273984422990485)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.14607763687154948), np.float64(0.8838961340436813)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.12889524618083806), np.float64(0.8974722614169671)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.458129129895309), np.float64(0.6469814963653725)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.652595783198803), np.float64(0.514200478639306)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.9444375852095515), np.float64(0.3452252912295846)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.003386323203404004), np.float64(0.08377266744172869)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0039734834523933605), np.float64(0.10387835636102809)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0015424772469546143), np.float64(0.2847062110057054)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.007629902653399795), np.float64(0.3226346599600231)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.003213327125496761), np.float64(8.112769183428356e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.006364909951869407), np.float64(5.997441114802864e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01537779509261752), np.float64(8.424572639292422e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.02998020626047117), np.float64(1.5656727531270446e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.07525348423567149), np.float64(3.961755184904263e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.15244571068008983), np.float64(1.4075030594582204e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0002577519947242865), np.float64(0.4260868826461742)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00025482032857785476), np.float64(0.5092806220566554)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.000843067519418795), np.float64(0.05725597364242203)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0028746287992486084), np.float64(0.02051930829217443)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005130209183934248), np.float64(0.0019436738641234264)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00953377040846814), np.float64(0.00031858727682973134)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.022016322561345638), np.float64(0.0001685955385054399)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04358959016135782), np.float64(0.0003337490982760465)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.1016147602948295), np.float64(8.070029669764846e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.19962340880532564), np.float64(5.167226296033894e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0003032676734529334), np.float64(0.0037180784988912413)]</t>
+  </si>
+  <si>
+    <t>[np.float64(5.265008635798739e-06), np.float64(0.9683256032081461)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00022769593285102303), np.float64(0.16350434672896386)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0010584982693862886), np.float64(0.0008635144359722127)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.002206804337373991), np.float64(0.0003078373658067049)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004385899674429777), np.float64(0.00017293526989102344)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.010015949451041218), np.float64(0.00028290091451995574)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01948592159899509), np.float64(0.0005651418187124062)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.047780605817803766), np.float64(0.000935201632218448)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.09923772559553806), np.float64(0.0028706304791815147)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-6.402164927037588e-05), np.float64(0.5742165271053555)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00016319332753201497), np.float64(0.2696772287693042)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0003580464747866966), np.float64(0.04979512420269293)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0010344342753889299), np.float64(0.003924533714860793)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.002101983630070137), np.float64(0.00257973834873605)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.003829096429183291), np.float64(0.005563820983426099)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.008109960699370821), np.float64(0.005436039028145242)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.015431069464020291), np.float64(0.007445475877412057)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0377299318184101), np.float64(0.01118599295345581)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.07746028319789314), np.float64(0.015095892293250963)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00011072264227669552), np.float64(0.32619166173082015)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-6.342118181419334e-05), np.float64(0.6626154743563699)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.0598248055791756e-05), np.float64(0.9099255615114176)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0001886775584485715), np.float64(0.5638195254429849)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00019673023672775022), np.float64(0.7489192409482986)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.4166397666097133e-05), np.float64(0.9839969329412002)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0009873070938753658), np.float64(0.7350694608257852)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.003983454227215608), np.float64(0.5751367059858958)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.015712586130108168), np.float64(0.47753252567130333)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.020427469737357085), np.float64(0.5113832174447726)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0003025001396588869), np.float64(4.1674853533584335e-33)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00036786526115022275), np.float64(1.193094185955652e-40)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00041934785805042247), np.float64(2.633349146282154e-46)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005919476659418385), np.float64(3.5970798295615096e-60)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0007764771897930966), np.float64(1.0691000784957163e-65)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0009563977970958371), np.float64(1.5150567568872386e-59)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0011573592479148598), np.float64(1.8009259322177788e-39)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.001328179264829022), np.float64(4.075723478832657e-27)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0015683015900626962), np.float64(1.204996812086687e-15)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.001784827161490301), np.float64(1.540167250691355e-11)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.2704931164688467), np.float64(0.026509258613011392)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.3939500770352175), np.float64(0.00950009043030143)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.25150799759894527), np.float64(0.005027527617124735)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.3101787188389875), np.float64(0.00609683263376037)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.041728875630158035), np.float64(0.2896846792339962)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0632899687637782), np.float64(0.4086499425742683)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.11974224169606258), np.float64(0.5240184721658767)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.32137847168209677), np.float64(0.3865420125402662)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.6388633444252122), np.float64(0.5049745491630949)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.839627773407255), np.float64(0.36447568904220345)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.002144444984965744), np.float64(0.9152929318168488)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00024249661671766162), np.float64(0.9919352141878044)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0004781984331752599), np.float64(0.9861164186374017)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.016753793319045387), np.float64(0.8267283844110577)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0007659744350704989), np.float64(0.9939220016892036)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01798402069722839), np.float64(0.9104958891451277)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.06787327044743834), np.float64(0.8476833455182897)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.2561656209240673), np.float64(0.7248116272845698)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.7050460511757213), np.float64(0.6422992624060058)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.7285441366344436), np.float64(0.33875805851779495)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0018989044310518553), np.float64(0.7701497873439845)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0008581139883305229), np.float64(0.9171846211071313)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0020925947557649525), np.float64(0.8365618533865924)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.002965839305503538), np.float64(0.87954804761047)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009492578971358526), np.float64(0.7987094730120485)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.018705466675236097), np.float64(0.7908054600862762)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.057700118283566665), np.float64(0.7296333596793473)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.15658542126996308), np.float64(0.6441461185297285)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.44886730706775607), np.float64(0.5988289718300503)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.34502206969574983), np.float64(0.857984445212701)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00040648796494060087), np.float64(0.9543095217088814)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0011881037907286033), np.float64(0.8971916901145669)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.002439330930743505), np.float64(0.8293841740545106)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0020629826659787735), np.float64(0.9255514006561313)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.016017481631289), np.float64(0.7065982888789427)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.029608327714498027), np.float64(0.7231676486965601)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.06597842123490898), np.float64(0.7095808474311277)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.13401358207744077), np.float64(0.6988726944508746)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.043208991667041244), np.float64(0.9609029233031012)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.4611385841372791), np.float64(0.8045885884407522)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004880486327074459), np.float64(0.4862382899751421)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.002258869973295599), np.float64(0.802438874045415)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0016051430781145925), np.float64(0.8870367217390156)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.007562708772145881), np.float64(0.7077852907992179)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0153357926012867), np.float64(0.683201473047862)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.03230802711285229), np.float64(0.6593246401999023)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.08230470022446745), np.float64(0.643055709900326)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.24170511358737443), np.float64(0.5724797774218847)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.5096424621556395), np.float64(0.6979258649428522)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.5386252480283081), np.float64(0.7690620802226166)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00015173824240652492), np.float64(0.9191468100786199)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.2132258005082194e-05), np.float64(0.9890597737377844)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-7.451147517718602e-05), np.float64(0.9651307448974518)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0008085668880471028), np.float64(0.6930313474057508)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0018076330446946847), np.float64(0.4738698942357786)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.004428790249669927), np.float64(0.17938989919631695)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.008910594600559818), np.float64(0.07957242918720389)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.012528848870320014), np.float64(0.07882894271118143)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.014688505897613962), np.float64(0.1946924108041991)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.01878082839813843), np.float64(0.2120103439644387)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.1145741704302754), np.float64(0.034768557404528604)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.9007255919651704), np.float64(0.057689667805453405)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.5925155194565423), np.float64(0.11165571720839414)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.9504154766899129), np.float64(0.3421822445015129)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.6292148299597784), np.float64(0.008719087983774697)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.9540913618424045), np.float64(8.348621553820224e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.6297836509841375), np.float64(4.256732708668676e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.7340803234438935), np.float64(2.5933095710276047e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.633423225902457), np.float64(4.184430651634771e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.4082221237615755), np.float64(1.181337702426357e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.1429769752358685), np.float64(0.032409738774608794)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.2905005364398825), np.float64(0.19724201716318515)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.3740483289049576), np.float64(0.7084654115856626)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.3646958959953672), np.float64(0.17272438043443314)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.350083907506893), np.float64(0.019006198932643797)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.1719271598910765), np.float64(0.0015708825383300524)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.609580077454061), np.float64(0.00032537279053346626)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.547871107140271), np.float64(0.0004105017180226046)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.960161322982558), np.float64(8.143137076650928e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.1249645667325705), np.float64(4.0875777739011055e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.4841542775593712), np.float64(0.013185315100163568)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.94816452185168), np.float64(0.05173737341003618)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.4949416560395705), np.float64(0.13531580310525523)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.020418514135616527), np.float64(0.9837145002540036)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.3841587027068571), np.float64(0.16668783245062493)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.5980115450400687), np.float64(0.009545393201982473)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.2385122933982395), np.float64(0.0012500630237614037)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.294085464173742), np.float64(0.0010299232373680261)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.2896412427121944), np.float64(0.0010461087714264295)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.9753584242574713), np.float64(0.003012707753448411)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.064979711352966), np.float64(0.039239908120414786)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.6720693341529025), np.float64(0.09489354398750206)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.2512448626919435), np.float64(0.21120331794215688)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.06898668619696334), np.float64(0.9450170976166923)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.1069438344473903), np.float64(0.2686440194693153)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.7975858054507035), np.float64(0.07261181553459796)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.3578135292175495), np.float64(0.018617748708555554)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.4603280129329668), np.float64(0.014086964350224775)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.468918298821606), np.float64(0.013755787333621731)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.3854729329380393), np.float64(0.017284158350692375)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.1240496811186147), np.float64(0.033965802629252695)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.0257382396457704), np.float64(0.04311619099137118)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.8849331659812394), np.float64(0.05979355552241168)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3738003773321739), np.float64(0.16988046987579145)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.0761642877342226), np.float64(0.2821714688609018)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.868957917551869), np.float64(0.385125342951641)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7405092941909913), np.float64(0.4592037788745602)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7517708872860467), np.float64(0.45240535981039226)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7977884076801187), np.float64(0.4252251006660121)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7190914164577313), np.float64(0.4722902160214171)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3777599414827975), np.float64(0.16865467536849688)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.278673886189686), np.float64(0.20137501507677538)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.1785891158063526), np.float64(0.2389049695359015)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.8042947381593988), np.float64(0.42146074305944015)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.5043110152390546), np.float64(0.6141788128836853)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.19155121359985772), np.float64(0.848141355126897)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.11179260506343786), np.float64(0.9110153100368812)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.3930588243689686), np.float64(0.6943785727601114)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.6302485765753795), np.float64(0.52870819394094)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.7670385991371161), np.float64(0.4432801586638969)]</t>
+  </si>
+  <si>
+    <t>Returns</t>
   </si>
 </sst>
 </file>
@@ -1697,10 +2983,6169 @@
         <v>62</v>
       </c>
       <c r="V12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="W12" t="s">
-        <v>62</v>
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P61"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="B1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2">
+        <v>0.001037323185975824</v>
+      </c>
+      <c r="D2">
+        <v>-0.002556715626269579</v>
+      </c>
+      <c r="E2">
+        <v>0.04456016793847084</v>
+      </c>
+      <c r="F2">
+        <v>0.0008378687780350447</v>
+      </c>
+      <c r="G2">
+        <v>0.0008665486238896847</v>
+      </c>
+      <c r="H2">
+        <v>1.000554754032533</v>
+      </c>
+      <c r="I2">
+        <v>0.04895201470336813</v>
+      </c>
+      <c r="J2">
+        <v>-0.05737670511007309</v>
+      </c>
+      <c r="K2">
+        <v>-0.9997720718383789</v>
+      </c>
+      <c r="L2">
+        <v>2.550461530685425</v>
+      </c>
+      <c r="M2">
+        <v>-3.284033298492432</v>
+      </c>
+      <c r="N2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O2" t="s">
+        <v>189</v>
+      </c>
+      <c r="P2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3">
+        <v>0.001379186670824149</v>
+      </c>
+      <c r="D3">
+        <v>-0.002905797911807895</v>
+      </c>
+      <c r="E3">
+        <v>0.05941937491297722</v>
+      </c>
+      <c r="F3">
+        <v>0.0009924637852236629</v>
+      </c>
+      <c r="G3">
+        <v>0.0009671798325143754</v>
+      </c>
+      <c r="H3">
+        <v>1.000788938775954</v>
+      </c>
+      <c r="I3">
+        <v>0.04888388696760482</v>
+      </c>
+      <c r="J3">
+        <v>-0.0489032045006752</v>
+      </c>
+      <c r="K3">
+        <v>-0.9999275803565979</v>
+      </c>
+      <c r="L3">
+        <v>3.400948286056519</v>
+      </c>
+      <c r="M3">
+        <v>-2.799041032791138</v>
+      </c>
+      <c r="N3" t="s">
+        <v>130</v>
+      </c>
+      <c r="O3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4">
+        <v>0.0017192761906826</v>
+      </c>
+      <c r="D4">
+        <v>-0.0009263124084100127</v>
+      </c>
+      <c r="E4">
+        <v>0.0334627740085125</v>
+      </c>
+      <c r="F4">
+        <v>0.001122665707953274</v>
+      </c>
+      <c r="G4">
+        <v>0.001107678515836596</v>
+      </c>
+      <c r="H4">
+        <v>1.000925086840055</v>
+      </c>
+      <c r="I4">
+        <v>0.04885675796343468</v>
+      </c>
+      <c r="J4">
+        <v>-0.02768187783658504</v>
+      </c>
+      <c r="K4">
+        <v>-0.9519742131233215</v>
+      </c>
+      <c r="L4">
+        <v>1.915287137031555</v>
+      </c>
+      <c r="M4">
+        <v>-1.584409713745117</v>
+      </c>
+      <c r="N4" t="s">
+        <v>131</v>
+      </c>
+      <c r="O4" t="s">
+        <v>191</v>
+      </c>
+      <c r="P4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5">
+        <v>0.003392683534972071</v>
+      </c>
+      <c r="D5">
+        <v>-0.0007081993389874697</v>
+      </c>
+      <c r="E5">
+        <v>0.06689544022083282</v>
+      </c>
+      <c r="F5">
+        <v>0.001623521558940411</v>
+      </c>
+      <c r="G5">
+        <v>0.001470064395107329</v>
+      </c>
+      <c r="H5">
+        <v>1.001137240682899</v>
+      </c>
+      <c r="I5">
+        <v>0.04891994825573227</v>
+      </c>
+      <c r="J5">
+        <v>-0.01058666128665209</v>
+      </c>
+      <c r="K5">
+        <v>-0.9018205404281616</v>
+      </c>
+      <c r="L5">
+        <v>3.828850984573364</v>
+      </c>
+      <c r="M5">
+        <v>-0.6059418320655823</v>
+      </c>
+      <c r="N5" t="s">
+        <v>132</v>
+      </c>
+      <c r="O5" t="s">
+        <v>192</v>
+      </c>
+      <c r="P5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6">
+        <v>0.006663540906233376</v>
+      </c>
+      <c r="D6">
+        <v>0.003610121784731746</v>
+      </c>
+      <c r="E6">
+        <v>0.02629266493022442</v>
+      </c>
+      <c r="F6">
+        <v>0.002182671334594488</v>
+      </c>
+      <c r="G6">
+        <v>0.001814882387407124</v>
+      </c>
+      <c r="H6">
+        <v>1.001139458014937</v>
+      </c>
+      <c r="I6">
+        <v>0.04915346636836831</v>
+      </c>
+      <c r="J6">
+        <v>0.1373052895069122</v>
+      </c>
+      <c r="K6">
+        <v>133986.59375</v>
+      </c>
+      <c r="L6">
+        <v>1.50489616394043</v>
+      </c>
+      <c r="M6">
+        <v>7.858853816986084</v>
+      </c>
+      <c r="N6" t="s">
+        <v>133</v>
+      </c>
+      <c r="O6" t="s">
+        <v>193</v>
+      </c>
+      <c r="P6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7">
+        <v>0.01310982540403567</v>
+      </c>
+      <c r="D7">
+        <v>0.007132654543966055</v>
+      </c>
+      <c r="E7">
+        <v>0.05267377570271492</v>
+      </c>
+      <c r="F7">
+        <v>0.002654996002092957</v>
+      </c>
+      <c r="G7">
+        <v>0.002096727723255754</v>
+      </c>
+      <c r="H7">
+        <v>1.000997107562548</v>
+      </c>
+      <c r="I7">
+        <v>0.04929794908564448</v>
+      </c>
+      <c r="J7">
+        <v>0.135411873459816</v>
+      </c>
+      <c r="K7">
+        <v>12940410880</v>
+      </c>
+      <c r="L7">
+        <v>3.014854669570923</v>
+      </c>
+      <c r="M7">
+        <v>7.750481605529785</v>
+      </c>
+      <c r="N7" t="s">
+        <v>134</v>
+      </c>
+      <c r="O7" t="s">
+        <v>194</v>
+      </c>
+      <c r="P7" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8">
+        <v>0.03216097856041264</v>
+      </c>
+      <c r="D8">
+        <v>0.01734519936144352</v>
+      </c>
+      <c r="E8">
+        <v>0.1315051168203354</v>
+      </c>
+      <c r="F8">
+        <v>0.002915807999670506</v>
+      </c>
+      <c r="G8">
+        <v>0.002156128874048591</v>
+      </c>
+      <c r="H8">
+        <v>1.000737224220895</v>
+      </c>
+      <c r="I8">
+        <v>0.05075143075558838</v>
+      </c>
+      <c r="J8">
+        <v>0.1318975239992142</v>
+      </c>
+      <c r="K8">
+        <v>2.925964610666203E+24</v>
+      </c>
+      <c r="L8">
+        <v>7.526873111724854</v>
+      </c>
+      <c r="M8">
+        <v>7.549333095550537</v>
+      </c>
+      <c r="N8" t="s">
+        <v>135</v>
+      </c>
+      <c r="O8" t="s">
+        <v>195</v>
+      </c>
+      <c r="P8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9">
+        <v>0.06365464850431177</v>
+      </c>
+      <c r="D9">
+        <v>0.0341244600713253</v>
+      </c>
+      <c r="E9">
+        <v>0.2629496455192566</v>
+      </c>
+      <c r="F9">
+        <v>0.00285229180008173</v>
+      </c>
+      <c r="G9">
+        <v>0.002178045688197017</v>
+      </c>
+      <c r="H9">
+        <v>1.000459525332196</v>
+      </c>
+      <c r="I9">
+        <v>0.0523476116147411</v>
+      </c>
+      <c r="J9">
+        <v>0.1297756433486938</v>
+      </c>
+      <c r="K9" t="s">
+        <v>128</v>
+      </c>
+      <c r="L9">
+        <v>15.05027866363525</v>
+      </c>
+      <c r="M9">
+        <v>7.427884101867676</v>
+      </c>
+      <c r="N9" t="s">
+        <v>136</v>
+      </c>
+      <c r="O9" t="s">
+        <v>196</v>
+      </c>
+      <c r="P9" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10">
+        <v>0.1589829611338154</v>
+      </c>
+      <c r="D10">
+        <v>0.08484706282615662</v>
+      </c>
+      <c r="E10">
+        <v>0.6680541634559631</v>
+      </c>
+      <c r="F10">
+        <v>0.002618926111608744</v>
+      </c>
+      <c r="G10">
+        <v>0.002297504805028439</v>
+      </c>
+      <c r="H10">
+        <v>1.001259535378263</v>
+      </c>
+      <c r="I10">
+        <v>0.05748742474759053</v>
+      </c>
+      <c r="J10">
+        <v>0.1270062625408173</v>
+      </c>
+      <c r="K10" t="s">
+        <v>128</v>
+      </c>
+      <c r="L10">
+        <v>38.23698425292969</v>
+      </c>
+      <c r="M10">
+        <v>7.269374847412109</v>
+      </c>
+      <c r="N10" t="s">
+        <v>137</v>
+      </c>
+      <c r="O10" t="s">
+        <v>197</v>
+      </c>
+      <c r="P10" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11">
+        <v>0.3104409893431678</v>
+      </c>
+      <c r="D11">
+        <v>0.1655652523040771</v>
+      </c>
+      <c r="E11">
+        <v>1.23819899559021</v>
+      </c>
+      <c r="F11">
+        <v>0.002522442257031798</v>
+      </c>
+      <c r="G11">
+        <v>0.002551616402342916</v>
+      </c>
+      <c r="H11">
+        <v>1.002294981640147</v>
+      </c>
+      <c r="I11">
+        <v>0.06679485957697048</v>
+      </c>
+      <c r="J11">
+        <v>0.133714571595192</v>
+      </c>
+      <c r="K11" t="s">
+        <v>128</v>
+      </c>
+      <c r="L11">
+        <v>70.8699951171875</v>
+      </c>
+      <c r="M11">
+        <v>7.653334140777588</v>
+      </c>
+      <c r="N11" t="s">
+        <v>138</v>
+      </c>
+      <c r="O11" t="s">
+        <v>198</v>
+      </c>
+      <c r="P11" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12">
+        <v>0.001723267072087891</v>
+      </c>
+      <c r="D12">
+        <v>-8.156361582223326E-05</v>
+      </c>
+      <c r="E12">
+        <v>0.01190125476568937</v>
+      </c>
+      <c r="F12">
+        <v>0.0008512174244970083</v>
+      </c>
+      <c r="G12">
+        <v>0.0008793076267465949</v>
+      </c>
+      <c r="H12">
+        <v>1.00052926122389</v>
+      </c>
+      <c r="I12">
+        <v>0.04893552915769078</v>
+      </c>
+      <c r="J12">
+        <v>-0.006853362545371056</v>
+      </c>
+      <c r="K12">
+        <v>-0.234428882598877</v>
+      </c>
+      <c r="L12">
+        <v>0.6811844110488892</v>
+      </c>
+      <c r="M12">
+        <v>-0.3922614753246307</v>
+      </c>
+      <c r="N12" t="s">
+        <v>139</v>
+      </c>
+      <c r="O12" t="s">
+        <v>199</v>
+      </c>
+      <c r="P12" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13">
+        <v>0.00229298204692478</v>
+      </c>
+      <c r="D13">
+        <v>0.0004785640921909362</v>
+      </c>
+      <c r="E13">
+        <v>0.01548304408788681</v>
+      </c>
+      <c r="F13">
+        <v>0.001020610914565623</v>
+      </c>
+      <c r="G13">
+        <v>0.0009908939246088266</v>
+      </c>
+      <c r="H13">
+        <v>1.000766257901839</v>
+      </c>
+      <c r="I13">
+        <v>0.04888503954811831</v>
+      </c>
+      <c r="J13">
+        <v>0.03090891428291798</v>
+      </c>
+      <c r="K13">
+        <v>3.793261051177979</v>
+      </c>
+      <c r="L13">
+        <v>0.8861929178237915</v>
+      </c>
+      <c r="M13">
+        <v>1.769113421440125</v>
+      </c>
+      <c r="N13" t="s">
+        <v>140</v>
+      </c>
+      <c r="O13" t="s">
+        <v>200</v>
+      </c>
+      <c r="P13" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14">
+        <v>0.002860241738807392</v>
+      </c>
+      <c r="D14">
+        <v>0.001141761895269156</v>
+      </c>
+      <c r="E14">
+        <v>0.01834324933588505</v>
+      </c>
+      <c r="F14">
+        <v>0.00116087740752846</v>
+      </c>
+      <c r="G14">
+        <v>0.001135407947003841</v>
+      </c>
+      <c r="H14">
+        <v>1.000853275206501</v>
+      </c>
+      <c r="I14">
+        <v>0.04888601957192142</v>
+      </c>
+      <c r="J14">
+        <v>0.06224425509572029</v>
+      </c>
+      <c r="K14">
+        <v>41.02896499633789</v>
+      </c>
+      <c r="L14">
+        <v>1.049900650978088</v>
+      </c>
+      <c r="M14">
+        <v>3.562633991241455</v>
+      </c>
+      <c r="N14" t="s">
+        <v>141</v>
+      </c>
+      <c r="O14" t="s">
+        <v>201</v>
+      </c>
+      <c r="P14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15">
+        <v>0.005670849399294254</v>
+      </c>
+      <c r="D15">
+        <v>0.003015561029314995</v>
+      </c>
+      <c r="E15">
+        <v>0.03670590743422508</v>
+      </c>
+      <c r="F15">
+        <v>0.001675708335824311</v>
+      </c>
+      <c r="G15">
+        <v>0.001500888261944056</v>
+      </c>
+      <c r="H15">
+        <v>1.001063446183707</v>
+      </c>
+      <c r="I15">
+        <v>0.04890607871993943</v>
+      </c>
+      <c r="J15">
+        <v>0.08215465396642685</v>
+      </c>
+      <c r="K15">
+        <v>19224.111328125</v>
+      </c>
+      <c r="L15">
+        <v>2.100912094116211</v>
+      </c>
+      <c r="M15">
+        <v>4.702232837677002</v>
+      </c>
+      <c r="N15" t="s">
+        <v>142</v>
+      </c>
+      <c r="O15" t="s">
+        <v>202</v>
+      </c>
+      <c r="P15" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16">
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16">
+        <v>0.01120697175058488</v>
+      </c>
+      <c r="D16">
+        <v>0.006440238561481237</v>
+      </c>
+      <c r="E16">
+        <v>0.07332383096218109</v>
+      </c>
+      <c r="F16">
+        <v>0.002243630355224013</v>
+      </c>
+      <c r="G16">
+        <v>0.00184881070163101</v>
+      </c>
+      <c r="H16">
+        <v>1.001104629878274</v>
+      </c>
+      <c r="I16">
+        <v>0.04916723818210433</v>
+      </c>
+      <c r="J16">
+        <v>0.08783281594514847</v>
+      </c>
+      <c r="K16">
+        <v>1359950336</v>
+      </c>
+      <c r="L16">
+        <v>4.196788311004639</v>
+      </c>
+      <c r="M16">
+        <v>5.027229785919189</v>
+      </c>
+      <c r="N16" t="s">
+        <v>143</v>
+      </c>
+      <c r="O16" t="s">
+        <v>203</v>
+      </c>
+      <c r="P16" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17">
+        <v>0.02212692381155571</v>
+      </c>
+      <c r="D17">
+        <v>0.0126764141023159</v>
+      </c>
+      <c r="E17">
+        <v>0.1460625529289246</v>
+      </c>
+      <c r="F17">
+        <v>0.002719677751883864</v>
+      </c>
+      <c r="G17">
+        <v>0.002126855775713921</v>
+      </c>
+      <c r="H17">
+        <v>1.000965375910554</v>
+      </c>
+      <c r="I17">
+        <v>0.04927035698397949</v>
+      </c>
+      <c r="J17">
+        <v>0.08678757399320602</v>
+      </c>
+      <c r="K17">
+        <v>8.354464556185027E+17</v>
+      </c>
+      <c r="L17">
+        <v>8.360087394714355</v>
+      </c>
+      <c r="M17">
+        <v>4.967403888702393</v>
+      </c>
+      <c r="N17" t="s">
+        <v>144</v>
+      </c>
+      <c r="O17" t="s">
+        <v>204</v>
+      </c>
+      <c r="P17" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18">
+        <v>0.05473970760490588</v>
+      </c>
+      <c r="D18">
+        <v>0.03109909035265446</v>
+      </c>
+      <c r="E18">
+        <v>0.3663161993026733</v>
+      </c>
+      <c r="F18">
+        <v>0.002961074002087116</v>
+      </c>
+      <c r="G18">
+        <v>0.002164172008633614</v>
+      </c>
+      <c r="H18">
+        <v>1.000762905192541</v>
+      </c>
+      <c r="I18">
+        <v>0.05070113268118612</v>
+      </c>
+      <c r="J18">
+        <v>0.08489684760570526</v>
+      </c>
+      <c r="K18" t="s">
+        <v>128</v>
+      </c>
+      <c r="L18">
+        <v>20.96660232543945</v>
+      </c>
+      <c r="M18">
+        <v>4.859185695648193</v>
+      </c>
+      <c r="N18" t="s">
+        <v>145</v>
+      </c>
+      <c r="O18" t="s">
+        <v>205</v>
+      </c>
+      <c r="P18" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="B19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19">
+        <v>0.1077994336853614</v>
+      </c>
+      <c r="D19">
+        <v>0.0609947182238102</v>
+      </c>
+      <c r="E19">
+        <v>0.7184882164001465</v>
+      </c>
+      <c r="F19">
+        <v>0.002869694726541638</v>
+      </c>
+      <c r="G19">
+        <v>0.002193794818595052</v>
+      </c>
+      <c r="H19">
+        <v>1.000521242229765</v>
+      </c>
+      <c r="I19">
+        <v>0.05230503043770476</v>
+      </c>
+      <c r="J19">
+        <v>0.08489313721656799</v>
+      </c>
+      <c r="K19" t="s">
+        <v>128</v>
+      </c>
+      <c r="L19">
+        <v>41.12364196777344</v>
+      </c>
+      <c r="M19">
+        <v>4.858973503112793</v>
+      </c>
+      <c r="N19" t="s">
+        <v>146</v>
+      </c>
+      <c r="O19" t="s">
+        <v>206</v>
+      </c>
+      <c r="P19" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20">
+        <v>0</v>
+      </c>
+      <c r="B20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20">
+        <v>0.2703179463159093</v>
+      </c>
+      <c r="D20">
+        <v>0.1524032950401306</v>
+      </c>
+      <c r="E20">
+        <v>1.828014373779297</v>
+      </c>
+      <c r="F20">
+        <v>0.002612120704725385</v>
+      </c>
+      <c r="G20">
+        <v>0.002307193819433451</v>
+      </c>
+      <c r="H20">
+        <v>1.001191535922258</v>
+      </c>
+      <c r="I20">
+        <v>0.05758748137680988</v>
+      </c>
+      <c r="J20">
+        <v>0.08337094634771347</v>
+      </c>
+      <c r="K20" t="s">
+        <v>128</v>
+      </c>
+      <c r="L20">
+        <v>104.6288757324219</v>
+      </c>
+      <c r="M20">
+        <v>4.771848678588867</v>
+      </c>
+      <c r="N20" t="s">
+        <v>147</v>
+      </c>
+      <c r="O20" t="s">
+        <v>207</v>
+      </c>
+      <c r="P20" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21">
+        <v>0</v>
+      </c>
+      <c r="B21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21">
+        <v>0.5260619026781979</v>
+      </c>
+      <c r="D21">
+        <v>0.2974801659584045</v>
+      </c>
+      <c r="E21">
+        <v>3.377854585647583</v>
+      </c>
+      <c r="F21">
+        <v>0.002530313329771161</v>
+      </c>
+      <c r="G21">
+        <v>0.002570838667452335</v>
+      </c>
+      <c r="H21">
+        <v>1.002294981640147</v>
+      </c>
+      <c r="I21">
+        <v>0.06679485957697048</v>
+      </c>
+      <c r="J21">
+        <v>0.08806778490543365</v>
+      </c>
+      <c r="K21" t="s">
+        <v>128</v>
+      </c>
+      <c r="L21">
+        <v>193.3360748291016</v>
+      </c>
+      <c r="M21">
+        <v>5.04067850112915</v>
+      </c>
+      <c r="N21" t="s">
+        <v>148</v>
+      </c>
+      <c r="O21" t="s">
+        <v>208</v>
+      </c>
+      <c r="P21" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22">
+        <v>0.0006822522345817392</v>
+      </c>
+      <c r="D22">
+        <v>-0.0002357302291784436</v>
+      </c>
+      <c r="E22">
+        <v>0.002924905391409993</v>
+      </c>
+      <c r="F22">
+        <v>0.0008850856684148312</v>
+      </c>
+      <c r="G22">
+        <v>0.0008865539566613734</v>
+      </c>
+      <c r="H22">
+        <v>1.000467898706979</v>
+      </c>
+      <c r="I22">
+        <v>0.04895588648411707</v>
+      </c>
+      <c r="J22">
+        <v>-0.08059413731098175</v>
+      </c>
+      <c r="K22">
+        <v>-0.5380799174308777</v>
+      </c>
+      <c r="L22">
+        <v>0.1674109101295471</v>
+      </c>
+      <c r="M22">
+        <v>-4.612914562225342</v>
+      </c>
+      <c r="N22" t="s">
+        <v>149</v>
+      </c>
+      <c r="O22" t="s">
+        <v>209</v>
+      </c>
+      <c r="P22" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23">
+        <v>0.0009040484370397762</v>
+      </c>
+      <c r="D23">
+        <v>6.339714309433475E-05</v>
+      </c>
+      <c r="E23">
+        <v>0.00375123112462461</v>
+      </c>
+      <c r="F23">
+        <v>0.001055320259183645</v>
+      </c>
+      <c r="G23">
+        <v>0.001030438113957644</v>
+      </c>
+      <c r="H23">
+        <v>1.000716699166875</v>
+      </c>
+      <c r="I23">
+        <v>0.04888810605443537</v>
+      </c>
+      <c r="J23">
+        <v>0.01690035685896873</v>
+      </c>
+      <c r="K23">
+        <v>0.2309117317199707</v>
+      </c>
+      <c r="L23">
+        <v>0.2147067785263062</v>
+      </c>
+      <c r="M23">
+        <v>0.9673147797584534</v>
+      </c>
+      <c r="N23" t="s">
+        <v>150</v>
+      </c>
+      <c r="O23" t="s">
+        <v>210</v>
+      </c>
+      <c r="P23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24">
+        <v>0</v>
+      </c>
+      <c r="B24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24">
+        <v>0.001122920970162164</v>
+      </c>
+      <c r="D24">
+        <v>0.0003077120054513216</v>
+      </c>
+      <c r="E24">
+        <v>0.004635926801711321</v>
+      </c>
+      <c r="F24">
+        <v>0.00121388747356832</v>
+      </c>
+      <c r="G24">
+        <v>0.001172160147689283</v>
+      </c>
+      <c r="H24">
+        <v>1.000822037677919</v>
+      </c>
+      <c r="I24">
+        <v>0.04889712578383524</v>
+      </c>
+      <c r="J24">
+        <v>0.06637550890445709</v>
+      </c>
+      <c r="K24">
+        <v>1.739572763442993</v>
+      </c>
+      <c r="L24">
+        <v>0.2653435468673706</v>
+      </c>
+      <c r="M24">
+        <v>3.799091815948486</v>
+      </c>
+      <c r="N24" t="s">
+        <v>151</v>
+      </c>
+      <c r="O24" t="s">
+        <v>211</v>
+      </c>
+      <c r="P24" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25">
+        <v>0</v>
+      </c>
+      <c r="B25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25">
+        <v>0.002183678379079013</v>
+      </c>
+      <c r="D25">
+        <v>0.001145779620856047</v>
+      </c>
+      <c r="E25">
+        <v>0.00913267582654953</v>
+      </c>
+      <c r="F25">
+        <v>0.001750470139086246</v>
+      </c>
+      <c r="G25">
+        <v>0.00153865956235677</v>
+      </c>
+      <c r="H25">
+        <v>1.001026832072036</v>
+      </c>
+      <c r="I25">
+        <v>0.04893035334958763</v>
+      </c>
+      <c r="J25">
+        <v>0.1254593580961227</v>
+      </c>
+      <c r="K25">
+        <v>41.57349014282227</v>
+      </c>
+      <c r="L25">
+        <v>0.5227210521697998</v>
+      </c>
+      <c r="M25">
+        <v>7.180835723876953</v>
+      </c>
+      <c r="N25" t="s">
+        <v>152</v>
+      </c>
+      <c r="O25" t="s">
+        <v>212</v>
+      </c>
+      <c r="P25" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26">
+        <v>0</v>
+      </c>
+      <c r="B26" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26">
+        <v>0.004218778498765066</v>
+      </c>
+      <c r="D26">
+        <v>0.002352281240746379</v>
+      </c>
+      <c r="E26">
+        <v>0.01819942705333233</v>
+      </c>
+      <c r="F26">
+        <v>0.002316545695066452</v>
+      </c>
+      <c r="G26">
+        <v>0.00188416603486985</v>
+      </c>
+      <c r="H26">
+        <v>1.001051725913894</v>
+      </c>
+      <c r="I26">
+        <v>0.04916309091851311</v>
+      </c>
+      <c r="J26">
+        <v>0.1292502880096436</v>
+      </c>
+      <c r="K26">
+        <v>2200.47265625</v>
+      </c>
+      <c r="L26">
+        <v>1.041668772697449</v>
+      </c>
+      <c r="M26">
+        <v>7.397814750671387</v>
+      </c>
+      <c r="N26" t="s">
+        <v>153</v>
+      </c>
+      <c r="O26" t="s">
+        <v>213</v>
+      </c>
+      <c r="P26" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27">
+        <v>0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27">
+        <v>0.008176656028151119</v>
+      </c>
+      <c r="D27">
+        <v>0.00450826995074749</v>
+      </c>
+      <c r="E27">
+        <v>0.03646796569228172</v>
+      </c>
+      <c r="F27">
+        <v>0.002796054817736149</v>
+      </c>
+      <c r="G27">
+        <v>0.002150331158190966</v>
+      </c>
+      <c r="H27">
+        <v>1.000929491085092</v>
+      </c>
+      <c r="I27">
+        <v>0.04923989884574686</v>
+      </c>
+      <c r="J27">
+        <v>0.1236227452754974</v>
+      </c>
+      <c r="K27">
+        <v>2510161.5</v>
+      </c>
+      <c r="L27">
+        <v>2.087293386459351</v>
+      </c>
+      <c r="M27">
+        <v>7.075715065002441</v>
+      </c>
+      <c r="N27" t="s">
+        <v>154</v>
+      </c>
+      <c r="O27" t="s">
+        <v>214</v>
+      </c>
+      <c r="P27" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="B28" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28">
+        <v>0.0197812350068714</v>
+      </c>
+      <c r="D28">
+        <v>0.01051892712712288</v>
+      </c>
+      <c r="E28">
+        <v>0.09080538153648376</v>
+      </c>
+      <c r="F28">
+        <v>0.002988465595990419</v>
+      </c>
+      <c r="G28">
+        <v>0.002185532590374351</v>
+      </c>
+      <c r="H28">
+        <v>1.000807322523818</v>
+      </c>
+      <c r="I28">
+        <v>0.05071419831136231</v>
+      </c>
+      <c r="J28">
+        <v>0.1158403530716896</v>
+      </c>
+      <c r="K28">
+        <v>771968429195264</v>
+      </c>
+      <c r="L28">
+        <v>5.197368621826172</v>
+      </c>
+      <c r="M28">
+        <v>6.630279064178467</v>
+      </c>
+      <c r="N28" t="s">
+        <v>155</v>
+      </c>
+      <c r="O28" t="s">
+        <v>215</v>
+      </c>
+      <c r="P28" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29">
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29">
+        <v>0.03920789620740933</v>
+      </c>
+      <c r="D29">
+        <v>0.02097158692777157</v>
+      </c>
+      <c r="E29">
+        <v>0.1843648999929428</v>
+      </c>
+      <c r="F29">
+        <v>0.002869572723284364</v>
+      </c>
+      <c r="G29">
+        <v>0.002209815429523587</v>
+      </c>
+      <c r="H29">
+        <v>1.000571893377351</v>
+      </c>
+      <c r="I29">
+        <v>0.05214385013165069</v>
+      </c>
+      <c r="J29">
+        <v>0.1137504279613495</v>
+      </c>
+      <c r="K29">
+        <v>3.378059105345472E+29</v>
+      </c>
+      <c r="L29">
+        <v>10.5523738861084</v>
+      </c>
+      <c r="M29">
+        <v>6.510659217834473</v>
+      </c>
+      <c r="N29" t="s">
+        <v>156</v>
+      </c>
+      <c r="O29" t="s">
+        <v>216</v>
+      </c>
+      <c r="P29" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30">
+        <v>0.09575416644805497</v>
+      </c>
+      <c r="D30">
+        <v>0.05070452392101288</v>
+      </c>
+      <c r="E30">
+        <v>0.45087069272995</v>
+      </c>
+      <c r="F30">
+        <v>0.002634426113218069</v>
+      </c>
+      <c r="G30">
+        <v>0.002351016737520695</v>
+      </c>
+      <c r="H30">
+        <v>1.001327534834267</v>
+      </c>
+      <c r="I30">
+        <v>0.05745298505740964</v>
+      </c>
+      <c r="J30">
+        <v>0.112459123134613</v>
+      </c>
+      <c r="K30" t="s">
+        <v>128</v>
+      </c>
+      <c r="L30">
+        <v>25.80619239807129</v>
+      </c>
+      <c r="M30">
+        <v>6.436749935150146</v>
+      </c>
+      <c r="N30" t="s">
+        <v>157</v>
+      </c>
+      <c r="O30" t="s">
+        <v>217</v>
+      </c>
+      <c r="P30" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31">
+        <v>0</v>
+      </c>
+      <c r="B31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31">
+        <v>0.1948817510408083</v>
+      </c>
+      <c r="D31">
+        <v>0.1026887223124504</v>
+      </c>
+      <c r="E31">
+        <v>0.9872246384620667</v>
+      </c>
+      <c r="F31">
+        <v>0.002571019576862454</v>
+      </c>
+      <c r="G31">
+        <v>0.002634482691064477</v>
+      </c>
+      <c r="H31">
+        <v>1.002417380660955</v>
+      </c>
+      <c r="I31">
+        <v>0.06651474321265036</v>
+      </c>
+      <c r="J31">
+        <v>0.104017585515976</v>
+      </c>
+      <c r="K31" t="s">
+        <v>128</v>
+      </c>
+      <c r="L31">
+        <v>56.50513458251953</v>
+      </c>
+      <c r="M31">
+        <v>5.953587055206299</v>
+      </c>
+      <c r="N31" t="s">
+        <v>158</v>
+      </c>
+      <c r="O31" t="s">
+        <v>218</v>
+      </c>
+      <c r="P31" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32">
+        <v>0</v>
+      </c>
+      <c r="B32" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32">
+        <v>0.0005969128192975974</v>
+      </c>
+      <c r="D32">
+        <v>-6.04798951826524E-05</v>
+      </c>
+      <c r="E32">
+        <v>0.003251031739637256</v>
+      </c>
+      <c r="F32">
+        <v>0.0009257733472622931</v>
+      </c>
+      <c r="G32">
+        <v>0.0009089020313695073</v>
+      </c>
+      <c r="H32">
+        <v>1.000408254234385</v>
+      </c>
+      <c r="I32">
+        <v>0.04898244594226519</v>
+      </c>
+      <c r="J32">
+        <v>-0.01860329322516918</v>
+      </c>
+      <c r="K32">
+        <v>-0.1797940135002136</v>
+      </c>
+      <c r="L32">
+        <v>0.1860771924257278</v>
+      </c>
+      <c r="M32">
+        <v>-1.064784646034241</v>
+      </c>
+      <c r="N32" t="s">
+        <v>159</v>
+      </c>
+      <c r="O32" t="s">
+        <v>219</v>
+      </c>
+      <c r="P32" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33">
+        <v>0</v>
+      </c>
+      <c r="B33" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33">
+        <v>0.0007882858955686544</v>
+      </c>
+      <c r="D33">
+        <v>0.0001736059930408373</v>
+      </c>
+      <c r="E33">
+        <v>0.004238356836140156</v>
+      </c>
+      <c r="F33">
+        <v>0.00111927546095103</v>
+      </c>
+      <c r="G33">
+        <v>0.00108557369094342</v>
+      </c>
+      <c r="H33">
+        <v>1.000612763981562</v>
+      </c>
+      <c r="I33">
+        <v>0.04893700836608734</v>
+      </c>
+      <c r="J33">
+        <v>0.04096068441867828</v>
+      </c>
+      <c r="K33">
+        <v>0.7657257318496704</v>
+      </c>
+      <c r="L33">
+        <v>0.242588073015213</v>
+      </c>
+      <c r="M33">
+        <v>2.344440221786499</v>
+      </c>
+      <c r="N33" t="s">
+        <v>160</v>
+      </c>
+      <c r="O33" t="s">
+        <v>220</v>
+      </c>
+      <c r="P33" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C34">
+        <v>0.0009759174607764713</v>
+      </c>
+      <c r="D34">
+        <v>0.0003685480041895062</v>
+      </c>
+      <c r="E34">
+        <v>0.005254292394965887</v>
+      </c>
+      <c r="F34">
+        <v>0.001278528710827231</v>
+      </c>
+      <c r="G34">
+        <v>0.001217328826896846</v>
+      </c>
+      <c r="H34">
+        <v>1.000708829836743</v>
+      </c>
+      <c r="I34">
+        <v>0.04897453406212497</v>
+      </c>
+      <c r="J34">
+        <v>0.07014226913452148</v>
+      </c>
+      <c r="K34">
+        <v>2.344426155090332</v>
+      </c>
+      <c r="L34">
+        <v>0.3007365167140961</v>
+      </c>
+      <c r="M34">
+        <v>4.014687538146973</v>
+      </c>
+      <c r="N34" t="s">
+        <v>161</v>
+      </c>
+      <c r="O34" t="s">
+        <v>221</v>
+      </c>
+      <c r="P34" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35">
+        <v>0</v>
+      </c>
+      <c r="B35" t="s">
+        <v>102</v>
+      </c>
+      <c r="C35">
+        <v>0.001876626248306467</v>
+      </c>
+      <c r="D35">
+        <v>0.001052686828188598</v>
+      </c>
+      <c r="E35">
+        <v>0.0103917783126235</v>
+      </c>
+      <c r="F35">
+        <v>0.001824424718506634</v>
+      </c>
+      <c r="G35">
+        <v>0.001586646540090442</v>
+      </c>
+      <c r="H35">
+        <v>1.000921100036051</v>
+      </c>
+      <c r="I35">
+        <v>0.04896070069875758</v>
+      </c>
+      <c r="J35">
+        <v>0.1012999713420868</v>
+      </c>
+      <c r="K35">
+        <v>30.40456008911133</v>
+      </c>
+      <c r="L35">
+        <v>0.5947874784469604</v>
+      </c>
+      <c r="M35">
+        <v>5.798040866851807</v>
+      </c>
+      <c r="N35" t="s">
+        <v>162</v>
+      </c>
+      <c r="O35" t="s">
+        <v>222</v>
+      </c>
+      <c r="P35" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="B36" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36">
+        <v>0.003586914295923911</v>
+      </c>
+      <c r="D36">
+        <v>0.002148383064195514</v>
+      </c>
+      <c r="E36">
+        <v>0.02052854374051094</v>
+      </c>
+      <c r="F36">
+        <v>0.002404559403657913</v>
+      </c>
+      <c r="G36">
+        <v>0.001938453293405473</v>
+      </c>
+      <c r="H36">
+        <v>1.000958326937508</v>
+      </c>
+      <c r="I36">
+        <v>0.04921720277672809</v>
+      </c>
+      <c r="J36">
+        <v>0.1046534553170204</v>
+      </c>
+      <c r="K36">
+        <v>1129.68115234375</v>
+      </c>
+      <c r="L36">
+        <v>1.174978971481323</v>
+      </c>
+      <c r="M36">
+        <v>5.989982128143311</v>
+      </c>
+      <c r="N36" t="s">
+        <v>163</v>
+      </c>
+      <c r="O36" t="s">
+        <v>223</v>
+      </c>
+      <c r="P36" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37">
+        <v>0</v>
+      </c>
+      <c r="B37" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37">
+        <v>0.006877606952772608</v>
+      </c>
+      <c r="D37">
+        <v>0.00396040640771389</v>
+      </c>
+      <c r="E37">
+        <v>0.04102139547467232</v>
+      </c>
+      <c r="F37">
+        <v>0.002873682416975498</v>
+      </c>
+      <c r="G37">
+        <v>0.002184180309996009</v>
+      </c>
+      <c r="H37">
+        <v>1.000830895920322</v>
+      </c>
+      <c r="I37">
+        <v>0.04933478056434331</v>
+      </c>
+      <c r="J37">
+        <v>0.09654489904642105</v>
+      </c>
+      <c r="K37">
+        <v>420226.625</v>
+      </c>
+      <c r="L37">
+        <v>2.347914934158325</v>
+      </c>
+      <c r="M37">
+        <v>5.525877952575684</v>
+      </c>
+      <c r="N37" t="s">
+        <v>164</v>
+      </c>
+      <c r="O37" t="s">
+        <v>224</v>
+      </c>
+      <c r="P37" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38">
+        <v>0</v>
+      </c>
+      <c r="B38" t="s">
+        <v>105</v>
+      </c>
+      <c r="C38">
+        <v>0.01651771387880842</v>
+      </c>
+      <c r="D38">
+        <v>0.009070256724953651</v>
+      </c>
+      <c r="E38">
+        <v>0.1025295928120613</v>
+      </c>
+      <c r="F38">
+        <v>0.003021964337676764</v>
+      </c>
+      <c r="G38">
+        <v>0.002205620286986232</v>
+      </c>
+      <c r="H38">
+        <v>1.000762399550391</v>
+      </c>
+      <c r="I38">
+        <v>0.05073063896436553</v>
+      </c>
+      <c r="J38">
+        <v>0.08846476674079895</v>
+      </c>
+      <c r="K38">
+        <v>7023475818496</v>
+      </c>
+      <c r="L38">
+        <v>5.868419647216797</v>
+      </c>
+      <c r="M38">
+        <v>5.063400268554688</v>
+      </c>
+      <c r="N38" t="s">
+        <v>165</v>
+      </c>
+      <c r="O38" t="s">
+        <v>225</v>
+      </c>
+      <c r="P38" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39">
+        <v>0.03238361374347552</v>
+      </c>
+      <c r="D39">
+        <v>0.01738790236413479</v>
+      </c>
+      <c r="E39">
+        <v>0.2051113247871399</v>
+      </c>
+      <c r="F39">
+        <v>0.002876629354432225</v>
+      </c>
+      <c r="G39">
+        <v>0.002224672585725784</v>
+      </c>
+      <c r="H39">
+        <v>1.000545284894566</v>
+      </c>
+      <c r="I39">
+        <v>0.05217189511782164</v>
+      </c>
+      <c r="J39">
+        <v>0.0847729966044426</v>
+      </c>
+      <c r="K39">
+        <v>3.356998438451904E+24</v>
+      </c>
+      <c r="L39">
+        <v>11.73982334136963</v>
+      </c>
+      <c r="M39">
+        <v>4.852097034454346</v>
+      </c>
+      <c r="N39" t="s">
+        <v>166</v>
+      </c>
+      <c r="O39" t="s">
+        <v>226</v>
+      </c>
+      <c r="P39" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40">
+        <v>0</v>
+      </c>
+      <c r="B40" t="s">
+        <v>107</v>
+      </c>
+      <c r="C40">
+        <v>0.07834820742249611</v>
+      </c>
+      <c r="D40">
+        <v>0.04145744442939758</v>
+      </c>
+      <c r="E40">
+        <v>0.5000109076499939</v>
+      </c>
+      <c r="F40">
+        <v>0.002669230103492737</v>
+      </c>
+      <c r="G40">
+        <v>0.002429784275591373</v>
+      </c>
+      <c r="H40">
+        <v>1.001266335323863</v>
+      </c>
+      <c r="I40">
+        <v>0.05742769980278833</v>
+      </c>
+      <c r="J40">
+        <v>0.08291307836771011</v>
+      </c>
+      <c r="K40" t="s">
+        <v>128</v>
+      </c>
+      <c r="L40">
+        <v>28.61879920959473</v>
+      </c>
+      <c r="M40">
+        <v>4.745642185211182</v>
+      </c>
+      <c r="N40" t="s">
+        <v>167</v>
+      </c>
+      <c r="O40" t="s">
+        <v>227</v>
+      </c>
+      <c r="P40" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41">
+        <v>0</v>
+      </c>
+      <c r="B41" t="s">
+        <v>108</v>
+      </c>
+      <c r="C41">
+        <v>0.1630866792942786</v>
+      </c>
+      <c r="D41">
+        <v>0.08574061840772629</v>
+      </c>
+      <c r="E41">
+        <v>1.102043986320496</v>
+      </c>
+      <c r="F41">
+        <v>0.002592786913737655</v>
+      </c>
+      <c r="G41">
+        <v>0.002647426445037127</v>
+      </c>
+      <c r="H41">
+        <v>1.002417380660955</v>
+      </c>
+      <c r="I41">
+        <v>0.06651474321265036</v>
+      </c>
+      <c r="J41">
+        <v>0.07780145108699799</v>
+      </c>
+      <c r="K41" t="s">
+        <v>128</v>
+      </c>
+      <c r="L41">
+        <v>63.07697677612305</v>
+      </c>
+      <c r="M41">
+        <v>4.453071117401123</v>
+      </c>
+      <c r="N41" t="s">
+        <v>168</v>
+      </c>
+      <c r="O41" t="s">
+        <v>228</v>
+      </c>
+      <c r="P41" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42">
+        <v>0</v>
+      </c>
+      <c r="B42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C42">
+        <v>0.00019924359358437</v>
+      </c>
+      <c r="D42">
+        <v>1.874218105513137E-05</v>
+      </c>
+      <c r="E42">
+        <v>0.001506942440755665</v>
+      </c>
+      <c r="F42">
+        <v>0.0009822893189266324</v>
+      </c>
+      <c r="G42">
+        <v>0.0009685127297416329</v>
+      </c>
+      <c r="H42">
+        <v>1.000228443395394</v>
+      </c>
+      <c r="I42">
+        <v>0.04919483740004945</v>
+      </c>
+      <c r="J42">
+        <v>0.01243722438812256</v>
+      </c>
+      <c r="K42">
+        <v>0.06323122978210449</v>
+      </c>
+      <c r="L42">
+        <v>0.0862518846988678</v>
+      </c>
+      <c r="M42">
+        <v>0.7118613123893738</v>
+      </c>
+      <c r="N42" t="s">
+        <v>169</v>
+      </c>
+      <c r="O42" t="s">
+        <v>229</v>
+      </c>
+      <c r="P42" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43">
+        <v>0</v>
+      </c>
+      <c r="B43" t="s">
+        <v>110</v>
+      </c>
+      <c r="C43">
+        <v>0.0002545392056276249</v>
+      </c>
+      <c r="D43">
+        <v>0.0001421078632120043</v>
+      </c>
+      <c r="E43">
+        <v>0.0009263649699278176</v>
+      </c>
+      <c r="F43">
+        <v>0.001178291509859264</v>
+      </c>
+      <c r="G43">
+        <v>0.001138201216235757</v>
+      </c>
+      <c r="H43">
+        <v>1.000439248168745</v>
+      </c>
+      <c r="I43">
+        <v>0.04910644680593987</v>
+      </c>
+      <c r="J43">
+        <v>0.1534037590026855</v>
+      </c>
+      <c r="K43">
+        <v>0.5927757024765015</v>
+      </c>
+      <c r="L43">
+        <v>0.05302175134420395</v>
+      </c>
+      <c r="M43">
+        <v>8.780271530151367</v>
+      </c>
+      <c r="N43" t="s">
+        <v>170</v>
+      </c>
+      <c r="O43" t="s">
+        <v>230</v>
+      </c>
+      <c r="P43" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44">
+        <v>0</v>
+      </c>
+      <c r="B44" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44">
+        <v>0.0003050504726041457</v>
+      </c>
+      <c r="D44">
+        <v>0.0002368538698647171</v>
+      </c>
+      <c r="E44">
+        <v>0.001034280750900507</v>
+      </c>
+      <c r="F44">
+        <v>0.001357824075967073</v>
+      </c>
+      <c r="G44">
+        <v>0.001275096670724452</v>
+      </c>
+      <c r="H44">
+        <v>1.000580867170201</v>
+      </c>
+      <c r="I44">
+        <v>0.04905984319598113</v>
+      </c>
+      <c r="J44">
+        <v>0.2290034592151642</v>
+      </c>
+      <c r="K44">
+        <v>1.172525882720947</v>
+      </c>
+      <c r="L44">
+        <v>0.05919845774769783</v>
+      </c>
+      <c r="M44">
+        <v>13.10732269287109</v>
+      </c>
+      <c r="N44" t="s">
+        <v>171</v>
+      </c>
+      <c r="O44" t="s">
+        <v>231</v>
+      </c>
+      <c r="P44" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45">
+        <v>0</v>
+      </c>
+      <c r="B45" t="s">
+        <v>112</v>
+      </c>
+      <c r="C45">
+        <v>0.0005122335529941117</v>
+      </c>
+      <c r="D45">
+        <v>0.0005096917739138007</v>
+      </c>
+      <c r="E45">
+        <v>0.001488537178374827</v>
+      </c>
+      <c r="F45">
+        <v>0.001932949176989496</v>
+      </c>
+      <c r="G45">
+        <v>0.001652198145166039</v>
+      </c>
+      <c r="H45">
+        <v>1.000829364425308</v>
+      </c>
+      <c r="I45">
+        <v>0.04910969876871363</v>
+      </c>
+      <c r="J45">
+        <v>0.3424111902713776</v>
+      </c>
+      <c r="K45">
+        <v>4.309401988983154</v>
+      </c>
+      <c r="L45">
+        <v>0.08519843965768814</v>
+      </c>
+      <c r="M45">
+        <v>19.59836769104004</v>
+      </c>
+      <c r="N45" t="s">
+        <v>172</v>
+      </c>
+      <c r="O45" t="s">
+        <v>232</v>
+      </c>
+      <c r="P45" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46">
+        <v>0</v>
+      </c>
+      <c r="B46" t="s">
+        <v>113</v>
+      </c>
+      <c r="C46">
+        <v>0.0008209258144532564</v>
+      </c>
+      <c r="D46">
+        <v>0.0007959717768244445</v>
+      </c>
+      <c r="E46">
+        <v>0.002527877921238542</v>
+      </c>
+      <c r="F46">
+        <v>0.002525095595046878</v>
+      </c>
+      <c r="G46">
+        <v>0.002007114933803678</v>
+      </c>
+      <c r="H46">
+        <v>1.000892603190966</v>
+      </c>
+      <c r="I46">
+        <v>0.04930582122782975</v>
+      </c>
+      <c r="J46">
+        <v>0.314877450466156</v>
+      </c>
+      <c r="K46">
+        <v>12.5519323348999</v>
+      </c>
+      <c r="L46">
+        <v>0.1446865051984787</v>
+      </c>
+      <c r="M46">
+        <v>18.02243614196777</v>
+      </c>
+      <c r="N46" t="s">
+        <v>173</v>
+      </c>
+      <c r="O46" t="s">
+        <v>233</v>
+      </c>
+      <c r="P46" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47">
+        <v>0</v>
+      </c>
+      <c r="B47" t="s">
+        <v>114</v>
+      </c>
+      <c r="C47">
+        <v>0.001309206189384814</v>
+      </c>
+      <c r="D47">
+        <v>0.001144556910730898</v>
+      </c>
+      <c r="E47">
+        <v>0.004602119792252779</v>
+      </c>
+      <c r="F47">
+        <v>0.002974976785480976</v>
+      </c>
+      <c r="G47">
+        <v>0.002224353840574622</v>
+      </c>
+      <c r="H47">
+        <v>1.00068078268614</v>
+      </c>
+      <c r="I47">
+        <v>0.04942837249506987</v>
+      </c>
+      <c r="J47">
+        <v>0.2487021088600159</v>
+      </c>
+      <c r="K47">
+        <v>41.40774154663086</v>
+      </c>
+      <c r="L47">
+        <v>0.2634085416793823</v>
+      </c>
+      <c r="M47">
+        <v>14.23480129241943</v>
+      </c>
+      <c r="N47" t="s">
+        <v>174</v>
+      </c>
+      <c r="O47" t="s">
+        <v>234</v>
+      </c>
+      <c r="P47" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48">
+        <v>0</v>
+      </c>
+      <c r="B48" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48">
+        <v>0.00252942099386052</v>
+      </c>
+      <c r="D48">
+        <v>0.001849144580774009</v>
+      </c>
+      <c r="E48">
+        <v>0.01092623174190521</v>
+      </c>
+      <c r="F48">
+        <v>0.003018217394128442</v>
+      </c>
+      <c r="G48">
+        <v>0.002217957517132163</v>
+      </c>
+      <c r="H48">
+        <v>1.000549521961876</v>
+      </c>
+      <c r="I48">
+        <v>0.05094311126913416</v>
+      </c>
+      <c r="J48">
+        <v>0.1692389994859695</v>
+      </c>
+      <c r="K48">
+        <v>424.0902404785156</v>
+      </c>
+      <c r="L48">
+        <v>0.6253776550292969</v>
+      </c>
+      <c r="M48">
+        <v>9.686622619628906</v>
+      </c>
+      <c r="N48" t="s">
+        <v>175</v>
+      </c>
+      <c r="O48" t="s">
+        <v>235</v>
+      </c>
+      <c r="P48" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49">
+        <v>0</v>
+      </c>
+      <c r="B49" t="s">
+        <v>116</v>
+      </c>
+      <c r="C49">
+        <v>0.004337488972161529</v>
+      </c>
+      <c r="D49">
+        <v>0.002851582132279873</v>
+      </c>
+      <c r="E49">
+        <v>0.02118486538529396</v>
+      </c>
+      <c r="F49">
+        <v>0.002862566616386175</v>
+      </c>
+      <c r="G49">
+        <v>0.002257351530715823</v>
+      </c>
+      <c r="H49">
+        <v>1.000232015327258</v>
+      </c>
+      <c r="I49">
+        <v>0.052562406234497</v>
+      </c>
+      <c r="J49">
+        <v>0.1346046924591064</v>
+      </c>
+      <c r="K49">
+        <v>11253.96875</v>
+      </c>
+      <c r="L49">
+        <v>1.212544441223145</v>
+      </c>
+      <c r="M49">
+        <v>7.704281330108643</v>
+      </c>
+      <c r="N49" t="s">
+        <v>176</v>
+      </c>
+      <c r="O49" t="s">
+        <v>236</v>
+      </c>
+      <c r="P49" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50">
+        <v>0</v>
+      </c>
+      <c r="B50" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50">
+        <v>0.009599166751422496</v>
+      </c>
+      <c r="D50">
+        <v>0.005672892555594444</v>
+      </c>
+      <c r="E50">
+        <v>0.05425257235765457</v>
+      </c>
+      <c r="F50">
+        <v>0.002670676214620471</v>
+      </c>
+      <c r="G50">
+        <v>0.002469491912052035</v>
+      </c>
+      <c r="H50">
+        <v>1.000994337499845</v>
+      </c>
+      <c r="I50">
+        <v>0.05789222431688975</v>
+      </c>
+      <c r="J50">
+        <v>0.1045644879341125</v>
+      </c>
+      <c r="K50">
+        <v>111776096</v>
+      </c>
+      <c r="L50">
+        <v>3.10521936416626</v>
+      </c>
+      <c r="M50">
+        <v>5.984889507293701</v>
+      </c>
+      <c r="N50" t="s">
+        <v>177</v>
+      </c>
+      <c r="O50" t="s">
+        <v>237</v>
+      </c>
+      <c r="P50" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51">
+        <v>0</v>
+      </c>
+      <c r="B51" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51">
+        <v>0.01740919361499568</v>
+      </c>
+      <c r="D51">
+        <v>0.009834945201873779</v>
+      </c>
+      <c r="E51">
+        <v>0.1012747660279274</v>
+      </c>
+      <c r="F51">
+        <v>0.002594875637441874</v>
+      </c>
+      <c r="G51">
+        <v>0.00253947195596993</v>
+      </c>
+      <c r="H51">
+        <v>1.002570379436964</v>
+      </c>
+      <c r="I51">
+        <v>0.06636489074762002</v>
+      </c>
+      <c r="J51">
+        <v>0.09711150825023651</v>
+      </c>
+      <c r="K51">
+        <v>84019299483648</v>
+      </c>
+      <c r="L51">
+        <v>5.796597957611084</v>
+      </c>
+      <c r="M51">
+        <v>5.558308601379395</v>
+      </c>
+      <c r="N51" t="s">
+        <v>178</v>
+      </c>
+      <c r="O51" t="s">
+        <v>238</v>
+      </c>
+      <c r="P51" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52">
+        <v>0</v>
+      </c>
+      <c r="B52" t="s">
+        <v>119</v>
+      </c>
+      <c r="C52">
+        <v>0.0002153375631379222</v>
+      </c>
+      <c r="D52">
+        <v>0.0003069719823542982</v>
+      </c>
+      <c r="E52">
+        <v>0.0006897940766066313</v>
+      </c>
+      <c r="F52">
+        <v>0.001095964689739048</v>
+      </c>
+      <c r="G52">
+        <v>0.001061031362041831</v>
+      </c>
+      <c r="H52">
+        <v>0.9996293862812106</v>
+      </c>
+      <c r="I52">
+        <v>0.04957148312149522</v>
+      </c>
+      <c r="J52">
+        <v>0.4450197517871857</v>
+      </c>
+      <c r="K52">
+        <v>1.733162879943848</v>
+      </c>
+      <c r="L52">
+        <v>0.03948129713535309</v>
+      </c>
+      <c r="M52">
+        <v>25.47130584716797</v>
+      </c>
+      <c r="N52" t="s">
+        <v>179</v>
+      </c>
+      <c r="O52" t="s">
+        <v>239</v>
+      </c>
+      <c r="P52" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53">
+        <v>0</v>
+      </c>
+      <c r="B53" t="s">
+        <v>120</v>
+      </c>
+      <c r="C53">
+        <v>0.0002635324989281152</v>
+      </c>
+      <c r="D53">
+        <v>0.0003713382175192237</v>
+      </c>
+      <c r="E53">
+        <v>0.0007462885696440935</v>
+      </c>
+      <c r="F53">
+        <v>0.001295391353778541</v>
+      </c>
+      <c r="G53">
+        <v>0.001224871957674623</v>
+      </c>
+      <c r="H53">
+        <v>0.9999594660461584</v>
+      </c>
+      <c r="I53">
+        <v>0.04935923527852887</v>
+      </c>
+      <c r="J53">
+        <v>0.4975799322128296</v>
+      </c>
+      <c r="K53">
+        <v>2.374590635299683</v>
+      </c>
+      <c r="L53">
+        <v>0.04271483421325684</v>
+      </c>
+      <c r="M53">
+        <v>28.47966003417969</v>
+      </c>
+      <c r="N53" t="s">
+        <v>180</v>
+      </c>
+      <c r="O53" t="s">
+        <v>240</v>
+      </c>
+      <c r="P53" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54">
+        <v>0</v>
+      </c>
+      <c r="B54" t="s">
+        <v>121</v>
+      </c>
+      <c r="C54">
+        <v>0.0003036880569272323</v>
+      </c>
+      <c r="D54">
+        <v>0.0004232871579006314</v>
+      </c>
+      <c r="E54">
+        <v>0.0007876929012127221</v>
+      </c>
+      <c r="F54">
+        <v>0.0014772490831092</v>
+      </c>
+      <c r="G54">
+        <v>0.001363469869829714</v>
+      </c>
+      <c r="H54">
+        <v>1.000218354175298</v>
+      </c>
+      <c r="I54">
+        <v>0.04931420804967379</v>
+      </c>
+      <c r="J54">
+        <v>0.5373758673667908</v>
+      </c>
+      <c r="K54">
+        <v>3.000731945037842</v>
+      </c>
+      <c r="L54">
+        <v>0.04508466646075249</v>
+      </c>
+      <c r="M54">
+        <v>30.75743293762207</v>
+      </c>
+      <c r="N54" t="s">
+        <v>181</v>
+      </c>
+      <c r="O54" t="s">
+        <v>241</v>
+      </c>
+      <c r="P54" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
+      <c r="A55">
+        <v>0</v>
+      </c>
+      <c r="B55" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55">
+        <v>0.0004407729444229309</v>
+      </c>
+      <c r="D55">
+        <v>0.0005958206602372229</v>
+      </c>
+      <c r="E55">
+        <v>0.0009522149921394885</v>
+      </c>
+      <c r="F55">
+        <v>0.002056653844192624</v>
+      </c>
+      <c r="G55">
+        <v>0.001742701628245413</v>
+      </c>
+      <c r="H55">
+        <v>1.000587840621275</v>
+      </c>
+      <c r="I55">
+        <v>0.04923116641662285</v>
+      </c>
+      <c r="J55">
+        <v>0.625720739364624</v>
+      </c>
+      <c r="K55">
+        <v>6.037731170654297</v>
+      </c>
+      <c r="L55">
+        <v>0.05450130999088287</v>
+      </c>
+      <c r="M55">
+        <v>35.81397247314453</v>
+      </c>
+      <c r="N55" t="s">
+        <v>182</v>
+      </c>
+      <c r="O55" t="s">
+        <v>242</v>
+      </c>
+      <c r="P55" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56">
+        <v>0</v>
+      </c>
+      <c r="B56" t="s">
+        <v>122</v>
+      </c>
+      <c r="C56">
+        <v>0.0005898335565144211</v>
+      </c>
+      <c r="D56">
+        <v>0.0007815051940269768</v>
+      </c>
+      <c r="E56">
+        <v>0.0011844492983073</v>
+      </c>
+      <c r="F56">
+        <v>0.002653796458616853</v>
+      </c>
+      <c r="G56">
+        <v>0.002098654164001346</v>
+      </c>
+      <c r="H56">
+        <v>1.000549033197906</v>
+      </c>
+      <c r="I56">
+        <v>0.04964589685687466</v>
+      </c>
+      <c r="J56">
+        <v>0.6598047018051147</v>
+      </c>
+      <c r="K56">
+        <v>11.92692470550537</v>
+      </c>
+      <c r="L56">
+        <v>0.06779355555772781</v>
+      </c>
+      <c r="M56">
+        <v>37.76481246948242</v>
+      </c>
+      <c r="N56" t="s">
+        <v>183</v>
+      </c>
+      <c r="O56" t="s">
+        <v>243</v>
+      </c>
+      <c r="P56" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57">
+        <v>0</v>
+      </c>
+      <c r="B57" t="s">
+        <v>123</v>
+      </c>
+      <c r="C57">
+        <v>0.0007526416321236369</v>
+      </c>
+      <c r="D57">
+        <v>0.0009599236072972417</v>
+      </c>
+      <c r="E57">
+        <v>0.001547640189528465</v>
+      </c>
+      <c r="F57">
+        <v>0.003016050439327955</v>
+      </c>
+      <c r="G57">
+        <v>0.002262854715809226</v>
+      </c>
+      <c r="H57">
+        <v>1.000518678190687</v>
+      </c>
+      <c r="I57">
+        <v>0.04979379350535114</v>
+      </c>
+      <c r="J57">
+        <v>0.62024986743927</v>
+      </c>
+      <c r="K57">
+        <v>22.17412567138672</v>
+      </c>
+      <c r="L57">
+        <v>0.08858127892017365</v>
+      </c>
+      <c r="M57">
+        <v>35.50083923339844</v>
+      </c>
+      <c r="N57" t="s">
+        <v>184</v>
+      </c>
+      <c r="O57" t="s">
+        <v>244</v>
+      </c>
+      <c r="P57" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58">
+        <v>0</v>
+      </c>
+      <c r="B58" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58">
+        <v>0.001004516597493747</v>
+      </c>
+      <c r="D58">
+        <v>0.001153704477474093</v>
+      </c>
+      <c r="E58">
+        <v>0.002389972098171711</v>
+      </c>
+      <c r="F58">
+        <v>0.002957394113764167</v>
+      </c>
+      <c r="G58">
+        <v>0.002314249519258738</v>
+      </c>
+      <c r="H58">
+        <v>1.000041410095958</v>
+      </c>
+      <c r="I58">
+        <v>0.05200615787021406</v>
+      </c>
+      <c r="J58">
+        <v>0.4827271699905396</v>
+      </c>
+      <c r="K58">
+        <v>42.70083618164062</v>
+      </c>
+      <c r="L58">
+        <v>0.1367932856082916</v>
+      </c>
+      <c r="M58">
+        <v>27.62954139709473</v>
+      </c>
+      <c r="N58" t="s">
+        <v>185</v>
+      </c>
+      <c r="O58" t="s">
+        <v>245</v>
+      </c>
+      <c r="P58" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
+      <c r="A59">
+        <v>0</v>
+      </c>
+      <c r="B59" t="s">
+        <v>125</v>
+      </c>
+      <c r="C59">
+        <v>0.001223459745634973</v>
+      </c>
+      <c r="D59">
+        <v>0.001321426127105951</v>
+      </c>
+      <c r="E59">
+        <v>0.003395310835912824</v>
+      </c>
+      <c r="F59">
+        <v>0.002783579286187887</v>
+      </c>
+      <c r="G59">
+        <v>0.002350199967622757</v>
+      </c>
+      <c r="H59">
+        <v>0.9996499173301745</v>
+      </c>
+      <c r="I59">
+        <v>0.05445518745828572</v>
+      </c>
+      <c r="J59">
+        <v>0.3891915082931519</v>
+      </c>
+      <c r="K59">
+        <v>74.65346527099609</v>
+      </c>
+      <c r="L59">
+        <v>0.1943352073431015</v>
+      </c>
+      <c r="M59">
+        <v>22.27590179443359</v>
+      </c>
+      <c r="N59" t="s">
+        <v>186</v>
+      </c>
+      <c r="O59" t="s">
+        <v>246</v>
+      </c>
+      <c r="P59" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60">
+        <v>0</v>
+      </c>
+      <c r="B60" t="s">
+        <v>126</v>
+      </c>
+      <c r="C60">
+        <v>0.00152815682295394</v>
+      </c>
+      <c r="D60">
+        <v>0.001560431555844843</v>
+      </c>
+      <c r="E60">
+        <v>0.005490465555340052</v>
+      </c>
+      <c r="F60">
+        <v>0.002622697735205293</v>
+      </c>
+      <c r="G60">
+        <v>0.00248813908547163</v>
+      </c>
+      <c r="H60">
+        <v>1.000766539322231</v>
+      </c>
+      <c r="I60">
+        <v>0.0585543604956988</v>
+      </c>
+      <c r="J60">
+        <v>0.2842075228691101</v>
+      </c>
+      <c r="K60">
+        <v>164.3473663330078</v>
+      </c>
+      <c r="L60">
+        <v>0.3142542243003845</v>
+      </c>
+      <c r="M60">
+        <v>16.26700210571289</v>
+      </c>
+      <c r="N60" t="s">
+        <v>187</v>
+      </c>
+      <c r="O60" t="s">
+        <v>247</v>
+      </c>
+      <c r="P60" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61">
+        <v>0</v>
+      </c>
+      <c r="B61" t="s">
+        <v>127</v>
+      </c>
+      <c r="C61">
+        <v>0.001754368537981622</v>
+      </c>
+      <c r="D61">
+        <v>0.001777235185727477</v>
+      </c>
+      <c r="E61">
+        <v>0.007449895143508911</v>
+      </c>
+      <c r="F61">
+        <v>0.002559332875534892</v>
+      </c>
+      <c r="G61">
+        <v>0.002614669036120176</v>
+      </c>
+      <c r="H61">
+        <v>1.002172582619339</v>
+      </c>
+      <c r="I61">
+        <v>0.06707358248527952</v>
+      </c>
+      <c r="J61">
+        <v>0.2385584115982056</v>
+      </c>
+      <c r="K61">
+        <v>335.0427551269531</v>
+      </c>
+      <c r="L61">
+        <v>0.4264048039913177</v>
+      </c>
+      <c r="M61">
+        <v>13.65421295166016</v>
+      </c>
+      <c r="N61" t="s">
+        <v>188</v>
+      </c>
+      <c r="O61" t="s">
+        <v>248</v>
+      </c>
+      <c r="P61" t="s">
+        <v>308</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P61"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="B1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2">
+        <v>0.0009754027291191244</v>
+      </c>
+      <c r="D2">
+        <v>-0.003079827409237623</v>
+      </c>
+      <c r="E2">
+        <v>0.05593588575720787</v>
+      </c>
+      <c r="F2">
+        <v>0.0008395474287681282</v>
+      </c>
+      <c r="G2">
+        <v>0.0008764005033299327</v>
+      </c>
+      <c r="H2">
+        <v>1.000581740143232</v>
+      </c>
+      <c r="I2">
+        <v>0.04895064464998444</v>
+      </c>
+      <c r="J2">
+        <v>-0.05505995452404022</v>
+      </c>
+      <c r="K2">
+        <v>-0.9999591112136841</v>
+      </c>
+      <c r="L2">
+        <v>3.201565980911255</v>
+      </c>
+      <c r="M2">
+        <v>-3.15143084526062</v>
+      </c>
+      <c r="N2" t="s">
+        <v>309</v>
+      </c>
+      <c r="O2" t="s">
+        <v>369</v>
+      </c>
+      <c r="P2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3">
+        <v>0.001296741475898118</v>
+      </c>
+      <c r="D3">
+        <v>-0.003521273843944073</v>
+      </c>
+      <c r="E3">
+        <v>0.06986695528030396</v>
+      </c>
+      <c r="F3">
+        <v>0.0009934447007253766</v>
+      </c>
+      <c r="G3">
+        <v>0.0009752001496963203</v>
+      </c>
+      <c r="H3">
+        <v>1.000821939792972</v>
+      </c>
+      <c r="I3">
+        <v>0.04890202846732188</v>
+      </c>
+      <c r="J3">
+        <v>-0.05039970204234123</v>
+      </c>
+      <c r="K3">
+        <v>-0.9999904036521912</v>
+      </c>
+      <c r="L3">
+        <v>3.998929500579834</v>
+      </c>
+      <c r="M3">
+        <v>-2.884695053100586</v>
+      </c>
+      <c r="N3" t="s">
+        <v>310</v>
+      </c>
+      <c r="O3" t="s">
+        <v>370</v>
+      </c>
+      <c r="P3" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4">
+        <v>0.001616349105680836</v>
+      </c>
+      <c r="D4">
+        <v>-0.001259762211702764</v>
+      </c>
+      <c r="E4">
+        <v>0.04128335416316986</v>
+      </c>
+      <c r="F4">
+        <v>0.001124886330217123</v>
+      </c>
+      <c r="G4">
+        <v>0.001115063554607332</v>
+      </c>
+      <c r="H4">
+        <v>1.000945356870535</v>
+      </c>
+      <c r="I4">
+        <v>0.04889201282624914</v>
+      </c>
+      <c r="J4">
+        <v>-0.03051501512527466</v>
+      </c>
+      <c r="K4">
+        <v>-0.9839094281196594</v>
+      </c>
+      <c r="L4">
+        <v>2.362908601760864</v>
+      </c>
+      <c r="M4">
+        <v>-1.746568083763123</v>
+      </c>
+      <c r="N4" t="s">
+        <v>311</v>
+      </c>
+      <c r="O4" t="s">
+        <v>371</v>
+      </c>
+      <c r="P4" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5">
+        <v>0.003188341631001151</v>
+      </c>
+      <c r="D5">
+        <v>-0.006278079934418201</v>
+      </c>
+      <c r="E5">
+        <v>0.2209339886903763</v>
+      </c>
+      <c r="F5">
+        <v>0.001621997100301087</v>
+      </c>
+      <c r="G5">
+        <v>0.001476438599638641</v>
+      </c>
+      <c r="H5">
+        <v>1.001155820948931</v>
+      </c>
+      <c r="I5">
+        <v>0.04892467631012033</v>
+      </c>
+      <c r="J5">
+        <v>-0.02841608971357346</v>
+      </c>
+      <c r="K5">
+        <v>-1</v>
+      </c>
+      <c r="L5">
+        <v>12.6454553604126</v>
+      </c>
+      <c r="M5">
+        <v>-1.626433253288269</v>
+      </c>
+      <c r="N5" t="s">
+        <v>312</v>
+      </c>
+      <c r="O5" t="s">
+        <v>372</v>
+      </c>
+      <c r="P5" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6">
+        <v>0.006257444496286693</v>
+      </c>
+      <c r="D6">
+        <v>0.003256292780861259</v>
+      </c>
+      <c r="E6">
+        <v>0.01845222339034081</v>
+      </c>
+      <c r="F6">
+        <v>0.002185040153563023</v>
+      </c>
+      <c r="G6">
+        <v>0.001816553412936628</v>
+      </c>
+      <c r="H6">
+        <v>1.001145495568775</v>
+      </c>
+      <c r="I6">
+        <v>0.04914777424489154</v>
+      </c>
+      <c r="J6">
+        <v>0.1764715611934662</v>
+      </c>
+      <c r="K6">
+        <v>42207.4765625</v>
+      </c>
+      <c r="L6">
+        <v>1.056137919425964</v>
+      </c>
+      <c r="M6">
+        <v>10.10058784484863</v>
+      </c>
+      <c r="N6" t="s">
+        <v>313</v>
+      </c>
+      <c r="O6" t="s">
+        <v>373</v>
+      </c>
+      <c r="P6" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7">
+        <v>0.01229779621042238</v>
+      </c>
+      <c r="D7">
+        <v>0.00642817746847868</v>
+      </c>
+      <c r="E7">
+        <v>0.03610912710428238</v>
+      </c>
+      <c r="F7">
+        <v>0.002649627858772874</v>
+      </c>
+      <c r="G7">
+        <v>0.002096559619531035</v>
+      </c>
+      <c r="H7">
+        <v>1.00100212391586</v>
+      </c>
+      <c r="I7">
+        <v>0.04929638581854942</v>
+      </c>
+      <c r="J7">
+        <v>0.1780208498239517</v>
+      </c>
+      <c r="K7">
+        <v>1307175680</v>
+      </c>
+      <c r="L7">
+        <v>2.066754579544067</v>
+      </c>
+      <c r="M7">
+        <v>10.18926429748535</v>
+      </c>
+      <c r="N7" t="s">
+        <v>314</v>
+      </c>
+      <c r="O7" t="s">
+        <v>374</v>
+      </c>
+      <c r="P7" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8">
+        <v>0.03013761953285152</v>
+      </c>
+      <c r="D8">
+        <v>0.0154972430318594</v>
+      </c>
+      <c r="E8">
+        <v>0.08841315656900406</v>
+      </c>
+      <c r="F8">
+        <v>0.002909867325797677</v>
+      </c>
+      <c r="G8">
+        <v>0.002160154050216079</v>
+      </c>
+      <c r="H8">
+        <v>1.000737224220895</v>
+      </c>
+      <c r="I8">
+        <v>0.05075143075558838</v>
+      </c>
+      <c r="J8">
+        <v>0.1752820909023285</v>
+      </c>
+      <c r="K8">
+        <v>7.57758953687743E+21</v>
+      </c>
+      <c r="L8">
+        <v>5.060446262359619</v>
+      </c>
+      <c r="M8">
+        <v>10.03250694274902</v>
+      </c>
+      <c r="N8" t="s">
+        <v>315</v>
+      </c>
+      <c r="O8" t="s">
+        <v>375</v>
+      </c>
+      <c r="P8" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9">
+        <v>0.05961056721989336</v>
+      </c>
+      <c r="D9">
+        <v>0.0302891694009304</v>
+      </c>
+      <c r="E9">
+        <v>0.1769014149904251</v>
+      </c>
+      <c r="F9">
+        <v>0.002857697429135442</v>
+      </c>
+      <c r="G9">
+        <v>0.002175471046939492</v>
+      </c>
+      <c r="H9">
+        <v>1.000459525332196</v>
+      </c>
+      <c r="I9">
+        <v>0.0523476116147411</v>
+      </c>
+      <c r="J9">
+        <v>0.1712206155061722</v>
+      </c>
+      <c r="K9" t="s">
+        <v>128</v>
+      </c>
+      <c r="L9">
+        <v>10.1251916885376</v>
+      </c>
+      <c r="M9">
+        <v>9.800043106079102</v>
+      </c>
+      <c r="N9" t="s">
+        <v>316</v>
+      </c>
+      <c r="O9" t="s">
+        <v>376</v>
+      </c>
+      <c r="P9" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10">
+        <v>0.148725111725193</v>
+      </c>
+      <c r="D10">
+        <v>0.07588034123182297</v>
+      </c>
+      <c r="E10">
+        <v>0.4624150991439819</v>
+      </c>
+      <c r="F10">
+        <v>0.002616578945890069</v>
+      </c>
+      <c r="G10">
+        <v>0.002299556974321604</v>
+      </c>
+      <c r="H10">
+        <v>1.001259535378263</v>
+      </c>
+      <c r="I10">
+        <v>0.05748742474759053</v>
+      </c>
+      <c r="J10">
+        <v>0.1640957295894623</v>
+      </c>
+      <c r="K10" t="s">
+        <v>128</v>
+      </c>
+      <c r="L10">
+        <v>26.46695327758789</v>
+      </c>
+      <c r="M10">
+        <v>9.392240524291992</v>
+      </c>
+      <c r="N10" t="s">
+        <v>317</v>
+      </c>
+      <c r="O10" t="s">
+        <v>377</v>
+      </c>
+      <c r="P10" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11">
+        <v>0.2914743859574022</v>
+      </c>
+      <c r="D11">
+        <v>0.1545259952545166</v>
+      </c>
+      <c r="E11">
+        <v>0.9956306219100952</v>
+      </c>
+      <c r="F11">
+        <v>0.002535628154873848</v>
+      </c>
+      <c r="G11">
+        <v>0.0025510776322335</v>
+      </c>
+      <c r="H11">
+        <v>1.002294981640147</v>
+      </c>
+      <c r="I11">
+        <v>0.06679485957697048</v>
+      </c>
+      <c r="J11">
+        <v>0.1552041471004486</v>
+      </c>
+      <c r="K11" t="s">
+        <v>128</v>
+      </c>
+      <c r="L11">
+        <v>56.98626327514648</v>
+      </c>
+      <c r="M11">
+        <v>8.883318901062012</v>
+      </c>
+      <c r="N11" t="s">
+        <v>318</v>
+      </c>
+      <c r="O11" t="s">
+        <v>378</v>
+      </c>
+      <c r="P11" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12">
+        <v>0.001324709454511081</v>
+      </c>
+      <c r="D12">
+        <v>-0.0002553322701714933</v>
+      </c>
+      <c r="E12">
+        <v>0.009229160845279694</v>
+      </c>
+      <c r="F12">
+        <v>0.0008541790302842855</v>
+      </c>
+      <c r="G12">
+        <v>0.0008855424239300191</v>
+      </c>
+      <c r="H12">
+        <v>1.000554774125491</v>
+      </c>
+      <c r="I12">
+        <v>0.04896775892076151</v>
+      </c>
+      <c r="J12">
+        <v>-0.02766581624746323</v>
+      </c>
+      <c r="K12">
+        <v>-0.5668283700942993</v>
+      </c>
+      <c r="L12">
+        <v>0.5282434821128845</v>
+      </c>
+      <c r="M12">
+        <v>-1.583490371704102</v>
+      </c>
+      <c r="N12" t="s">
+        <v>319</v>
+      </c>
+      <c r="O12" t="s">
+        <v>379</v>
+      </c>
+      <c r="P12" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13">
+        <v>0.001761803731060153</v>
+      </c>
+      <c r="D13">
+        <v>0.0002550951321609318</v>
+      </c>
+      <c r="E13">
+        <v>0.01100417040288448</v>
+      </c>
+      <c r="F13">
+        <v>0.00102453154977411</v>
+      </c>
+      <c r="G13">
+        <v>0.0009977519512176514</v>
+      </c>
+      <c r="H13">
+        <v>1.000778337435698</v>
+      </c>
+      <c r="I13">
+        <v>0.04892597003808475</v>
+      </c>
+      <c r="J13">
+        <v>0.02318167686462402</v>
+      </c>
+      <c r="K13">
+        <v>1.306259155273438</v>
+      </c>
+      <c r="L13">
+        <v>0.6298385858535767</v>
+      </c>
+      <c r="M13">
+        <v>1.326834559440613</v>
+      </c>
+      <c r="N13" t="s">
+        <v>320</v>
+      </c>
+      <c r="O13" t="s">
+        <v>380</v>
+      </c>
+      <c r="P13" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14">
+        <v>0.002196568364834902</v>
+      </c>
+      <c r="D14">
+        <v>0.0008425365667790174</v>
+      </c>
+      <c r="E14">
+        <v>0.01262593828141689</v>
+      </c>
+      <c r="F14">
+        <v>0.001164923654869199</v>
+      </c>
+      <c r="G14">
+        <v>0.001144525711424649</v>
+      </c>
+      <c r="H14">
+        <v>1.000882422604427</v>
+      </c>
+      <c r="I14">
+        <v>0.048925629728056</v>
+      </c>
+      <c r="J14">
+        <v>0.06673061102628708</v>
+      </c>
+      <c r="K14">
+        <v>14.78564929962158</v>
+      </c>
+      <c r="L14">
+        <v>0.722662627696991</v>
+      </c>
+      <c r="M14">
+        <v>3.819416761398315</v>
+      </c>
+      <c r="N14" t="s">
+        <v>321</v>
+      </c>
+      <c r="O14" t="s">
+        <v>381</v>
+      </c>
+      <c r="P14" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15">
+        <v>0.004343836515063781</v>
+      </c>
+      <c r="D15">
+        <v>0.002892118180170655</v>
+      </c>
+      <c r="E15">
+        <v>0.03532479703426361</v>
+      </c>
+      <c r="F15">
+        <v>0.001669206307269633</v>
+      </c>
+      <c r="G15">
+        <v>0.00149723154027015</v>
+      </c>
+      <c r="H15">
+        <v>1.001089027687838</v>
+      </c>
+      <c r="I15">
+        <v>0.04894746659199145</v>
+      </c>
+      <c r="J15">
+        <v>0.08187218010425568</v>
+      </c>
+      <c r="K15">
+        <v>12847.2744140625</v>
+      </c>
+      <c r="L15">
+        <v>2.021862506866455</v>
+      </c>
+      <c r="M15">
+        <v>4.686064720153809</v>
+      </c>
+      <c r="N15" t="s">
+        <v>322</v>
+      </c>
+      <c r="O15" t="s">
+        <v>382</v>
+      </c>
+      <c r="P15" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16">
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16">
+        <v>0.008556170781302387</v>
+      </c>
+      <c r="D16">
+        <v>0.005131002049893141</v>
+      </c>
+      <c r="E16">
+        <v>0.04707466438412666</v>
+      </c>
+      <c r="F16">
+        <v>0.002247394761070609</v>
+      </c>
+      <c r="G16">
+        <v>0.001849945518188179</v>
+      </c>
+      <c r="H16">
+        <v>1.001113336674918</v>
+      </c>
+      <c r="I16">
+        <v>0.04917138463373212</v>
+      </c>
+      <c r="J16">
+        <v>0.108997106552124</v>
+      </c>
+      <c r="K16">
+        <v>19119120</v>
+      </c>
+      <c r="L16">
+        <v>2.694381952285767</v>
+      </c>
+      <c r="M16">
+        <v>6.238596439361572</v>
+      </c>
+      <c r="N16" t="s">
+        <v>323</v>
+      </c>
+      <c r="O16" t="s">
+        <v>383</v>
+      </c>
+      <c r="P16" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17">
+        <v>0.01684840522311541</v>
+      </c>
+      <c r="D17">
+        <v>0.009552071802318096</v>
+      </c>
+      <c r="E17">
+        <v>0.07523566484451294</v>
+      </c>
+      <c r="F17">
+        <v>0.002712841611355543</v>
+      </c>
+      <c r="G17">
+        <v>0.002132146852090955</v>
+      </c>
+      <c r="H17">
+        <v>1.000970911981184</v>
+      </c>
+      <c r="I17">
+        <v>0.04926800453537673</v>
+      </c>
+      <c r="J17">
+        <v>0.1269620209932327</v>
+      </c>
+      <c r="K17">
+        <v>33556034224128</v>
+      </c>
+      <c r="L17">
+        <v>4.306214809417725</v>
+      </c>
+      <c r="M17">
+        <v>7.266842842102051</v>
+      </c>
+      <c r="N17" t="s">
+        <v>324</v>
+      </c>
+      <c r="O17" t="s">
+        <v>384</v>
+      </c>
+      <c r="P17" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18">
+        <v>0.04151007031276818</v>
+      </c>
+      <c r="D18">
+        <v>0.02208577282726765</v>
+      </c>
+      <c r="E18">
+        <v>0.1661862432956696</v>
+      </c>
+      <c r="F18">
+        <v>0.002950375434011221</v>
+      </c>
+      <c r="G18">
+        <v>0.002172599313780665</v>
+      </c>
+      <c r="H18">
+        <v>1.000762905192541</v>
+      </c>
+      <c r="I18">
+        <v>0.05070113268118612</v>
+      </c>
+      <c r="J18">
+        <v>0.1328977197408676</v>
+      </c>
+      <c r="K18">
+        <v>1.203799127891389E+31</v>
+      </c>
+      <c r="L18">
+        <v>9.511894226074219</v>
+      </c>
+      <c r="M18">
+        <v>7.60658073425293</v>
+      </c>
+      <c r="N18" t="s">
+        <v>325</v>
+      </c>
+      <c r="O18" t="s">
+        <v>385</v>
+      </c>
+      <c r="P18" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="B19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19">
+        <v>0.08183262190577446</v>
+      </c>
+      <c r="D19">
+        <v>0.04384502023458481</v>
+      </c>
+      <c r="E19">
+        <v>0.3452177345752716</v>
+      </c>
+      <c r="F19">
+        <v>0.002869262592867017</v>
+      </c>
+      <c r="G19">
+        <v>0.00219794362783432</v>
+      </c>
+      <c r="H19">
+        <v>1.000521242229765</v>
+      </c>
+      <c r="I19">
+        <v>0.05230503043770476</v>
+      </c>
+      <c r="J19">
+        <v>0.127006858587265</v>
+      </c>
+      <c r="K19" t="s">
+        <v>128</v>
+      </c>
+      <c r="L19">
+        <v>19.75900268554688</v>
+      </c>
+      <c r="M19">
+        <v>7.2694091796875</v>
+      </c>
+      <c r="N19" t="s">
+        <v>326</v>
+      </c>
+      <c r="O19" t="s">
+        <v>386</v>
+      </c>
+      <c r="P19" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20">
+        <v>0</v>
+      </c>
+      <c r="B20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20">
+        <v>0.2043583782010431</v>
+      </c>
+      <c r="D20">
+        <v>0.1023243740200996</v>
+      </c>
+      <c r="E20">
+        <v>0.7318083047866821</v>
+      </c>
+      <c r="F20">
+        <v>0.00262188189662993</v>
+      </c>
+      <c r="G20">
+        <v>0.002314310288056731</v>
+      </c>
+      <c r="H20">
+        <v>1.001191535922258</v>
+      </c>
+      <c r="I20">
+        <v>0.05758748137680988</v>
+      </c>
+      <c r="J20">
+        <v>0.1398240178823471</v>
+      </c>
+      <c r="K20" t="s">
+        <v>128</v>
+      </c>
+      <c r="L20">
+        <v>41.88603591918945</v>
+      </c>
+      <c r="M20">
+        <v>8.003016471862793</v>
+      </c>
+      <c r="N20" t="s">
+        <v>327</v>
+      </c>
+      <c r="O20" t="s">
+        <v>387</v>
+      </c>
+      <c r="P20" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21">
+        <v>0</v>
+      </c>
+      <c r="B21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21">
+        <v>0.4035142808512813</v>
+      </c>
+      <c r="D21">
+        <v>0.2029733806848526</v>
+      </c>
+      <c r="E21">
+        <v>1.399285793304443</v>
+      </c>
+      <c r="F21">
+        <v>0.002552420599386096</v>
+      </c>
+      <c r="G21">
+        <v>0.002584820846095681</v>
+      </c>
+      <c r="H21">
+        <v>1.002294981640147</v>
+      </c>
+      <c r="I21">
+        <v>0.06679485957697048</v>
+      </c>
+      <c r="J21">
+        <v>0.1450549811124802</v>
+      </c>
+      <c r="K21" t="s">
+        <v>128</v>
+      </c>
+      <c r="L21">
+        <v>80.09001159667969</v>
+      </c>
+      <c r="M21">
+        <v>8.302417755126953</v>
+      </c>
+      <c r="N21" t="s">
+        <v>328</v>
+      </c>
+      <c r="O21" t="s">
+        <v>388</v>
+      </c>
+      <c r="P21" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22">
+        <v>0.0006494287259465072</v>
+      </c>
+      <c r="D22">
+        <v>-0.0003011580556631088</v>
+      </c>
+      <c r="E22">
+        <v>0.002972299931570888</v>
+      </c>
+      <c r="F22">
+        <v>0.0008824081742204726</v>
+      </c>
+      <c r="G22">
+        <v>0.000889778311830014</v>
+      </c>
+      <c r="H22">
+        <v>1.000485644848131</v>
+      </c>
+      <c r="I22">
+        <v>0.04894858907867339</v>
+      </c>
+      <c r="J22">
+        <v>-0.1013215556740761</v>
+      </c>
+      <c r="K22">
+        <v>-0.6272404193878174</v>
+      </c>
+      <c r="L22">
+        <v>0.1701236069202423</v>
+      </c>
+      <c r="M22">
+        <v>-5.799276351928711</v>
+      </c>
+      <c r="N22" t="s">
+        <v>329</v>
+      </c>
+      <c r="O22" t="s">
+        <v>389</v>
+      </c>
+      <c r="P22" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23">
+        <v>0.0008604610003403946</v>
+      </c>
+      <c r="D23">
+        <v>4.297509349271422E-06</v>
+      </c>
+      <c r="E23">
+        <v>0.003779418300837278</v>
+      </c>
+      <c r="F23">
+        <v>0.001061610062606633</v>
+      </c>
+      <c r="G23">
+        <v>0.001038296730257571</v>
+      </c>
+      <c r="H23">
+        <v>1.00072958920826</v>
+      </c>
+      <c r="I23">
+        <v>0.04889521541436054</v>
+      </c>
+      <c r="J23">
+        <v>0.001137082232162356</v>
+      </c>
+      <c r="K23">
+        <v>0.01415836811065674</v>
+      </c>
+      <c r="L23">
+        <v>0.2163201123476028</v>
+      </c>
+      <c r="M23">
+        <v>0.06508243829011917</v>
+      </c>
+      <c r="N23" t="s">
+        <v>330</v>
+      </c>
+      <c r="O23" t="s">
+        <v>390</v>
+      </c>
+      <c r="P23" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24">
+        <v>0</v>
+      </c>
+      <c r="B24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24">
+        <v>0.001068697581208768</v>
+      </c>
+      <c r="D24">
+        <v>0.0002300039341207594</v>
+      </c>
+      <c r="E24">
+        <v>0.004655797965824604</v>
+      </c>
+      <c r="F24">
+        <v>0.001212559873238206</v>
+      </c>
+      <c r="G24">
+        <v>0.00117278890684247</v>
+      </c>
+      <c r="H24">
+        <v>1.000834953226637</v>
+      </c>
+      <c r="I24">
+        <v>0.04889772626940114</v>
+      </c>
+      <c r="J24">
+        <v>0.04940161481499672</v>
+      </c>
+      <c r="K24">
+        <v>1.123880863189697</v>
+      </c>
+      <c r="L24">
+        <v>0.2664808928966522</v>
+      </c>
+      <c r="M24">
+        <v>2.827568054199219</v>
+      </c>
+      <c r="N24" t="s">
+        <v>331</v>
+      </c>
+      <c r="O24" t="s">
+        <v>391</v>
+      </c>
+      <c r="P24" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25">
+        <v>0</v>
+      </c>
+      <c r="B25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25">
+        <v>0.002077173245425244</v>
+      </c>
+      <c r="D25">
+        <v>0.001061607734300196</v>
+      </c>
+      <c r="E25">
+        <v>0.009028784930706024</v>
+      </c>
+      <c r="F25">
+        <v>0.001751040806993842</v>
+      </c>
+      <c r="G25">
+        <v>0.001534610171802342</v>
+      </c>
+      <c r="H25">
+        <v>1.001028800000556</v>
+      </c>
+      <c r="I25">
+        <v>0.04897098206220236</v>
+      </c>
+      <c r="J25">
+        <v>0.1175803542137146</v>
+      </c>
+      <c r="K25">
+        <v>31.32438278198242</v>
+      </c>
+      <c r="L25">
+        <v>0.5167747139930725</v>
+      </c>
+      <c r="M25">
+        <v>6.729870319366455</v>
+      </c>
+      <c r="N25" t="s">
+        <v>332</v>
+      </c>
+      <c r="O25" t="s">
+        <v>392</v>
+      </c>
+      <c r="P25" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26">
+        <v>0</v>
+      </c>
+      <c r="B26" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26">
+        <v>0.004008847266312376</v>
+      </c>
+      <c r="D26">
+        <v>0.002216943074017763</v>
+      </c>
+      <c r="E26">
+        <v>0.01736822538077831</v>
+      </c>
+      <c r="F26">
+        <v>0.002317839069291949</v>
+      </c>
+      <c r="G26">
+        <v>0.001885279547423124</v>
+      </c>
+      <c r="H26">
+        <v>1.001049845109873</v>
+      </c>
+      <c r="I26">
+        <v>0.04918579060228363</v>
+      </c>
+      <c r="J26">
+        <v>0.1276436150074005</v>
+      </c>
+      <c r="K26">
+        <v>1413.655029296875</v>
+      </c>
+      <c r="L26">
+        <v>0.9940938353538513</v>
+      </c>
+      <c r="M26">
+        <v>7.305854797363281</v>
+      </c>
+      <c r="N26" t="s">
+        <v>333</v>
+      </c>
+      <c r="O26" t="s">
+        <v>393</v>
+      </c>
+      <c r="P26" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27">
+        <v>0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27">
+        <v>0.007759251997854669</v>
+      </c>
+      <c r="D27">
+        <v>0.004405634943395853</v>
+      </c>
+      <c r="E27">
+        <v>0.03315935656428337</v>
+      </c>
+      <c r="F27">
+        <v>0.002789834281429648</v>
+      </c>
+      <c r="G27">
+        <v>0.00215567834675312</v>
+      </c>
+      <c r="H27">
+        <v>1.000918201000241</v>
+      </c>
+      <c r="I27">
+        <v>0.04924612055190135</v>
+      </c>
+      <c r="J27">
+        <v>0.1328624933958054</v>
+      </c>
+      <c r="K27">
+        <v>1796055.5</v>
+      </c>
+      <c r="L27">
+        <v>1.897920608520508</v>
+      </c>
+      <c r="M27">
+        <v>7.604564189910889</v>
+      </c>
+      <c r="N27" t="s">
+        <v>334</v>
+      </c>
+      <c r="O27" t="s">
+        <v>394</v>
+      </c>
+      <c r="P27" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="B28" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28">
+        <v>0.01874682719140683</v>
+      </c>
+      <c r="D28">
+        <v>0.01007543131709099</v>
+      </c>
+      <c r="E28">
+        <v>0.0783660039305687</v>
+      </c>
+      <c r="F28">
+        <v>0.002986139617860317</v>
+      </c>
+      <c r="G28">
+        <v>0.00218434352427721</v>
+      </c>
+      <c r="H28">
+        <v>1.000807322523818</v>
+      </c>
+      <c r="I28">
+        <v>0.05071419831136231</v>
+      </c>
+      <c r="J28">
+        <v>0.1285689026117325</v>
+      </c>
+      <c r="K28">
+        <v>183273653272576</v>
+      </c>
+      <c r="L28">
+        <v>4.485383987426758</v>
+      </c>
+      <c r="M28">
+        <v>7.358814716339111</v>
+      </c>
+      <c r="N28" t="s">
+        <v>335</v>
+      </c>
+      <c r="O28" t="s">
+        <v>395</v>
+      </c>
+      <c r="P28" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29">
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29">
+        <v>0.03710942779072943</v>
+      </c>
+      <c r="D29">
+        <v>0.01965745724737644</v>
+      </c>
+      <c r="E29">
+        <v>0.1605760306119919</v>
+      </c>
+      <c r="F29">
+        <v>0.002866968279704452</v>
+      </c>
+      <c r="G29">
+        <v>0.002208099467679858</v>
+      </c>
+      <c r="H29">
+        <v>1.000571893377351</v>
+      </c>
+      <c r="I29">
+        <v>0.05214385013165069</v>
+      </c>
+      <c r="J29">
+        <v>0.1224183812737465</v>
+      </c>
+      <c r="K29">
+        <v>4.969760637582599E+27</v>
+      </c>
+      <c r="L29">
+        <v>9.190786361694336</v>
+      </c>
+      <c r="M29">
+        <v>7.006781578063965</v>
+      </c>
+      <c r="N29" t="s">
+        <v>336</v>
+      </c>
+      <c r="O29" t="s">
+        <v>396</v>
+      </c>
+      <c r="P29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30">
+        <v>0.09062110527805738</v>
+      </c>
+      <c r="D30">
+        <v>0.04823774099349976</v>
+      </c>
+      <c r="E30">
+        <v>0.4104974567890167</v>
+      </c>
+      <c r="F30">
+        <v>0.002644329331815243</v>
+      </c>
+      <c r="G30">
+        <v>0.002347814152017236</v>
+      </c>
+      <c r="H30">
+        <v>1.001327534834267</v>
+      </c>
+      <c r="I30">
+        <v>0.05745298505740964</v>
+      </c>
+      <c r="J30">
+        <v>0.1175104528665543</v>
+      </c>
+      <c r="K30" t="s">
+        <v>128</v>
+      </c>
+      <c r="L30">
+        <v>23.49537658691406</v>
+      </c>
+      <c r="M30">
+        <v>6.725869655609131</v>
+      </c>
+      <c r="N30" t="s">
+        <v>337</v>
+      </c>
+      <c r="O30" t="s">
+        <v>397</v>
+      </c>
+      <c r="P30" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31">
+        <v>0</v>
+      </c>
+      <c r="B31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31">
+        <v>0.1838369863684084</v>
+      </c>
+      <c r="D31">
+        <v>0.09965718537569046</v>
+      </c>
+      <c r="E31">
+        <v>0.9462221264839172</v>
+      </c>
+      <c r="F31">
+        <v>0.002569854725152254</v>
+      </c>
+      <c r="G31">
+        <v>0.002622339874505997</v>
+      </c>
+      <c r="H31">
+        <v>1.002417380660955</v>
+      </c>
+      <c r="I31">
+        <v>0.06651474321265036</v>
+      </c>
+      <c r="J31">
+        <v>0.1053211316466331</v>
+      </c>
+      <c r="K31" t="s">
+        <v>128</v>
+      </c>
+      <c r="L31">
+        <v>54.15830230712891</v>
+      </c>
+      <c r="M31">
+        <v>6.028197288513184</v>
+      </c>
+      <c r="N31" t="s">
+        <v>338</v>
+      </c>
+      <c r="O31" t="s">
+        <v>398</v>
+      </c>
+      <c r="P31" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32">
+        <v>0</v>
+      </c>
+      <c r="B32" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32">
+        <v>0.0005043044277630344</v>
+      </c>
+      <c r="D32">
+        <v>-6.447567284340039E-05</v>
+      </c>
+      <c r="E32">
+        <v>0.003247791668400168</v>
+      </c>
+      <c r="F32">
+        <v>0.0009305114508606493</v>
+      </c>
+      <c r="G32">
+        <v>0.0009172953432425857</v>
+      </c>
+      <c r="H32">
+        <v>1.000412757184527</v>
+      </c>
+      <c r="I32">
+        <v>0.04901094655067183</v>
+      </c>
+      <c r="J32">
+        <v>-0.0198521576821804</v>
+      </c>
+      <c r="K32">
+        <v>-0.1904553174972534</v>
+      </c>
+      <c r="L32">
+        <v>0.1858917474746704</v>
+      </c>
+      <c r="M32">
+        <v>-1.13626503944397</v>
+      </c>
+      <c r="N32" t="s">
+        <v>339</v>
+      </c>
+      <c r="O32" t="s">
+        <v>399</v>
+      </c>
+      <c r="P32" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33">
+        <v>0</v>
+      </c>
+      <c r="B33" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33">
+        <v>0.0006651304193507917</v>
+      </c>
+      <c r="D33">
+        <v>0.000161847667186521</v>
+      </c>
+      <c r="E33">
+        <v>0.00421258294954896</v>
+      </c>
+      <c r="F33">
+        <v>0.001117726438678801</v>
+      </c>
+      <c r="G33">
+        <v>0.001077191205695271</v>
+      </c>
+      <c r="H33">
+        <v>1.000634918492357</v>
+      </c>
+      <c r="I33">
+        <v>0.04896675355202861</v>
+      </c>
+      <c r="J33">
+        <v>0.03842005506157875</v>
+      </c>
+      <c r="K33">
+        <v>0.699435830116272</v>
+      </c>
+      <c r="L33">
+        <v>0.2411128729581833</v>
+      </c>
+      <c r="M33">
+        <v>2.199023723602295</v>
+      </c>
+      <c r="N33" t="s">
+        <v>340</v>
+      </c>
+      <c r="O33" t="s">
+        <v>400</v>
+      </c>
+      <c r="P33" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C34">
+        <v>0.0008223794167008398</v>
+      </c>
+      <c r="D34">
+        <v>0.0003553724964149296</v>
+      </c>
+      <c r="E34">
+        <v>0.005197225138545036</v>
+      </c>
+      <c r="F34">
+        <v>0.001270228647626936</v>
+      </c>
+      <c r="G34">
+        <v>0.001207950874231756</v>
+      </c>
+      <c r="H34">
+        <v>1.000739149256932</v>
+      </c>
+      <c r="I34">
+        <v>0.04897725339707514</v>
+      </c>
+      <c r="J34">
+        <v>0.06837735325098038</v>
+      </c>
+      <c r="K34">
+        <v>2.20259690284729</v>
+      </c>
+      <c r="L34">
+        <v>0.2974702119827271</v>
+      </c>
+      <c r="M34">
+        <v>3.913670301437378</v>
+      </c>
+      <c r="N34" t="s">
+        <v>341</v>
+      </c>
+      <c r="O34" t="s">
+        <v>401</v>
+      </c>
+      <c r="P34" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35">
+        <v>0</v>
+      </c>
+      <c r="B35" t="s">
+        <v>102</v>
+      </c>
+      <c r="C35">
+        <v>0.001571886188429426</v>
+      </c>
+      <c r="D35">
+        <v>0.001032209489494562</v>
+      </c>
+      <c r="E35">
+        <v>0.01019977498799562</v>
+      </c>
+      <c r="F35">
+        <v>0.001823756378144026</v>
+      </c>
+      <c r="G35">
+        <v>0.001582861528731883</v>
+      </c>
+      <c r="H35">
+        <v>1.000950241031598</v>
+      </c>
+      <c r="I35">
+        <v>0.04900376496632266</v>
+      </c>
+      <c r="J35">
+        <v>0.1011992394924164</v>
+      </c>
+      <c r="K35">
+        <v>28.36642456054688</v>
+      </c>
+      <c r="L35">
+        <v>0.5837978720664978</v>
+      </c>
+      <c r="M35">
+        <v>5.792275428771973</v>
+      </c>
+      <c r="N35" t="s">
+        <v>342</v>
+      </c>
+      <c r="O35" t="s">
+        <v>402</v>
+      </c>
+      <c r="P35" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="B36" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36">
+        <v>0.002979620182033035</v>
+      </c>
+      <c r="D36">
+        <v>0.002084617735818028</v>
+      </c>
+      <c r="E36">
+        <v>0.01983163319528103</v>
+      </c>
+      <c r="F36">
+        <v>0.002403915394097567</v>
+      </c>
+      <c r="G36">
+        <v>0.001940970309078693</v>
+      </c>
+      <c r="H36">
+        <v>1.000966028533528</v>
+      </c>
+      <c r="I36">
+        <v>0.04922357166875092</v>
+      </c>
+      <c r="J36">
+        <v>0.1051157861948013</v>
+      </c>
+      <c r="K36">
+        <v>916.8953857421875</v>
+      </c>
+      <c r="L36">
+        <v>1.135090351104736</v>
+      </c>
+      <c r="M36">
+        <v>6.016444206237793</v>
+      </c>
+      <c r="N36" t="s">
+        <v>343</v>
+      </c>
+      <c r="O36" t="s">
+        <v>403</v>
+      </c>
+      <c r="P36" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37">
+        <v>0</v>
+      </c>
+      <c r="B37" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37">
+        <v>0.005667132465349877</v>
+      </c>
+      <c r="D37">
+        <v>0.003796308068558574</v>
+      </c>
+      <c r="E37">
+        <v>0.03928614780306816</v>
+      </c>
+      <c r="F37">
+        <v>0.002869994146749377</v>
+      </c>
+      <c r="G37">
+        <v>0.002187849022448063</v>
+      </c>
+      <c r="H37">
+        <v>1.000836126647707</v>
+      </c>
+      <c r="I37">
+        <v>0.04933401159560953</v>
+      </c>
+      <c r="J37">
+        <v>0.0966322273015976</v>
+      </c>
+      <c r="K37">
+        <v>246041.390625</v>
+      </c>
+      <c r="L37">
+        <v>2.248595714569092</v>
+      </c>
+      <c r="M37">
+        <v>5.530876159667969</v>
+      </c>
+      <c r="N37" t="s">
+        <v>344</v>
+      </c>
+      <c r="O37" t="s">
+        <v>404</v>
+      </c>
+      <c r="P37" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38">
+        <v>0</v>
+      </c>
+      <c r="B38" t="s">
+        <v>105</v>
+      </c>
+      <c r="C38">
+        <v>0.01349756433169082</v>
+      </c>
+      <c r="D38">
+        <v>0.008040765300393105</v>
+      </c>
+      <c r="E38">
+        <v>0.08299913257360458</v>
+      </c>
+      <c r="F38">
+        <v>0.003023689612746239</v>
+      </c>
+      <c r="G38">
+        <v>0.002209417289122939</v>
+      </c>
+      <c r="H38">
+        <v>1.00074964965239</v>
+      </c>
+      <c r="I38">
+        <v>0.05073738171027949</v>
+      </c>
+      <c r="J38">
+        <v>0.09687770158052444</v>
+      </c>
+      <c r="K38">
+        <v>247895949312</v>
+      </c>
+      <c r="L38">
+        <v>4.750567436218262</v>
+      </c>
+      <c r="M38">
+        <v>5.544926166534424</v>
+      </c>
+      <c r="N38" t="s">
+        <v>345</v>
+      </c>
+      <c r="O38" t="s">
+        <v>405</v>
+      </c>
+      <c r="P38" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39">
+        <v>0.0263449288344934</v>
+      </c>
+      <c r="D39">
+        <v>0.01528610941022635</v>
+      </c>
+      <c r="E39">
+        <v>0.1640636175870895</v>
+      </c>
+      <c r="F39">
+        <v>0.002877618884667754</v>
+      </c>
+      <c r="G39">
+        <v>0.002229833044111729</v>
+      </c>
+      <c r="H39">
+        <v>1.000545284894566</v>
+      </c>
+      <c r="I39">
+        <v>0.05217189511782164</v>
+      </c>
+      <c r="J39">
+        <v>0.09317184239625931</v>
+      </c>
+      <c r="K39">
+        <v>3.834546274103219E+21</v>
+      </c>
+      <c r="L39">
+        <v>9.390402793884277</v>
+      </c>
+      <c r="M39">
+        <v>5.332816123962402</v>
+      </c>
+      <c r="N39" t="s">
+        <v>346</v>
+      </c>
+      <c r="O39" t="s">
+        <v>406</v>
+      </c>
+      <c r="P39" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40">
+        <v>0</v>
+      </c>
+      <c r="B40" t="s">
+        <v>107</v>
+      </c>
+      <c r="C40">
+        <v>0.06362595677780358</v>
+      </c>
+      <c r="D40">
+        <v>0.03768165782094002</v>
+      </c>
+      <c r="E40">
+        <v>0.4232111573219299</v>
+      </c>
+      <c r="F40">
+        <v>0.002671352587640285</v>
+      </c>
+      <c r="G40">
+        <v>0.002430576365441084</v>
+      </c>
+      <c r="H40">
+        <v>1.001266335323863</v>
+      </c>
+      <c r="I40">
+        <v>0.05742769980278833</v>
+      </c>
+      <c r="J40">
+        <v>0.08903748542070389</v>
+      </c>
+      <c r="K40" t="s">
+        <v>128</v>
+      </c>
+      <c r="L40">
+        <v>24.22306251525879</v>
+      </c>
+      <c r="M40">
+        <v>5.09618091583252</v>
+      </c>
+      <c r="N40" t="s">
+        <v>347</v>
+      </c>
+      <c r="O40" t="s">
+        <v>407</v>
+      </c>
+      <c r="P40" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41">
+        <v>0</v>
+      </c>
+      <c r="B41" t="s">
+        <v>108</v>
+      </c>
+      <c r="C41">
+        <v>0.1306553315760989</v>
+      </c>
+      <c r="D41">
+        <v>0.07689297199249268</v>
+      </c>
+      <c r="E41">
+        <v>0.9068531394004822</v>
+      </c>
+      <c r="F41">
+        <v>0.002583107445389032</v>
+      </c>
+      <c r="G41">
+        <v>0.002633759053424001</v>
+      </c>
+      <c r="H41">
+        <v>1.002417380660955</v>
+      </c>
+      <c r="I41">
+        <v>0.06651474321265036</v>
+      </c>
+      <c r="J41">
+        <v>0.08479098975658417</v>
+      </c>
+      <c r="K41" t="s">
+        <v>128</v>
+      </c>
+      <c r="L41">
+        <v>51.90496444702148</v>
+      </c>
+      <c r="M41">
+        <v>4.853127002716064</v>
+      </c>
+      <c r="N41" t="s">
+        <v>348</v>
+      </c>
+      <c r="O41" t="s">
+        <v>408</v>
+      </c>
+      <c r="P41" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42">
+        <v>0</v>
+      </c>
+      <c r="B42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C42">
+        <v>0.0005473018329486819</v>
+      </c>
+      <c r="D42">
+        <v>-0.0001053285086527467</v>
+      </c>
+      <c r="E42">
+        <v>0.003214832628145814</v>
+      </c>
+      <c r="F42">
+        <v>0.0009865307947620749</v>
+      </c>
+      <c r="G42">
+        <v>0.0009770386386662722</v>
+      </c>
+      <c r="H42">
+        <v>1.000272686250441</v>
+      </c>
+      <c r="I42">
+        <v>0.04913370000545161</v>
+      </c>
+      <c r="J42">
+        <v>-0.0327632948756218</v>
+      </c>
+      <c r="K42">
+        <v>-0.2918158173561096</v>
+      </c>
+      <c r="L42">
+        <v>0.1840052902698517</v>
+      </c>
+      <c r="M42">
+        <v>-1.875251412391663</v>
+      </c>
+      <c r="N42" t="s">
+        <v>349</v>
+      </c>
+      <c r="O42" t="s">
+        <v>409</v>
+      </c>
+      <c r="P42" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43">
+        <v>0</v>
+      </c>
+      <c r="B43" t="s">
+        <v>110</v>
+      </c>
+      <c r="C43">
+        <v>0.0007193255016852831</v>
+      </c>
+      <c r="D43">
+        <v>-6.090912575018592E-05</v>
+      </c>
+      <c r="E43">
+        <v>0.004143568687140942</v>
+      </c>
+      <c r="F43">
+        <v>0.001187324174679816</v>
+      </c>
+      <c r="G43">
+        <v>0.001147962990216911</v>
+      </c>
+      <c r="H43">
+        <v>1.000442328204659</v>
+      </c>
+      <c r="I43">
+        <v>0.04906486306505311</v>
+      </c>
+      <c r="J43">
+        <v>-0.01469967793673277</v>
+      </c>
+      <c r="K43">
+        <v>-0.1809144020080566</v>
+      </c>
+      <c r="L43">
+        <v>0.2371627539396286</v>
+      </c>
+      <c r="M43">
+        <v>-0.8413559198379517</v>
+      </c>
+      <c r="N43" t="s">
+        <v>350</v>
+      </c>
+      <c r="O43" t="s">
+        <v>410</v>
+      </c>
+      <c r="P43" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44">
+        <v>0</v>
+      </c>
+      <c r="B44" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44">
+        <v>0.0008866892436689367</v>
+      </c>
+      <c r="D44">
+        <v>-1.884298944787588E-05</v>
+      </c>
+      <c r="E44">
+        <v>0.005190654192119837</v>
+      </c>
+      <c r="F44">
+        <v>0.001366126467473805</v>
+      </c>
+      <c r="G44">
+        <v>0.00129055546130985</v>
+      </c>
+      <c r="H44">
+        <v>1.000571420403856</v>
+      </c>
+      <c r="I44">
+        <v>0.04905375990286966</v>
+      </c>
+      <c r="J44">
+        <v>-0.003630176186561584</v>
+      </c>
+      <c r="K44">
+        <v>-0.05983912944793701</v>
+      </c>
+      <c r="L44">
+        <v>0.2970941066741943</v>
+      </c>
+      <c r="M44">
+        <v>-0.2077780365943909</v>
+      </c>
+      <c r="N44" t="s">
+        <v>351</v>
+      </c>
+      <c r="O44" t="s">
+        <v>411</v>
+      </c>
+      <c r="P44" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45">
+        <v>0</v>
+      </c>
+      <c r="B45" t="s">
+        <v>112</v>
+      </c>
+      <c r="C45">
+        <v>0.001677265660507488</v>
+      </c>
+      <c r="D45">
+        <v>0.0001804927596822381</v>
+      </c>
+      <c r="E45">
+        <v>0.009319880977272987</v>
+      </c>
+      <c r="F45">
+        <v>0.001929214457049966</v>
+      </c>
+      <c r="G45">
+        <v>0.001649863319471478</v>
+      </c>
+      <c r="H45">
+        <v>1.000821621405115</v>
+      </c>
+      <c r="I45">
+        <v>0.04912113564418373</v>
+      </c>
+      <c r="J45">
+        <v>0.0193664226680994</v>
+      </c>
+      <c r="K45">
+        <v>0.806169867515564</v>
+      </c>
+      <c r="L45">
+        <v>0.5334360003471375</v>
+      </c>
+      <c r="M45">
+        <v>1.108463406562805</v>
+      </c>
+      <c r="N45" t="s">
+        <v>352</v>
+      </c>
+      <c r="O45" t="s">
+        <v>412</v>
+      </c>
+      <c r="P45" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46">
+        <v>0</v>
+      </c>
+      <c r="B46" t="s">
+        <v>113</v>
+      </c>
+      <c r="C46">
+        <v>0.003155090260510145</v>
+      </c>
+      <c r="D46">
+        <v>0.0001800478348741308</v>
+      </c>
+      <c r="E46">
+        <v>0.01752584986388683</v>
+      </c>
+      <c r="F46">
+        <v>0.002524491865187883</v>
+      </c>
+      <c r="G46">
+        <v>0.002008086303249002</v>
+      </c>
+      <c r="H46">
+        <v>1.000887885836834</v>
+      </c>
+      <c r="I46">
+        <v>0.0493103594313693</v>
+      </c>
+      <c r="J46">
+        <v>0.01027327310293913</v>
+      </c>
+      <c r="K46">
+        <v>0.8033511638641357</v>
+      </c>
+      <c r="L46">
+        <v>1.003115653991699</v>
+      </c>
+      <c r="M46">
+        <v>0.5880046486854553</v>
+      </c>
+      <c r="N46" t="s">
+        <v>353</v>
+      </c>
+      <c r="O46" t="s">
+        <v>413</v>
+      </c>
+      <c r="P46" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47">
+        <v>0</v>
+      </c>
+      <c r="B47" t="s">
+        <v>114</v>
+      </c>
+      <c r="C47">
+        <v>0.006002069299008307</v>
+      </c>
+      <c r="D47">
+        <v>-5.982951188343577E-05</v>
+      </c>
+      <c r="E47">
+        <v>0.03435325622558594</v>
+      </c>
+      <c r="F47">
+        <v>0.00297520961612463</v>
+      </c>
+      <c r="G47">
+        <v>0.002225124510005116</v>
+      </c>
+      <c r="H47">
+        <v>1.00068563979014</v>
+      </c>
+      <c r="I47">
+        <v>0.04942537703329125</v>
+      </c>
+      <c r="J47">
+        <v>-0.00174159649759531</v>
+      </c>
+      <c r="K47">
+        <v>-0.1780303120613098</v>
+      </c>
+      <c r="L47">
+        <v>1.966255068778992</v>
+      </c>
+      <c r="M47">
+        <v>-0.09968262910842896</v>
+      </c>
+      <c r="N47" t="s">
+        <v>354</v>
+      </c>
+      <c r="O47" t="s">
+        <v>414</v>
+      </c>
+      <c r="P47" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48">
+        <v>0</v>
+      </c>
+      <c r="B48" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48">
+        <v>0.01421835699048325</v>
+      </c>
+      <c r="D48">
+        <v>-0.001079675159417093</v>
+      </c>
+      <c r="E48">
+        <v>0.08318383246660233</v>
+      </c>
+      <c r="F48">
+        <v>0.003023156896233559</v>
+      </c>
+      <c r="G48">
+        <v>0.002219492103904486</v>
+      </c>
+      <c r="H48">
+        <v>1.000533416827559</v>
+      </c>
+      <c r="I48">
+        <v>0.05093703505271813</v>
+      </c>
+      <c r="J48">
+        <v>-0.01297938730567694</v>
+      </c>
+      <c r="K48">
+        <v>-0.9709558486938477</v>
+      </c>
+      <c r="L48">
+        <v>4.761138916015625</v>
+      </c>
+      <c r="M48">
+        <v>-0.7428927421569824</v>
+      </c>
+      <c r="N48" t="s">
+        <v>355</v>
+      </c>
+      <c r="O48" t="s">
+        <v>415</v>
+      </c>
+      <c r="P48" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49">
+        <v>0</v>
+      </c>
+      <c r="B49" t="s">
+        <v>116</v>
+      </c>
+      <c r="C49">
+        <v>0.02823125327652523</v>
+      </c>
+      <c r="D49">
+        <v>-0.004250034224241972</v>
+      </c>
+      <c r="E49">
+        <v>0.2026477009057999</v>
+      </c>
+      <c r="F49">
+        <v>0.002868752926588058</v>
+      </c>
+      <c r="G49">
+        <v>0.00225606863386929</v>
+      </c>
+      <c r="H49">
+        <v>1.000232015327258</v>
+      </c>
+      <c r="I49">
+        <v>0.052562406234497</v>
+      </c>
+      <c r="J49">
+        <v>-0.02097252570092678</v>
+      </c>
+      <c r="K49">
+        <v>-0.9999991059303284</v>
+      </c>
+      <c r="L49">
+        <v>11.59881496429443</v>
+      </c>
+      <c r="M49">
+        <v>-1.200390815734863</v>
+      </c>
+      <c r="N49" t="s">
+        <v>356</v>
+      </c>
+      <c r="O49" t="s">
+        <v>416</v>
+      </c>
+      <c r="P49" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50">
+        <v>0</v>
+      </c>
+      <c r="B50" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50">
+        <v>0.07066278278924883</v>
+      </c>
+      <c r="D50">
+        <v>-0.0163482129573822</v>
+      </c>
+      <c r="E50">
+        <v>0.6303431391716003</v>
+      </c>
+      <c r="F50">
+        <v>0.002682674676179886</v>
+      </c>
+      <c r="G50">
+        <v>0.002482978859916329</v>
+      </c>
+      <c r="H50">
+        <v>1.000994337499845</v>
+      </c>
+      <c r="I50">
+        <v>0.05789222431688975</v>
+      </c>
+      <c r="J50">
+        <v>-0.02593541890382767</v>
+      </c>
+      <c r="K50">
+        <v>-1</v>
+      </c>
+      <c r="L50">
+        <v>36.07854080200195</v>
+      </c>
+      <c r="M50">
+        <v>-1.484448790550232</v>
+      </c>
+      <c r="N50" t="s">
+        <v>357</v>
+      </c>
+      <c r="O50" t="s">
+        <v>417</v>
+      </c>
+      <c r="P50" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51">
+        <v>0</v>
+      </c>
+      <c r="B51" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51">
+        <v>0.1273169861378646</v>
+      </c>
+      <c r="D51">
+        <v>-0.02108206413686275</v>
+      </c>
+      <c r="E51">
+        <v>0.8865062594413757</v>
+      </c>
+      <c r="F51">
+        <v>0.002596415113657713</v>
+      </c>
+      <c r="G51">
+        <v>0.002536255633458495</v>
+      </c>
+      <c r="H51">
+        <v>1.002570379436964</v>
+      </c>
+      <c r="I51">
+        <v>0.06636489074762002</v>
+      </c>
+      <c r="J51">
+        <v>-0.0237810667604208</v>
+      </c>
+      <c r="K51">
+        <v>-1</v>
+      </c>
+      <c r="L51">
+        <v>50.74038314819336</v>
+      </c>
+      <c r="M51">
+        <v>-1.361141443252563</v>
+      </c>
+      <c r="N51" t="s">
+        <v>358</v>
+      </c>
+      <c r="O51" t="s">
+        <v>418</v>
+      </c>
+      <c r="P51" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52">
+        <v>0</v>
+      </c>
+      <c r="B52" t="s">
+        <v>119</v>
+      </c>
+      <c r="C52">
+        <v>0.0002099837335729461</v>
+      </c>
+      <c r="D52">
+        <v>0.0003023363242391497</v>
+      </c>
+      <c r="E52">
+        <v>0.0006880525615997612</v>
+      </c>
+      <c r="F52">
+        <v>0.001099861576221883</v>
+      </c>
+      <c r="G52">
+        <v>0.001066045369952917</v>
+      </c>
+      <c r="H52">
+        <v>0.9996355095462761</v>
+      </c>
+      <c r="I52">
+        <v>0.04954052001105987</v>
+      </c>
+      <c r="J52">
+        <v>0.4394087493419647</v>
+      </c>
+      <c r="K52">
+        <v>1.691862821578979</v>
+      </c>
+      <c r="L52">
+        <v>0.03938161954283714</v>
+      </c>
+      <c r="M52">
+        <v>25.15015411376953</v>
+      </c>
+      <c r="N52" t="s">
+        <v>359</v>
+      </c>
+      <c r="O52" t="s">
+        <v>419</v>
+      </c>
+      <c r="P52" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53">
+        <v>0</v>
+      </c>
+      <c r="B53" t="s">
+        <v>120</v>
+      </c>
+      <c r="C53">
+        <v>0.0002575964929570067</v>
+      </c>
+      <c r="D53">
+        <v>0.0003678893262986094</v>
+      </c>
+      <c r="E53">
+        <v>0.0007431164849549532</v>
+      </c>
+      <c r="F53">
+        <v>0.001298991264775395</v>
+      </c>
+      <c r="G53">
+        <v>0.001235443749465048</v>
+      </c>
+      <c r="H53">
+        <v>0.9999752730280188</v>
+      </c>
+      <c r="I53">
+        <v>0.04933825069200614</v>
+      </c>
+      <c r="J53">
+        <v>0.4950627982616425</v>
+      </c>
+      <c r="K53">
+        <v>2.336601734161377</v>
+      </c>
+      <c r="L53">
+        <v>0.0425332747399807</v>
+      </c>
+      <c r="M53">
+        <v>28.3355884552002</v>
+      </c>
+      <c r="N53" t="s">
+        <v>360</v>
+      </c>
+      <c r="O53" t="s">
+        <v>420</v>
+      </c>
+      <c r="P53" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54">
+        <v>0</v>
+      </c>
+      <c r="B54" t="s">
+        <v>121</v>
+      </c>
+      <c r="C54">
+        <v>0.0002974568592246115</v>
+      </c>
+      <c r="D54">
+        <v>0.0004192670166958123</v>
+      </c>
+      <c r="E54">
+        <v>0.0007850323454476893</v>
+      </c>
+      <c r="F54">
+        <v>0.001469571841880679</v>
+      </c>
+      <c r="G54">
+        <v>0.001365749514661729</v>
+      </c>
+      <c r="H54">
+        <v>1.000232049712122</v>
+      </c>
+      <c r="I54">
+        <v>0.04929266001925449</v>
+      </c>
+      <c r="J54">
+        <v>0.5340760946273804</v>
+      </c>
+      <c r="K54">
+        <v>2.947983264923096</v>
+      </c>
+      <c r="L54">
+        <v>0.04493238776922226</v>
+      </c>
+      <c r="M54">
+        <v>30.56856727600098</v>
+      </c>
+      <c r="N54" t="s">
+        <v>361</v>
+      </c>
+      <c r="O54" t="s">
+        <v>421</v>
+      </c>
+      <c r="P54" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
+      <c r="A55">
+        <v>0</v>
+      </c>
+      <c r="B55" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55">
+        <v>0.0004340408960831805</v>
+      </c>
+      <c r="D55">
+        <v>0.0005911001935601234</v>
+      </c>
+      <c r="E55">
+        <v>0.0009483301546424627</v>
+      </c>
+      <c r="F55">
+        <v>0.002065256470814347</v>
+      </c>
+      <c r="G55">
+        <v>0.001752244308590889</v>
+      </c>
+      <c r="H55">
+        <v>1.000603193146043</v>
+      </c>
+      <c r="I55">
+        <v>0.04922346476327379</v>
+      </c>
+      <c r="J55">
+        <v>0.6233063340187073</v>
+      </c>
+      <c r="K55">
+        <v>5.931416988372803</v>
+      </c>
+      <c r="L55">
+        <v>0.05427895858883858</v>
+      </c>
+      <c r="M55">
+        <v>35.67578125</v>
+      </c>
+      <c r="N55" t="s">
+        <v>362</v>
+      </c>
+      <c r="O55" t="s">
+        <v>422</v>
+      </c>
+      <c r="P55" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56">
+        <v>0</v>
+      </c>
+      <c r="B56" t="s">
+        <v>122</v>
+      </c>
+      <c r="C56">
+        <v>0.0005831851173610313</v>
+      </c>
+      <c r="D56">
+        <v>0.0007745533366687596</v>
+      </c>
+      <c r="E56">
+        <v>0.001179406652227044</v>
+      </c>
+      <c r="F56">
+        <v>0.002674942836165428</v>
+      </c>
+      <c r="G56">
+        <v>0.002109373221173882</v>
+      </c>
+      <c r="H56">
+        <v>1.000586669117729</v>
+      </c>
+      <c r="I56">
+        <v>0.04959651472320963</v>
+      </c>
+      <c r="J56">
+        <v>0.6567313671112061</v>
+      </c>
+      <c r="K56">
+        <v>11.63270378112793</v>
+      </c>
+      <c r="L56">
+        <v>0.06750493496656418</v>
+      </c>
+      <c r="M56">
+        <v>37.58890533447266</v>
+      </c>
+      <c r="N56" t="s">
+        <v>363</v>
+      </c>
+      <c r="O56" t="s">
+        <v>423</v>
+      </c>
+      <c r="P56" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57">
+        <v>0</v>
+      </c>
+      <c r="B57" t="s">
+        <v>123</v>
+      </c>
+      <c r="C57">
+        <v>0.0007463787270494083</v>
+      </c>
+      <c r="D57">
+        <v>0.0009516929276287556</v>
+      </c>
+      <c r="E57">
+        <v>0.001543426536954939</v>
+      </c>
+      <c r="F57">
+        <v>0.003046562196686864</v>
+      </c>
+      <c r="G57">
+        <v>0.002262303838506341</v>
+      </c>
+      <c r="H57">
+        <v>1.000544112738359</v>
+      </c>
+      <c r="I57">
+        <v>0.04976086608447924</v>
+      </c>
+      <c r="J57">
+        <v>0.6166104674339294</v>
+      </c>
+      <c r="K57">
+        <v>21.5585823059082</v>
+      </c>
+      <c r="L57">
+        <v>0.08834010362625122</v>
+      </c>
+      <c r="M57">
+        <v>35.29253387451172</v>
+      </c>
+      <c r="N57" t="s">
+        <v>364</v>
+      </c>
+      <c r="O57" t="s">
+        <v>424</v>
+      </c>
+      <c r="P57" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58">
+        <v>0</v>
+      </c>
+      <c r="B58" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58">
+        <v>0.0009989395452740877</v>
+      </c>
+      <c r="D58">
+        <v>0.001147714676335454</v>
+      </c>
+      <c r="E58">
+        <v>0.002383002080023289</v>
+      </c>
+      <c r="F58">
+        <v>0.002986398991197348</v>
+      </c>
+      <c r="G58">
+        <v>0.002310264389961958</v>
+      </c>
+      <c r="H58">
+        <v>1.000066698763051</v>
+      </c>
+      <c r="I58">
+        <v>0.05195711418106834</v>
+      </c>
+      <c r="J58">
+        <v>0.4816255569458008</v>
+      </c>
+      <c r="K58">
+        <v>41.85675048828125</v>
+      </c>
+      <c r="L58">
+        <v>0.1363943368196487</v>
+      </c>
+      <c r="M58">
+        <v>27.56649017333984</v>
+      </c>
+      <c r="N58" t="s">
+        <v>365</v>
+      </c>
+      <c r="O58" t="s">
+        <v>425</v>
+      </c>
+      <c r="P58" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
+      <c r="A59">
+        <v>0</v>
+      </c>
+      <c r="B59" t="s">
+        <v>125</v>
+      </c>
+      <c r="C59">
+        <v>0.00121842078341957</v>
+      </c>
+      <c r="D59">
+        <v>0.00131466961465776</v>
+      </c>
+      <c r="E59">
+        <v>0.003393764374777675</v>
+      </c>
+      <c r="F59">
+        <v>0.002808468881994486</v>
+      </c>
+      <c r="G59">
+        <v>0.002356182551011443</v>
+      </c>
+      <c r="H59">
+        <v>0.9996449642359766</v>
+      </c>
+      <c r="I59">
+        <v>0.05394452602068969</v>
+      </c>
+      <c r="J59">
+        <v>0.3873779773712158</v>
+      </c>
+      <c r="K59">
+        <v>72.99018096923828</v>
+      </c>
+      <c r="L59">
+        <v>0.19424669444561</v>
+      </c>
+      <c r="M59">
+        <v>22.1721019744873</v>
+      </c>
+      <c r="N59" t="s">
+        <v>366</v>
+      </c>
+      <c r="O59" t="s">
+        <v>426</v>
+      </c>
+      <c r="P59" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60">
+        <v>0</v>
+      </c>
+      <c r="B60" t="s">
+        <v>126</v>
+      </c>
+      <c r="C60">
+        <v>0.00152361112458634</v>
+      </c>
+      <c r="D60">
+        <v>0.001551353838294744</v>
+      </c>
+      <c r="E60">
+        <v>0.005482275504618883</v>
+      </c>
+      <c r="F60">
+        <v>0.002637954661622643</v>
+      </c>
+      <c r="G60">
+        <v>0.002491025486961007</v>
+      </c>
+      <c r="H60">
+        <v>1.000826038846235</v>
+      </c>
+      <c r="I60">
+        <v>0.05815807285453824</v>
+      </c>
+      <c r="J60">
+        <v>0.2829762697219849</v>
+      </c>
+      <c r="K60">
+        <v>159.5193328857422</v>
+      </c>
+      <c r="L60">
+        <v>0.3137854337692261</v>
+      </c>
+      <c r="M60">
+        <v>16.19652938842773</v>
+      </c>
+      <c r="N60" t="s">
+        <v>367</v>
+      </c>
+      <c r="O60" t="s">
+        <v>427</v>
+      </c>
+      <c r="P60" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61">
+        <v>0</v>
+      </c>
+      <c r="B61" t="s">
+        <v>127</v>
+      </c>
+      <c r="C61">
+        <v>0.001750075317269635</v>
+      </c>
+      <c r="D61">
+        <v>0.001761390012688935</v>
+      </c>
+      <c r="E61">
+        <v>0.007444880902767181</v>
+      </c>
+      <c r="F61">
+        <v>0.002573625883087516</v>
+      </c>
+      <c r="G61">
+        <v>0.002637855708599091</v>
+      </c>
+      <c r="H61">
+        <v>1.002294981640147</v>
+      </c>
+      <c r="I61">
+        <v>0.06661113617095596</v>
+      </c>
+      <c r="J61">
+        <v>0.2365907579660416</v>
+      </c>
+      <c r="K61">
+        <v>318.0633544921875</v>
+      </c>
+      <c r="L61">
+        <v>0.4261178076267242</v>
+      </c>
+      <c r="M61">
+        <v>13.54159164428711</v>
+      </c>
+      <c r="N61" t="s">
+        <v>368</v>
+      </c>
+      <c r="O61" t="s">
+        <v>428</v>
+      </c>
+      <c r="P61" t="s">
+        <v>488</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" t="s">
+        <v>489</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/gbrt_standard_l2/performance.xlsx
+++ b/scripts/gbrt_standard_l2/performance.xlsx
@@ -9110,12 +9110,6556 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1"/>
+  <dimension ref="A1:B819"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
         <v>489</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.000770441722124815</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>-0.0001028071128530428</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.001715013640932739</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>-0.0003380241105332971</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>-0.0001853131107054651</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>-2.77215508504014E-06</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.0008724986691959202</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.0002553502563387156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.0006626725662499666</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.0006226093973964453</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.0002117732947226614</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0.000945317093282938</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>0.002619890728965402</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>0.0002742083743214607</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>0.0004044049710500985</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>6.364654109347612E-05</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>-0.0001481523649999872</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>0.00121728761587292</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>0.0004666263412218541</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>0.0007858558092266321</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>0.000182788833626546</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>0.0009476979030296206</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>0.001978994579985738</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>0.000863464898429811</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>0.001030732761137187</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>0.0005395409534685314</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>-8.173258538590744E-05</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>-0.0001228617911692709</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>-0.0009065986960195005</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>-3.930926141038071E-06</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>0.0003044613404199481</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <v>0.0002057750389212742</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>-0.0001874161243904382</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <v>0.0002528015756979585</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36">
+        <v>0.0008136127726174891</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>-3.765724250115454E-05</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>0.001090249395929277</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>-0.000774047861341387</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>0.001896122936159372</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>0.0007020663470029831</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>-0.0001471860450692475</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>0.001386709976941347</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>0.0001884701632661745</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>-0.0002889719908125699</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>0.001814932911656797</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>6.492176908068359E-05</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>0.0001196853554574773</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>0.0003658852656371891</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>0.0002476791560184211</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>0.0007629762985743582</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>-0.001457588747143745</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <v>-1.22720575745916E-06</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>0.0001707548944978043</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>0.0002991114743053913</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <v>0.0003856905095744878</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <v>0.0007956588524393737</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58">
+        <v>0.000401391473133117</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59">
+        <v>0.0005097539979033172</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60">
+        <v>0.0009115893044508994</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61">
+        <v>0.0007433913415297866</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62">
+        <v>0.0004205382720101625</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63">
+        <v>0.0001121377499657683</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="B64">
+        <v>0.000701285433024168</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="B65">
+        <v>0.002449336461722851</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="B66">
+        <v>0.0005200384184718132</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67">
+        <v>0.0003116689040325582</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="B68">
+        <v>0.0004327587375883013</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69">
+        <v>67</v>
+      </c>
+      <c r="B69">
+        <v>0.0004804546770174056</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70">
+        <v>68</v>
+      </c>
+      <c r="B70">
+        <v>0.00149270158726722</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71">
+        <v>69</v>
+      </c>
+      <c r="B71">
+        <v>0.0009745928691700101</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72">
+        <v>70</v>
+      </c>
+      <c r="B72">
+        <v>0.0004653470532502979</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73">
+        <v>71</v>
+      </c>
+      <c r="B73">
+        <v>-0.0005072774365544319</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74">
+        <v>72</v>
+      </c>
+      <c r="B74">
+        <v>0.0008948839968070388</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75">
+        <v>73</v>
+      </c>
+      <c r="B75">
+        <v>0.001236394047737122</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76">
+        <v>74</v>
+      </c>
+      <c r="B76">
+        <v>0.001796173281036317</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77">
+        <v>75</v>
+      </c>
+      <c r="B77">
+        <v>-0.0007087885751388967</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78">
+        <v>76</v>
+      </c>
+      <c r="B78">
+        <v>0.003428520867601037</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79">
+        <v>77</v>
+      </c>
+      <c r="B79">
+        <v>0.0008156115654855967</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80">
+        <v>78</v>
+      </c>
+      <c r="B80">
+        <v>0.0001745657064020634</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81">
+        <v>79</v>
+      </c>
+      <c r="B81">
+        <v>-6.416687028831802E-06</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82">
+        <v>80</v>
+      </c>
+      <c r="B82">
+        <v>2.730797132244334E-05</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83">
+        <v>81</v>
+      </c>
+      <c r="B83">
+        <v>0.0001765281485859305</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84">
+        <v>82</v>
+      </c>
+      <c r="B84">
+        <v>0.000604292144998908</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85">
+        <v>83</v>
+      </c>
+      <c r="B85">
+        <v>0.000350291928043589</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86">
+        <v>84</v>
+      </c>
+      <c r="B86">
+        <v>0.0002533260558266193</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87">
+        <v>85</v>
+      </c>
+      <c r="B87">
+        <v>0.0002491873747203499</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88">
+        <v>86</v>
+      </c>
+      <c r="B88">
+        <v>0.0009879504796117544</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89">
+        <v>87</v>
+      </c>
+      <c r="B89">
+        <v>0.0001646368618821725</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90">
+        <v>88</v>
+      </c>
+      <c r="B90">
+        <v>0.000951294437982142</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91">
+        <v>89</v>
+      </c>
+      <c r="B91">
+        <v>0.0004936718032695353</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92">
+        <v>90</v>
+      </c>
+      <c r="B92">
+        <v>0.0005025527207180858</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93">
+        <v>91</v>
+      </c>
+      <c r="B93">
+        <v>0.00124579353723675</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94">
+        <v>92</v>
+      </c>
+      <c r="B94">
+        <v>0.0007000305340625346</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95">
+        <v>93</v>
+      </c>
+      <c r="B95">
+        <v>0.001828460139222443</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96">
+        <v>94</v>
+      </c>
+      <c r="B96">
+        <v>0.0001026967074722052</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97">
+        <v>95</v>
+      </c>
+      <c r="B97">
+        <v>0.0006605933886021376</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98">
+        <v>96</v>
+      </c>
+      <c r="B98">
+        <v>0.0003987303643953055</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99">
+        <v>97</v>
+      </c>
+      <c r="B99">
+        <v>0.0004656975215766579</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100">
+        <v>98</v>
+      </c>
+      <c r="B100">
+        <v>0.0002443398116156459</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101">
+        <v>99</v>
+      </c>
+      <c r="B101">
+        <v>5.846767817274667E-05</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102">
+        <v>100</v>
+      </c>
+      <c r="B102">
+        <v>0.0003874915710184723</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103">
+        <v>101</v>
+      </c>
+      <c r="B103">
+        <v>-0.0001872163848020136</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104">
+        <v>102</v>
+      </c>
+      <c r="B104">
+        <v>0.002255282597616315</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105">
+        <v>103</v>
+      </c>
+      <c r="B105">
+        <v>0.000282497116131708</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106">
+        <v>104</v>
+      </c>
+      <c r="B106">
+        <v>0.0003460856969468296</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107">
+        <v>105</v>
+      </c>
+      <c r="B107">
+        <v>0.001459233462810516</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108">
+        <v>106</v>
+      </c>
+      <c r="B108">
+        <v>0.001584341865964234</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109">
+        <v>107</v>
+      </c>
+      <c r="B109">
+        <v>0.0003287957515567541</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110">
+        <v>108</v>
+      </c>
+      <c r="B110">
+        <v>0.0005238943849690259</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111">
+        <v>109</v>
+      </c>
+      <c r="B111">
+        <v>0.001761522958986461</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112">
+        <v>110</v>
+      </c>
+      <c r="B112">
+        <v>0.000493512605316937</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113">
+        <v>111</v>
+      </c>
+      <c r="B113">
+        <v>4.403282218845561E-05</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114">
+        <v>112</v>
+      </c>
+      <c r="B114">
+        <v>0.001147604314610362</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115">
+        <v>113</v>
+      </c>
+      <c r="B115">
+        <v>-0.0001313788525294513</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116">
+        <v>114</v>
+      </c>
+      <c r="B116">
+        <v>0.0003764723078347743</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117">
+        <v>115</v>
+      </c>
+      <c r="B117">
+        <v>-0.0006015296094119549</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118">
+        <v>116</v>
+      </c>
+      <c r="B118">
+        <v>6.167364335851744E-05</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119">
+        <v>117</v>
+      </c>
+      <c r="B119">
+        <v>9.747381409397349E-05</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120">
+        <v>118</v>
+      </c>
+      <c r="B120">
+        <v>0.0003257163043599576</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121">
+        <v>119</v>
+      </c>
+      <c r="B121">
+        <v>-0.0001159968815045431</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122">
+        <v>120</v>
+      </c>
+      <c r="B122">
+        <v>0.001033484702929854</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123">
+        <v>121</v>
+      </c>
+      <c r="B123">
+        <v>0.0003581833152566105</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124">
+        <v>122</v>
+      </c>
+      <c r="B124">
+        <v>0.0008567313780076802</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125">
+        <v>123</v>
+      </c>
+      <c r="B125">
+        <v>0.0002937921090051532</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126">
+        <v>124</v>
+      </c>
+      <c r="B126">
+        <v>0.0004994107875972986</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127">
+        <v>125</v>
+      </c>
+      <c r="B127">
+        <v>0.001138103427365422</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128">
+        <v>126</v>
+      </c>
+      <c r="B128">
+        <v>0.0008449094020761549</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129">
+        <v>127</v>
+      </c>
+      <c r="B129">
+        <v>0.0008651980897411704</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130">
+        <v>128</v>
+      </c>
+      <c r="B130">
+        <v>3.476342681096867E-05</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131">
+        <v>129</v>
+      </c>
+      <c r="B131">
+        <v>0.001754953642375767</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132">
+        <v>130</v>
+      </c>
+      <c r="B132">
+        <v>0.0003510580863803625</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133">
+        <v>131</v>
+      </c>
+      <c r="B133">
+        <v>0.0002640078018885106</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134">
+        <v>132</v>
+      </c>
+      <c r="B134">
+        <v>-6.55193070997484E-05</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135">
+        <v>133</v>
+      </c>
+      <c r="B135">
+        <v>0.000339509075274691</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136">
+        <v>134</v>
+      </c>
+      <c r="B136">
+        <v>0.0004622174892574549</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137">
+        <v>135</v>
+      </c>
+      <c r="B137">
+        <v>0.0013365134363994</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138">
+        <v>136</v>
+      </c>
+      <c r="B138">
+        <v>0.0002925756853073835</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139">
+        <v>137</v>
+      </c>
+      <c r="B139">
+        <v>0.0001848763204179704</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140">
+        <v>138</v>
+      </c>
+      <c r="B140">
+        <v>0.0009943793993443251</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141">
+        <v>139</v>
+      </c>
+      <c r="B141">
+        <v>0.0001433819998055696</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142">
+        <v>140</v>
+      </c>
+      <c r="B142">
+        <v>-0.0005588789936155081</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143">
+        <v>141</v>
+      </c>
+      <c r="B143">
+        <v>0.0055151148699224</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144">
+        <v>142</v>
+      </c>
+      <c r="B144">
+        <v>0.001197477802634239</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145">
+        <v>143</v>
+      </c>
+      <c r="B145">
+        <v>0.001175292767584324</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146">
+        <v>144</v>
+      </c>
+      <c r="B146">
+        <v>0.001153582357801497</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147">
+        <v>145</v>
+      </c>
+      <c r="B147">
+        <v>0.0005988270859234035</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148">
+        <v>146</v>
+      </c>
+      <c r="B148">
+        <v>0.001608598046004772</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149">
+        <v>147</v>
+      </c>
+      <c r="B149">
+        <v>0.0009463118622079492</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150">
+        <v>148</v>
+      </c>
+      <c r="B150">
+        <v>0.001262452686205506</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151">
+        <v>149</v>
+      </c>
+      <c r="B151">
+        <v>0.0003822445287369192</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152">
+        <v>150</v>
+      </c>
+      <c r="B152">
+        <v>0.0005143247544765472</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153">
+        <v>151</v>
+      </c>
+      <c r="B153">
+        <v>0.001155138947069645</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154">
+        <v>152</v>
+      </c>
+      <c r="B154">
+        <v>0.0004627616726793349</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155">
+        <v>153</v>
+      </c>
+      <c r="B155">
+        <v>-0.0002028460003202781</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156">
+        <v>154</v>
+      </c>
+      <c r="B156">
+        <v>0.004323058295994997</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157">
+        <v>155</v>
+      </c>
+      <c r="B157">
+        <v>0.001116517232730985</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158">
+        <v>156</v>
+      </c>
+      <c r="B158">
+        <v>0.0002702675410546362</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159">
+        <v>157</v>
+      </c>
+      <c r="B159">
+        <v>0.001366810756735504</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160">
+        <v>158</v>
+      </c>
+      <c r="B160">
+        <v>0.0008185940678231418</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161">
+        <v>159</v>
+      </c>
+      <c r="B161">
+        <v>0.0006083442131057382</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162">
+        <v>160</v>
+      </c>
+      <c r="B162">
+        <v>0.0004493342421483248</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163">
+        <v>161</v>
+      </c>
+      <c r="B163">
+        <v>0.0009010041248984635</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164">
+        <v>162</v>
+      </c>
+      <c r="B164">
+        <v>0.0008926824084483087</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165">
+        <v>163</v>
+      </c>
+      <c r="B165">
+        <v>0.001103044720366597</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166">
+        <v>164</v>
+      </c>
+      <c r="B166">
+        <v>0.0006298883236013353</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167">
+        <v>165</v>
+      </c>
+      <c r="B167">
+        <v>0.001062553375959396</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168">
+        <v>166</v>
+      </c>
+      <c r="B168">
+        <v>0.0001181151674245484</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169">
+        <v>167</v>
+      </c>
+      <c r="B169">
+        <v>0.002516953507438302</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170">
+        <v>168</v>
+      </c>
+      <c r="B170">
+        <v>0.0009860718855634332</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171">
+        <v>169</v>
+      </c>
+      <c r="B171">
+        <v>4.130394870571763E-07</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172">
+        <v>170</v>
+      </c>
+      <c r="B172">
+        <v>0.0002232761908089742</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173">
+        <v>171</v>
+      </c>
+      <c r="B173">
+        <v>0.0006058482103981078</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174">
+        <v>172</v>
+      </c>
+      <c r="B174">
+        <v>0.0001388669334119186</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175">
+        <v>173</v>
+      </c>
+      <c r="B175">
+        <v>-4.092749350093072E-06</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176">
+        <v>174</v>
+      </c>
+      <c r="B176">
+        <v>0.0005778694758191705</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177">
+        <v>175</v>
+      </c>
+      <c r="B177">
+        <v>0.0008636490674689412</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178">
+        <v>176</v>
+      </c>
+      <c r="B178">
+        <v>0.0005005375132896006</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179">
+        <v>177</v>
+      </c>
+      <c r="B179">
+        <v>0.000490188249386847</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180">
+        <v>178</v>
+      </c>
+      <c r="B180">
+        <v>0.0006098892772570252</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181">
+        <v>179</v>
+      </c>
+      <c r="B181">
+        <v>0.0007065547979436815</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182">
+        <v>180</v>
+      </c>
+      <c r="B182">
+        <v>-0.002096913289278746</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183">
+        <v>181</v>
+      </c>
+      <c r="B183">
+        <v>-0.0003185586247127503</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184">
+        <v>182</v>
+      </c>
+      <c r="B184">
+        <v>-7.044238736853004E-05</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185">
+        <v>183</v>
+      </c>
+      <c r="B185">
+        <v>0.0006908928044140339</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186">
+        <v>184</v>
+      </c>
+      <c r="B186">
+        <v>0.0006033077370375395</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187">
+        <v>185</v>
+      </c>
+      <c r="B187">
+        <v>0.000389064138289541</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188">
+        <v>186</v>
+      </c>
+      <c r="B188">
+        <v>0.001351447775959969</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189">
+        <v>187</v>
+      </c>
+      <c r="B189">
+        <v>0.001510037109255791</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190">
+        <v>188</v>
+      </c>
+      <c r="B190">
+        <v>0.0006067172507755458</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191">
+        <v>189</v>
+      </c>
+      <c r="B191">
+        <v>0.00071103242225945</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192">
+        <v>190</v>
+      </c>
+      <c r="B192">
+        <v>0.001258543110452592</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193">
+        <v>191</v>
+      </c>
+      <c r="B193">
+        <v>0.0006482576718553901</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194">
+        <v>192</v>
+      </c>
+      <c r="B194">
+        <v>-0.0006225165561772883</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195">
+        <v>193</v>
+      </c>
+      <c r="B195">
+        <v>-0.003491333918645978</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196">
+        <v>194</v>
+      </c>
+      <c r="B196">
+        <v>0.002255163621157408</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197">
+        <v>195</v>
+      </c>
+      <c r="B197">
+        <v>0.0005715423612855375</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198">
+        <v>196</v>
+      </c>
+      <c r="B198">
+        <v>0.0008703160565346479</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199">
+        <v>197</v>
+      </c>
+      <c r="B199">
+        <v>0.0004739909491036087</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200">
+        <v>198</v>
+      </c>
+      <c r="B200">
+        <v>7.599176024086773E-05</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201">
+        <v>199</v>
+      </c>
+      <c r="B201">
+        <v>0.0007651137420907617</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202">
+        <v>200</v>
+      </c>
+      <c r="B202">
+        <v>0.0002512625942472368</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203">
+        <v>201</v>
+      </c>
+      <c r="B203">
+        <v>0.0002705933293327689</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204">
+        <v>202</v>
+      </c>
+      <c r="B204">
+        <v>0.001222085207700729</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205">
+        <v>203</v>
+      </c>
+      <c r="B205">
+        <v>0.0005563049344345927</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206">
+        <v>204</v>
+      </c>
+      <c r="B206">
+        <v>1.869572588475421E-05</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207">
+        <v>205</v>
+      </c>
+      <c r="B207">
+        <v>0.0003726233553607017</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208">
+        <v>206</v>
+      </c>
+      <c r="B208">
+        <v>-0.003499008947983384</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209">
+        <v>207</v>
+      </c>
+      <c r="B209">
+        <v>-0.0001608014135854319</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210">
+        <v>208</v>
+      </c>
+      <c r="B210">
+        <v>0.0004324742476455867</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211">
+        <v>209</v>
+      </c>
+      <c r="B211">
+        <v>0.0001571618631714955</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212">
+        <v>210</v>
+      </c>
+      <c r="B212">
+        <v>0.0008527668542228639</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213">
+        <v>211</v>
+      </c>
+      <c r="B213">
+        <v>0.0003104545758105814</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214">
+        <v>212</v>
+      </c>
+      <c r="B214">
+        <v>0.0005467107403092086</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215">
+        <v>213</v>
+      </c>
+      <c r="B215">
+        <v>0.0004359916783869267</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216">
+        <v>214</v>
+      </c>
+      <c r="B216">
+        <v>0.0004290748620405793</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217">
+        <v>215</v>
+      </c>
+      <c r="B217">
+        <v>0.0007684269803576171</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218">
+        <v>216</v>
+      </c>
+      <c r="B218">
+        <v>0.0006340822437778115</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219">
+        <v>217</v>
+      </c>
+      <c r="B219">
+        <v>0.0004534514155238867</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220">
+        <v>218</v>
+      </c>
+      <c r="B220">
+        <v>0.0007235153461806476</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221">
+        <v>219</v>
+      </c>
+      <c r="B221">
+        <v>-0.002842776011675596</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222">
+        <v>220</v>
+      </c>
+      <c r="B222">
+        <v>0.001082502072677016</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223">
+        <v>221</v>
+      </c>
+      <c r="B223">
+        <v>-8.343936497112736E-05</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224">
+        <v>222</v>
+      </c>
+      <c r="B224">
+        <v>0.001394206425175071</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225">
+        <v>223</v>
+      </c>
+      <c r="B225">
+        <v>0.000392858317354694</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226">
+        <v>224</v>
+      </c>
+      <c r="B226">
+        <v>0.0006085871136747301</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227">
+        <v>225</v>
+      </c>
+      <c r="B227">
+        <v>0.001008569612167776</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228">
+        <v>226</v>
+      </c>
+      <c r="B228">
+        <v>-3.151825467284652E-06</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229">
+        <v>227</v>
+      </c>
+      <c r="B229">
+        <v>0.0007883149664849043</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230">
+        <v>228</v>
+      </c>
+      <c r="B230">
+        <v>0.001434514066204429</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231">
+        <v>229</v>
+      </c>
+      <c r="B231">
+        <v>0.0005859544035047293</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232">
+        <v>230</v>
+      </c>
+      <c r="B232">
+        <v>0.0002211407118011266</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233">
+        <v>231</v>
+      </c>
+      <c r="B233">
+        <v>-2.886453148676082E-05</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234">
+        <v>232</v>
+      </c>
+      <c r="B234">
+        <v>0.0002796224434860051</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235">
+        <v>233</v>
+      </c>
+      <c r="B235">
+        <v>0.0009731474565342069</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236">
+        <v>234</v>
+      </c>
+      <c r="B236">
+        <v>4.694554445450194E-05</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237">
+        <v>235</v>
+      </c>
+      <c r="B237">
+        <v>0.0006823645089752972</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238">
+        <v>236</v>
+      </c>
+      <c r="B238">
+        <v>0.0009834785014390945</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239">
+        <v>237</v>
+      </c>
+      <c r="B239">
+        <v>0.0001791491522453725</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240">
+        <v>238</v>
+      </c>
+      <c r="B240">
+        <v>-0.0005222957115620375</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241">
+        <v>239</v>
+      </c>
+      <c r="B241">
+        <v>0.002190529368817806</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242">
+        <v>240</v>
+      </c>
+      <c r="B242">
+        <v>0.0001122239846154116</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243">
+        <v>241</v>
+      </c>
+      <c r="B243">
+        <v>6.223028321983293E-05</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244">
+        <v>242</v>
+      </c>
+      <c r="B244">
+        <v>0.0005240742466412485</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245">
+        <v>243</v>
+      </c>
+      <c r="B245">
+        <v>0.000114477559691295</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246">
+        <v>244</v>
+      </c>
+      <c r="B246">
+        <v>0.0004492454463616014</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247">
+        <v>245</v>
+      </c>
+      <c r="B247">
+        <v>0.00329177244566381</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248">
+        <v>246</v>
+      </c>
+      <c r="B248">
+        <v>0.0004695471143350005</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249">
+        <v>247</v>
+      </c>
+      <c r="B249">
+        <v>-0.0001613336353329942</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250">
+        <v>248</v>
+      </c>
+      <c r="B250">
+        <v>0.0004957248456776142</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251">
+        <v>249</v>
+      </c>
+      <c r="B251">
+        <v>0.0001234634110005572</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252">
+        <v>250</v>
+      </c>
+      <c r="B252">
+        <v>0.0004942268715240061</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253">
+        <v>251</v>
+      </c>
+      <c r="B253">
+        <v>0.0008415021002292633</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254">
+        <v>252</v>
+      </c>
+      <c r="B254">
+        <v>9.788348688744009E-05</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255">
+        <v>253</v>
+      </c>
+      <c r="B255">
+        <v>-0.0001567536091897637</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256">
+        <v>254</v>
+      </c>
+      <c r="B256">
+        <v>0.0005938417743891478</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257">
+        <v>255</v>
+      </c>
+      <c r="B257">
+        <v>0.0001664238516241312</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258">
+        <v>256</v>
+      </c>
+      <c r="B258">
+        <v>0.0005772691802121699</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259">
+        <v>257</v>
+      </c>
+      <c r="B259">
+        <v>0.0001678273547440767</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260">
+        <v>258</v>
+      </c>
+      <c r="B260">
+        <v>0.001867415150627494</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261">
+        <v>259</v>
+      </c>
+      <c r="B261">
+        <v>-0.0003491454699542373</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262">
+        <v>260</v>
+      </c>
+      <c r="B262">
+        <v>0.00133557035587728</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263">
+        <v>261</v>
+      </c>
+      <c r="B263">
+        <v>0.0003154452133458108</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264">
+        <v>262</v>
+      </c>
+      <c r="B264">
+        <v>-2.592018063296564E-05</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265">
+        <v>263</v>
+      </c>
+      <c r="B265">
+        <v>0.0004085885302629322</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266">
+        <v>264</v>
+      </c>
+      <c r="B266">
+        <v>0.0008737595053389668</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267">
+        <v>265</v>
+      </c>
+      <c r="B267">
+        <v>0.0005211055395193398</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268">
+        <v>266</v>
+      </c>
+      <c r="B268">
+        <v>0.000316397548886016</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269">
+        <v>267</v>
+      </c>
+      <c r="B269">
+        <v>0.001309210667386651</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270">
+        <v>268</v>
+      </c>
+      <c r="B270">
+        <v>0.0002435739152133465</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271">
+        <v>269</v>
+      </c>
+      <c r="B271">
+        <v>0.0006365600856952369</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272">
+        <v>270</v>
+      </c>
+      <c r="B272">
+        <v>-0.0006637563928961754</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273">
+        <v>271</v>
+      </c>
+      <c r="B273">
+        <v>0.001942449249327183</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274">
+        <v>272</v>
+      </c>
+      <c r="B274">
+        <v>0.0007579956436529756</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275">
+        <v>273</v>
+      </c>
+      <c r="B275">
+        <v>0.0006526062497869134</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276">
+        <v>274</v>
+      </c>
+      <c r="B276">
+        <v>0.0005248195957392454</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277">
+        <v>275</v>
+      </c>
+      <c r="B277">
+        <v>0.0007698744302615523</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278">
+        <v>276</v>
+      </c>
+      <c r="B278">
+        <v>0.0002842446556314826</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279">
+        <v>277</v>
+      </c>
+      <c r="B279">
+        <v>0.0005090089980512857</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280">
+        <v>278</v>
+      </c>
+      <c r="B280">
+        <v>0.0001374303246848285</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281">
+        <v>279</v>
+      </c>
+      <c r="B281">
+        <v>0.0006894079269841313</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282">
+        <v>280</v>
+      </c>
+      <c r="B282">
+        <v>0.000163096105097793</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283">
+        <v>281</v>
+      </c>
+      <c r="B283">
+        <v>0.0006630307761952281</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284">
+        <v>282</v>
+      </c>
+      <c r="B284">
+        <v>0.000222611051867716</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285">
+        <v>283</v>
+      </c>
+      <c r="B285">
+        <v>5.485638666868908E-06</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286">
+        <v>284</v>
+      </c>
+      <c r="B286">
+        <v>0.001445787260308862</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287">
+        <v>285</v>
+      </c>
+      <c r="B287">
+        <v>0.0004335646226536483</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288">
+        <v>286</v>
+      </c>
+      <c r="B288">
+        <v>0.001054182997904718</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289">
+        <v>287</v>
+      </c>
+      <c r="B289">
+        <v>0.0003866736369673163</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290">
+        <v>288</v>
+      </c>
+      <c r="B290">
+        <v>0.0001340674207312986</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291">
+        <v>289</v>
+      </c>
+      <c r="B291">
+        <v>1.458058250136673E-05</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292">
+        <v>290</v>
+      </c>
+      <c r="B292">
+        <v>0.0009765419526956975</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293">
+        <v>291</v>
+      </c>
+      <c r="B293">
+        <v>0.0003287604486104101</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294">
+        <v>292</v>
+      </c>
+      <c r="B294">
+        <v>9.217101614922285E-05</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295">
+        <v>293</v>
+      </c>
+      <c r="B295">
+        <v>0.000683105259668082</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296">
+        <v>294</v>
+      </c>
+      <c r="B296">
+        <v>0.0002804739342536777</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297">
+        <v>295</v>
+      </c>
+      <c r="B297">
+        <v>0.0003432839585002512</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298">
+        <v>296</v>
+      </c>
+      <c r="B298">
+        <v>0.0003207509289495647</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299">
+        <v>297</v>
+      </c>
+      <c r="B299">
+        <v>-0.0004568722506519407</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300">
+        <v>298</v>
+      </c>
+      <c r="B300">
+        <v>0.0003982609487138689</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301">
+        <v>299</v>
+      </c>
+      <c r="B301">
+        <v>0.0006088691879995167</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302">
+        <v>300</v>
+      </c>
+      <c r="B302">
+        <v>0.0001008177277981304</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303">
+        <v>301</v>
+      </c>
+      <c r="B303">
+        <v>0.0002746850077528507</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304">
+        <v>302</v>
+      </c>
+      <c r="B304">
+        <v>0.0004200166731607169</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305">
+        <v>303</v>
+      </c>
+      <c r="B305">
+        <v>0.0008796254405751824</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306">
+        <v>304</v>
+      </c>
+      <c r="B306">
+        <v>0.000348283996572718</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307">
+        <v>305</v>
+      </c>
+      <c r="B307">
+        <v>0.0003298381634522229</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308">
+        <v>306</v>
+      </c>
+      <c r="B308">
+        <v>-0.0004582175170071423</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309">
+        <v>307</v>
+      </c>
+      <c r="B309">
+        <v>0.0007763283792883158</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310">
+        <v>308</v>
+      </c>
+      <c r="B310">
+        <v>0.0003588839608710259</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311">
+        <v>309</v>
+      </c>
+      <c r="B311">
+        <v>-5.052008054917678E-05</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312">
+        <v>310</v>
+      </c>
+      <c r="B312">
+        <v>0.000564312154892832</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313">
+        <v>311</v>
+      </c>
+      <c r="B313">
+        <v>-8.657079888507724E-05</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314">
+        <v>312</v>
+      </c>
+      <c r="B314">
+        <v>0.001330863684415817</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315">
+        <v>313</v>
+      </c>
+      <c r="B315">
+        <v>0.0007254019728861749</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316">
+        <v>314</v>
+      </c>
+      <c r="B316">
+        <v>0.0006037337007001042</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317">
+        <v>315</v>
+      </c>
+      <c r="B317">
+        <v>0.0003513389965519309</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318">
+        <v>316</v>
+      </c>
+      <c r="B318">
+        <v>0.001477608690038323</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319">
+        <v>317</v>
+      </c>
+      <c r="B319">
+        <v>-0.000256258761510253</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320">
+        <v>318</v>
+      </c>
+      <c r="B320">
+        <v>0.0002286635572090745</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321">
+        <v>319</v>
+      </c>
+      <c r="B321">
+        <v>0.000969671702478081</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322">
+        <v>320</v>
+      </c>
+      <c r="B322">
+        <v>0.0003327002341393381</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323">
+        <v>321</v>
+      </c>
+      <c r="B323">
+        <v>8.968696783995256E-05</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324">
+        <v>322</v>
+      </c>
+      <c r="B324">
+        <v>-0.0005508841131813824</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325">
+        <v>323</v>
+      </c>
+      <c r="B325">
+        <v>-0.001006009872071445</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326">
+        <v>324</v>
+      </c>
+      <c r="B326">
+        <v>-0.0001302539458265528</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327">
+        <v>325</v>
+      </c>
+      <c r="B327">
+        <v>0.0009813398355618119</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328">
+        <v>326</v>
+      </c>
+      <c r="B328">
+        <v>0.0004215812950860709</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329">
+        <v>327</v>
+      </c>
+      <c r="B329">
+        <v>0.0005294025177136064</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330">
+        <v>328</v>
+      </c>
+      <c r="B330">
+        <v>8.808587881503627E-05</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331">
+        <v>329</v>
+      </c>
+      <c r="B331">
+        <v>0.0002205590717494488</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332">
+        <v>330</v>
+      </c>
+      <c r="B332">
+        <v>0.001364596886560321</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333">
+        <v>331</v>
+      </c>
+      <c r="B333">
+        <v>0.001404065056703985</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334">
+        <v>332</v>
+      </c>
+      <c r="B334">
+        <v>0.0010115533368662</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335">
+        <v>333</v>
+      </c>
+      <c r="B335">
+        <v>0.001007670303806663</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336">
+        <v>334</v>
+      </c>
+      <c r="B336">
+        <v>0.0004687515611294657</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337">
+        <v>335</v>
+      </c>
+      <c r="B337">
+        <v>0.001919305883347988</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338">
+        <v>336</v>
+      </c>
+      <c r="B338">
+        <v>0.001321235205978155</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339">
+        <v>337</v>
+      </c>
+      <c r="B339">
+        <v>0.000508393335621804</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340">
+        <v>338</v>
+      </c>
+      <c r="B340">
+        <v>0.001104478375054896</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341">
+        <v>339</v>
+      </c>
+      <c r="B341">
+        <v>0.0001685573224676773</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342">
+        <v>340</v>
+      </c>
+      <c r="B342">
+        <v>0.001062869210727513</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343">
+        <v>341</v>
+      </c>
+      <c r="B343">
+        <v>0.0008479426032863557</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344">
+        <v>342</v>
+      </c>
+      <c r="B344">
+        <v>0.0004343884938862175</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345">
+        <v>343</v>
+      </c>
+      <c r="B345">
+        <v>0.00108334026299417</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346">
+        <v>344</v>
+      </c>
+      <c r="B346">
+        <v>0.0002339195052627474</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347">
+        <v>345</v>
+      </c>
+      <c r="B347">
+        <v>0.0004724370373878628</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348">
+        <v>346</v>
+      </c>
+      <c r="B348">
+        <v>0.0004256074607837945</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349">
+        <v>347</v>
+      </c>
+      <c r="B349">
+        <v>0.0004684030427597463</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350">
+        <v>348</v>
+      </c>
+      <c r="B350">
+        <v>0.0008250988321378827</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351">
+        <v>349</v>
+      </c>
+      <c r="B351">
+        <v>0.0006918431608937681</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352">
+        <v>350</v>
+      </c>
+      <c r="B352">
+        <v>0.001162197208032012</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353">
+        <v>351</v>
+      </c>
+      <c r="B353">
+        <v>0.000626809720415622</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354">
+        <v>352</v>
+      </c>
+      <c r="B354">
+        <v>0.0005374365136958659</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355">
+        <v>353</v>
+      </c>
+      <c r="B355">
+        <v>0.001013822737149894</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356">
+        <v>354</v>
+      </c>
+      <c r="B356">
+        <v>0.000819082953967154</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357">
+        <v>355</v>
+      </c>
+      <c r="B357">
+        <v>0.0006704757106490433</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358">
+        <v>356</v>
+      </c>
+      <c r="B358">
+        <v>0.0002990729990415275</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359">
+        <v>357</v>
+      </c>
+      <c r="B359">
+        <v>0.0001358165463898331</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360">
+        <v>358</v>
+      </c>
+      <c r="B360">
+        <v>0.0005428140284493566</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361">
+        <v>359</v>
+      </c>
+      <c r="B361">
+        <v>3.043960987270111E-06</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362">
+        <v>360</v>
+      </c>
+      <c r="B362">
+        <v>0.0001287815539399162</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363">
+        <v>361</v>
+      </c>
+      <c r="B363">
+        <v>0.002577769802883267</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364">
+        <v>362</v>
+      </c>
+      <c r="B364">
+        <v>-0.0002287082170369104</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365">
+        <v>363</v>
+      </c>
+      <c r="B365">
+        <v>-0.0008577272528782487</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366">
+        <v>364</v>
+      </c>
+      <c r="B366">
+        <v>0.000949876441154629</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367">
+        <v>365</v>
+      </c>
+      <c r="B367">
+        <v>0.001017743139527738</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368">
+        <v>366</v>
+      </c>
+      <c r="B368">
+        <v>0.0003887451603077352</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369">
+        <v>367</v>
+      </c>
+      <c r="B369">
+        <v>0.0008856042404659092</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370">
+        <v>368</v>
+      </c>
+      <c r="B370">
+        <v>0.0001623856369405985</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371">
+        <v>369</v>
+      </c>
+      <c r="B371">
+        <v>8.362517110072076E-05</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372">
+        <v>370</v>
+      </c>
+      <c r="B372">
+        <v>0.0006200836505740881</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373">
+        <v>371</v>
+      </c>
+      <c r="B373">
+        <v>0.0005133325466886163</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374">
+        <v>372</v>
+      </c>
+      <c r="B374">
+        <v>0.0005389777361415327</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375">
+        <v>373</v>
+      </c>
+      <c r="B375">
+        <v>0.0002680618781596422</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376">
+        <v>374</v>
+      </c>
+      <c r="B376">
+        <v>0.001554021378979087</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377">
+        <v>375</v>
+      </c>
+      <c r="B377">
+        <v>0.003501316299661994</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378">
+        <v>376</v>
+      </c>
+      <c r="B378">
+        <v>0.0001134952108259313</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379">
+        <v>377</v>
+      </c>
+      <c r="B379">
+        <v>-3.127050877083093E-05</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380">
+        <v>378</v>
+      </c>
+      <c r="B380">
+        <v>0.0004604030691552907</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381">
+        <v>379</v>
+      </c>
+      <c r="B381">
+        <v>0.0002895830548368394</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382">
+        <v>380</v>
+      </c>
+      <c r="B382">
+        <v>0.0007658017566427588</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383">
+        <v>381</v>
+      </c>
+      <c r="B383">
+        <v>0.0001412541168974712</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384">
+        <v>382</v>
+      </c>
+      <c r="B384">
+        <v>0.0006649221759289503</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385">
+        <v>383</v>
+      </c>
+      <c r="B385">
+        <v>0.0004873100260738283</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386">
+        <v>384</v>
+      </c>
+      <c r="B386">
+        <v>0.0008434266783297062</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387">
+        <v>385</v>
+      </c>
+      <c r="B387">
+        <v>0.001417496474459767</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388">
+        <v>386</v>
+      </c>
+      <c r="B388">
+        <v>0.00174104783218354</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389">
+        <v>387</v>
+      </c>
+      <c r="B389">
+        <v>0.001388635952025652</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390">
+        <v>388</v>
+      </c>
+      <c r="B390">
+        <v>0.0008195338887162507</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391">
+        <v>389</v>
+      </c>
+      <c r="B391">
+        <v>0.0009476449340581894</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392">
+        <v>390</v>
+      </c>
+      <c r="B392">
+        <v>0.0007769923540763557</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393">
+        <v>391</v>
+      </c>
+      <c r="B393">
+        <v>0.001257755444385111</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394">
+        <v>392</v>
+      </c>
+      <c r="B394">
+        <v>0.001224564854055643</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395">
+        <v>393</v>
+      </c>
+      <c r="B395">
+        <v>0.0002997315605171025</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396">
+        <v>394</v>
+      </c>
+      <c r="B396">
+        <v>0.000478954054415226</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397">
+        <v>395</v>
+      </c>
+      <c r="B397">
+        <v>0.0003011943481396884</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398">
+        <v>396</v>
+      </c>
+      <c r="B398">
+        <v>0.0002405741834081709</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399">
+        <v>397</v>
+      </c>
+      <c r="B399">
+        <v>5.512340067070909E-05</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400">
+        <v>398</v>
+      </c>
+      <c r="B400">
+        <v>-1.050735022545268E-06</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401">
+        <v>399</v>
+      </c>
+      <c r="B401">
+        <v>0.0003606860409490764</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402">
+        <v>400</v>
+      </c>
+      <c r="B402">
+        <v>5.132176283950685E-06</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403">
+        <v>401</v>
+      </c>
+      <c r="B403">
+        <v>0.0005756074679084122</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404">
+        <v>402</v>
+      </c>
+      <c r="B404">
+        <v>0.00130396313033998</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405">
+        <v>403</v>
+      </c>
+      <c r="B405">
+        <v>0.0006610978161916137</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406">
+        <v>404</v>
+      </c>
+      <c r="B406">
+        <v>-0.0001876833848655224</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407">
+        <v>405</v>
+      </c>
+      <c r="B407">
+        <v>0.001984934788197279</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408">
+        <v>406</v>
+      </c>
+      <c r="B408">
+        <v>0.001715175108984113</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409">
+        <v>407</v>
+      </c>
+      <c r="B409">
+        <v>-0.0001255155220860615</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410">
+        <v>408</v>
+      </c>
+      <c r="B410">
+        <v>0.000293463934212923</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411">
+        <v>409</v>
+      </c>
+      <c r="B411">
+        <v>0.0001514870527898893</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412">
+        <v>410</v>
+      </c>
+      <c r="B412">
+        <v>0.00194340234156698</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413">
+        <v>411</v>
+      </c>
+      <c r="B413">
+        <v>0.0003995899460278451</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414">
+        <v>412</v>
+      </c>
+      <c r="B414">
+        <v>-0.0003165457164868712</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415">
+        <v>413</v>
+      </c>
+      <c r="B415">
+        <v>-0.0003768099413719028</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416">
+        <v>414</v>
+      </c>
+      <c r="B416">
+        <v>0.0005224678898230195</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417">
+        <v>415</v>
+      </c>
+      <c r="B417">
+        <v>0.000518011802341789</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418">
+        <v>416</v>
+      </c>
+      <c r="B418">
+        <v>0.0007325517362914979</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419">
+        <v>417</v>
+      </c>
+      <c r="B419">
+        <v>0.0009177827159874141</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420">
+        <v>418</v>
+      </c>
+      <c r="B420">
+        <v>0.0006403903826139867</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421">
+        <v>419</v>
+      </c>
+      <c r="B421">
+        <v>0.0003538698656484485</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422">
+        <v>420</v>
+      </c>
+      <c r="B422">
+        <v>0.001441286527551711</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423">
+        <v>421</v>
+      </c>
+      <c r="B423">
+        <v>7.745688344584778E-05</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424">
+        <v>422</v>
+      </c>
+      <c r="B424">
+        <v>0.0009186648530885577</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425">
+        <v>423</v>
+      </c>
+      <c r="B425">
+        <v>0.0002488549507688731</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426">
+        <v>424</v>
+      </c>
+      <c r="B426">
+        <v>0.001527695916593075</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427">
+        <v>425</v>
+      </c>
+      <c r="B427">
+        <v>-0.0002553601516410708</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428">
+        <v>426</v>
+      </c>
+      <c r="B428">
+        <v>0.00180666265077889</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429">
+        <v>427</v>
+      </c>
+      <c r="B429">
+        <v>0.000922994629945606</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430">
+        <v>428</v>
+      </c>
+      <c r="B430">
+        <v>0.00112049316521734</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431">
+        <v>429</v>
+      </c>
+      <c r="B431">
+        <v>-3.046258279937319E-05</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432">
+        <v>430</v>
+      </c>
+      <c r="B432">
+        <v>0.0006620671483688056</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433">
+        <v>431</v>
+      </c>
+      <c r="B433">
+        <v>0.0004872440767940134</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434">
+        <v>432</v>
+      </c>
+      <c r="B434">
+        <v>0.001252535497769713</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435">
+        <v>433</v>
+      </c>
+      <c r="B435">
+        <v>0.000799201603513211</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436">
+        <v>434</v>
+      </c>
+      <c r="B436">
+        <v>0.0005824063555337489</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437">
+        <v>435</v>
+      </c>
+      <c r="B437">
+        <v>0.0009260457009077072</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438">
+        <v>436</v>
+      </c>
+      <c r="B438">
+        <v>0.002217777539044619</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439">
+        <v>437</v>
+      </c>
+      <c r="B439">
+        <v>0.0001182437263196334</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440">
+        <v>438</v>
+      </c>
+      <c r="B440">
+        <v>0.001893615582957864</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441">
+        <v>439</v>
+      </c>
+      <c r="B441">
+        <v>0.003493649186566472</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442">
+        <v>440</v>
+      </c>
+      <c r="B442">
+        <v>0.000227881595492363</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443">
+        <v>441</v>
+      </c>
+      <c r="B443">
+        <v>0.0006199812632985413</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444">
+        <v>442</v>
+      </c>
+      <c r="B444">
+        <v>0.0004827828088309616</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445">
+        <v>443</v>
+      </c>
+      <c r="B445">
+        <v>0.0006911450764164329</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446">
+        <v>444</v>
+      </c>
+      <c r="B446">
+        <v>0.0002738847979344428</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447">
+        <v>445</v>
+      </c>
+      <c r="B447">
+        <v>0.0003242844832129776</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448">
+        <v>446</v>
+      </c>
+      <c r="B448">
+        <v>0.0003021519805770367</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449">
+        <v>447</v>
+      </c>
+      <c r="B449">
+        <v>0.0007331825327128172</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450">
+        <v>448</v>
+      </c>
+      <c r="B450">
+        <v>0.0006133922142907977</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451">
+        <v>449</v>
+      </c>
+      <c r="B451">
+        <v>-0.0004640931438189</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452">
+        <v>450</v>
+      </c>
+      <c r="B452">
+        <v>1.956299638550263E-05</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453">
+        <v>451</v>
+      </c>
+      <c r="B453">
+        <v>0.0005546734319068491</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454">
+        <v>452</v>
+      </c>
+      <c r="B454">
+        <v>-0.001235418720170856</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455">
+        <v>453</v>
+      </c>
+      <c r="B455">
+        <v>-0.0003438142011873424</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456">
+        <v>454</v>
+      </c>
+      <c r="B456">
+        <v>0.0004354452539701015</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457">
+        <v>455</v>
+      </c>
+      <c r="B457">
+        <v>0.0006806019227951765</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458">
+        <v>456</v>
+      </c>
+      <c r="B458">
+        <v>0.0008005759445950389</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459">
+        <v>457</v>
+      </c>
+      <c r="B459">
+        <v>0.0008629330550320446</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460">
+        <v>458</v>
+      </c>
+      <c r="B460">
+        <v>0.0001754110853653401</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461">
+        <v>459</v>
+      </c>
+      <c r="B461">
+        <v>0.001134194084443152</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462">
+        <v>460</v>
+      </c>
+      <c r="B462">
+        <v>0.0002448530285619199</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463">
+        <v>461</v>
+      </c>
+      <c r="B463">
+        <v>0.002007332630455494</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464">
+        <v>462</v>
+      </c>
+      <c r="B464">
+        <v>0.000252152734901756</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465">
+        <v>463</v>
+      </c>
+      <c r="B465">
+        <v>-0.0001078559143934399</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466">
+        <v>464</v>
+      </c>
+      <c r="B466">
+        <v>0.001228222041390836</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467">
+        <v>465</v>
+      </c>
+      <c r="B467">
+        <v>0.0008520713308826089</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468">
+        <v>466</v>
+      </c>
+      <c r="B468">
+        <v>0.001410776516422629</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469">
+        <v>467</v>
+      </c>
+      <c r="B469">
+        <v>0.0005831438465975225</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470">
+        <v>468</v>
+      </c>
+      <c r="B470">
+        <v>0.001524867373518646</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471">
+        <v>469</v>
+      </c>
+      <c r="B471">
+        <v>0.000505540578160435</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472">
+        <v>470</v>
+      </c>
+      <c r="B472">
+        <v>0.0004046269750688225</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473">
+        <v>471</v>
+      </c>
+      <c r="B473">
+        <v>0.0005464342539198697</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474">
+        <v>472</v>
+      </c>
+      <c r="B474">
+        <v>0.0001130693199229427</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475">
+        <v>473</v>
+      </c>
+      <c r="B475">
+        <v>0.0003465382324066013</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476">
+        <v>474</v>
+      </c>
+      <c r="B476">
+        <v>0.0002274396101711318</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477">
+        <v>475</v>
+      </c>
+      <c r="B477">
+        <v>0.0003872479137498885</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478">
+        <v>476</v>
+      </c>
+      <c r="B478">
+        <v>0.001467995694838464</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479">
+        <v>477</v>
+      </c>
+      <c r="B479">
+        <v>0.0007743081660009921</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480">
+        <v>478</v>
+      </c>
+      <c r="B480">
+        <v>0.006223574746400118</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481">
+        <v>479</v>
+      </c>
+      <c r="B481">
+        <v>0.00104871264193207</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482">
+        <v>480</v>
+      </c>
+      <c r="B482">
+        <v>0.0002657411678228527</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2">
+      <c r="A483">
+        <v>481</v>
+      </c>
+      <c r="B483">
+        <v>0.000992158311419189</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484">
+        <v>482</v>
+      </c>
+      <c r="B484">
+        <v>0.0004114954208489507</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485">
+        <v>483</v>
+      </c>
+      <c r="B485">
+        <v>0.0006075026467442513</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486">
+        <v>484</v>
+      </c>
+      <c r="B486">
+        <v>-8.924693975131959E-05</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2">
+      <c r="A487">
+        <v>485</v>
+      </c>
+      <c r="B487">
+        <v>0.0002978396660182625</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2">
+      <c r="A488">
+        <v>486</v>
+      </c>
+      <c r="B488">
+        <v>0.0001096655687433667</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2">
+      <c r="A489">
+        <v>487</v>
+      </c>
+      <c r="B489">
+        <v>0.00154343678150326</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490">
+        <v>488</v>
+      </c>
+      <c r="B490">
+        <v>0.0005336666945368052</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2">
+      <c r="A491">
+        <v>489</v>
+      </c>
+      <c r="B491">
+        <v>0.0004230094491504133</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2">
+      <c r="A492">
+        <v>490</v>
+      </c>
+      <c r="B492">
+        <v>0.0005439668311737478</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2">
+      <c r="A493">
+        <v>491</v>
+      </c>
+      <c r="B493">
+        <v>0.00142307358328253</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2">
+      <c r="A494">
+        <v>492</v>
+      </c>
+      <c r="B494">
+        <v>0.0009200748172588646</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2">
+      <c r="A495">
+        <v>493</v>
+      </c>
+      <c r="B495">
+        <v>0.0008632269455119967</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2">
+      <c r="A496">
+        <v>494</v>
+      </c>
+      <c r="B496">
+        <v>0.0007919698255136609</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2">
+      <c r="A497">
+        <v>495</v>
+      </c>
+      <c r="B497">
+        <v>0.0006930443341843784</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2">
+      <c r="A498">
+        <v>496</v>
+      </c>
+      <c r="B498">
+        <v>0.0003392111102584749</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2">
+      <c r="A499">
+        <v>497</v>
+      </c>
+      <c r="B499">
+        <v>0.0001997090148506686</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2">
+      <c r="A500">
+        <v>498</v>
+      </c>
+      <c r="B500">
+        <v>0.000535108323674649</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2">
+      <c r="A501">
+        <v>499</v>
+      </c>
+      <c r="B501">
+        <v>0.0005339715862646699</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2">
+      <c r="A502">
+        <v>500</v>
+      </c>
+      <c r="B502">
+        <v>0.0007220310508273542</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2">
+      <c r="A503">
+        <v>501</v>
+      </c>
+      <c r="B503">
+        <v>0.0006616620230488479</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2">
+      <c r="A504">
+        <v>502</v>
+      </c>
+      <c r="B504">
+        <v>0.001389005687087774</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2">
+      <c r="A505">
+        <v>503</v>
+      </c>
+      <c r="B505">
+        <v>0.001430086325854063</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2">
+      <c r="A506">
+        <v>504</v>
+      </c>
+      <c r="B506">
+        <v>-0.0006273694452829659</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2">
+      <c r="A507">
+        <v>505</v>
+      </c>
+      <c r="B507">
+        <v>0.001391828758642077</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2">
+      <c r="A508">
+        <v>506</v>
+      </c>
+      <c r="B508">
+        <v>0.0009194243466481566</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2">
+      <c r="A509">
+        <v>507</v>
+      </c>
+      <c r="B509">
+        <v>0.0005234144628047943</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2">
+      <c r="A510">
+        <v>508</v>
+      </c>
+      <c r="B510">
+        <v>0.001090740785002708</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2">
+      <c r="A511">
+        <v>509</v>
+      </c>
+      <c r="B511">
+        <v>7.346242637140676E-05</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2">
+      <c r="A512">
+        <v>510</v>
+      </c>
+      <c r="B512">
+        <v>0.0004048136179335415</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2">
+      <c r="A513">
+        <v>511</v>
+      </c>
+      <c r="B513">
+        <v>0.0005594568210653961</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2">
+      <c r="A514">
+        <v>512</v>
+      </c>
+      <c r="B514">
+        <v>0.0002867328294087201</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2">
+      <c r="A515">
+        <v>513</v>
+      </c>
+      <c r="B515">
+        <v>4.460391210159287E-05</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2">
+      <c r="A516">
+        <v>514</v>
+      </c>
+      <c r="B516">
+        <v>-2.711616980377585E-05</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517">
+        <v>515</v>
+      </c>
+      <c r="B517">
+        <v>-3.834819654002786E-05</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518">
+        <v>516</v>
+      </c>
+      <c r="B518">
+        <v>0.001098648528568447</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="A519">
+        <v>517</v>
+      </c>
+      <c r="B519">
+        <v>0.001705598318949342</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="A520">
+        <v>518</v>
+      </c>
+      <c r="B520">
+        <v>0.0006783976568840444</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="A521">
+        <v>519</v>
+      </c>
+      <c r="B521">
+        <v>0.0001906457328004763</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522">
+        <v>520</v>
+      </c>
+      <c r="B522">
+        <v>0.0006598684703931212</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2">
+      <c r="A523">
+        <v>521</v>
+      </c>
+      <c r="B523">
+        <v>0.0003733141347765923</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="A524">
+        <v>522</v>
+      </c>
+      <c r="B524">
+        <v>0.001119960215874016</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525">
+        <v>523</v>
+      </c>
+      <c r="B525">
+        <v>0.001283011399209499</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526">
+        <v>524</v>
+      </c>
+      <c r="B526">
+        <v>0.0007175461505539715</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2">
+      <c r="A527">
+        <v>525</v>
+      </c>
+      <c r="B527">
+        <v>0.001467557973228395</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2">
+      <c r="A528">
+        <v>526</v>
+      </c>
+      <c r="B528">
+        <v>0.0001809342647902668</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529">
+        <v>527</v>
+      </c>
+      <c r="B529">
+        <v>7.403557538054883E-05</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530">
+        <v>528</v>
+      </c>
+      <c r="B530">
+        <v>0.0005908833118155599</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531">
+        <v>529</v>
+      </c>
+      <c r="B531">
+        <v>0.0005712761776521802</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532">
+        <v>530</v>
+      </c>
+      <c r="B532">
+        <v>0.0005625622579827905</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533">
+        <v>531</v>
+      </c>
+      <c r="B533">
+        <v>0.0004179799288976938</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534">
+        <v>532</v>
+      </c>
+      <c r="B534">
+        <v>0.0007116912165656686</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535">
+        <v>533</v>
+      </c>
+      <c r="B535">
+        <v>0.000635929056443274</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536">
+        <v>534</v>
+      </c>
+      <c r="B536">
+        <v>8.463058293273207E-06</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537">
+        <v>535</v>
+      </c>
+      <c r="B537">
+        <v>0.001431121490895748</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538">
+        <v>536</v>
+      </c>
+      <c r="B538">
+        <v>0.00079551269300282</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539">
+        <v>537</v>
+      </c>
+      <c r="B539">
+        <v>0.003234746167436242</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540">
+        <v>538</v>
+      </c>
+      <c r="B540">
+        <v>0.0001373867125948891</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541">
+        <v>539</v>
+      </c>
+      <c r="B541">
+        <v>0.0004717021365649998</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542">
+        <v>540</v>
+      </c>
+      <c r="B542">
+        <v>0.0005684276111423969</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543">
+        <v>541</v>
+      </c>
+      <c r="B543">
+        <v>0.0003489309165161103</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544">
+        <v>542</v>
+      </c>
+      <c r="B544">
+        <v>0.0005695851286873221</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545">
+        <v>543</v>
+      </c>
+      <c r="B545">
+        <v>0.0001093385508283973</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="A546">
+        <v>544</v>
+      </c>
+      <c r="B546">
+        <v>0.0008864328265190125</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="A547">
+        <v>545</v>
+      </c>
+      <c r="B547">
+        <v>0.0004185588622931391</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="A548">
+        <v>546</v>
+      </c>
+      <c r="B548">
+        <v>0.001064643263816833</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="A549">
+        <v>547</v>
+      </c>
+      <c r="B549">
+        <v>0.0007063979282975197</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="A550">
+        <v>548</v>
+      </c>
+      <c r="B550">
+        <v>0.000784055155236274</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="A551">
+        <v>549</v>
+      </c>
+      <c r="B551">
+        <v>0.00066946487640962</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="A552">
+        <v>550</v>
+      </c>
+      <c r="B552">
+        <v>0.001717678504064679</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="A553">
+        <v>551</v>
+      </c>
+      <c r="B553">
+        <v>0.001498268567956984</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554">
+        <v>552</v>
+      </c>
+      <c r="B554">
+        <v>0.0005259577883407474</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555">
+        <v>553</v>
+      </c>
+      <c r="B555">
+        <v>0.0007136861677281559</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556">
+        <v>554</v>
+      </c>
+      <c r="B556">
+        <v>0.0008821257506497204</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557">
+        <v>555</v>
+      </c>
+      <c r="B557">
+        <v>0.0008019954548217356</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558">
+        <v>556</v>
+      </c>
+      <c r="B558">
+        <v>0.001106858602724969</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559">
+        <v>557</v>
+      </c>
+      <c r="B559">
+        <v>0.001370351877994835</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560">
+        <v>558</v>
+      </c>
+      <c r="B560">
+        <v>0.001111499150283635</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561">
+        <v>559</v>
+      </c>
+      <c r="B561">
+        <v>0.00195368705317378</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562">
+        <v>560</v>
+      </c>
+      <c r="B562">
+        <v>0.0009740118985064328</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563">
+        <v>561</v>
+      </c>
+      <c r="B563">
+        <v>5.67055176361464E-05</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564">
+        <v>562</v>
+      </c>
+      <c r="B564">
+        <v>0.0008016905630938709</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565">
+        <v>563</v>
+      </c>
+      <c r="B565">
+        <v>-0.002610297640785575</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566">
+        <v>564</v>
+      </c>
+      <c r="B566">
+        <v>0.001133414683863521</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567">
+        <v>565</v>
+      </c>
+      <c r="B567">
+        <v>-0.0003024472389370203</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568">
+        <v>566</v>
+      </c>
+      <c r="B568">
+        <v>0.0004664474399760365</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2">
+      <c r="A569">
+        <v>567</v>
+      </c>
+      <c r="B569">
+        <v>0.000480338407214731</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570">
+        <v>568</v>
+      </c>
+      <c r="B570">
+        <v>0.0003609615087043494</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571">
+        <v>569</v>
+      </c>
+      <c r="B571">
+        <v>-0.0007416970329359174</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2">
+      <c r="A572">
+        <v>570</v>
+      </c>
+      <c r="B572">
+        <v>0.0007474964950233698</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2">
+      <c r="A573">
+        <v>571</v>
+      </c>
+      <c r="B573">
+        <v>0.0006797881214879453</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2">
+      <c r="A574">
+        <v>572</v>
+      </c>
+      <c r="B574">
+        <v>0.001054050051607192</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2">
+      <c r="A575">
+        <v>573</v>
+      </c>
+      <c r="B575">
+        <v>0.002313025295734406</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2">
+      <c r="A576">
+        <v>574</v>
+      </c>
+      <c r="B576">
+        <v>0.0007410760736092925</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2">
+      <c r="A577">
+        <v>575</v>
+      </c>
+      <c r="B577">
+        <v>0.0001554172486066818</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2">
+      <c r="A578">
+        <v>576</v>
+      </c>
+      <c r="B578">
+        <v>-4.770422037836397E-06</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2">
+      <c r="A579">
+        <v>577</v>
+      </c>
+      <c r="B579">
+        <v>0.0009507086942903697</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2">
+      <c r="A580">
+        <v>578</v>
+      </c>
+      <c r="B580">
+        <v>0.000800424488261342</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2">
+      <c r="A581">
+        <v>579</v>
+      </c>
+      <c r="B581">
+        <v>0.00149536831304431</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2">
+      <c r="A582">
+        <v>580</v>
+      </c>
+      <c r="B582">
+        <v>0.001622808282263577</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2">
+      <c r="A583">
+        <v>581</v>
+      </c>
+      <c r="B583">
+        <v>0.0004662395804189146</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2">
+      <c r="A584">
+        <v>582</v>
+      </c>
+      <c r="B584">
+        <v>0.000648333749268204</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2">
+      <c r="A585">
+        <v>583</v>
+      </c>
+      <c r="B585">
+        <v>0.0003396848915144801</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2">
+      <c r="A586">
+        <v>584</v>
+      </c>
+      <c r="B586">
+        <v>0.0004579983069561422</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2">
+      <c r="A587">
+        <v>585</v>
+      </c>
+      <c r="B587">
+        <v>0.0001541606761747971</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2">
+      <c r="A588">
+        <v>586</v>
+      </c>
+      <c r="B588">
+        <v>-0.0001511669397586957</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2">
+      <c r="A589">
+        <v>587</v>
+      </c>
+      <c r="B589">
+        <v>0.0003502400359138846</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2">
+      <c r="A590">
+        <v>588</v>
+      </c>
+      <c r="B590">
+        <v>0.0003145967202726752</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2">
+      <c r="A591">
+        <v>589</v>
+      </c>
+      <c r="B591">
+        <v>0.00224041985347867</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2">
+      <c r="A592">
+        <v>590</v>
+      </c>
+      <c r="B592">
+        <v>0.0004672204959206283</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2">
+      <c r="A593">
+        <v>591</v>
+      </c>
+      <c r="B593">
+        <v>0.001128745847381651</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2">
+      <c r="A594">
+        <v>592</v>
+      </c>
+      <c r="B594">
+        <v>0.0004722673620563</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2">
+      <c r="A595">
+        <v>593</v>
+      </c>
+      <c r="B595">
+        <v>0.0007112906314432621</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2">
+      <c r="A596">
+        <v>594</v>
+      </c>
+      <c r="B596">
+        <v>0.0005546239553950727</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2">
+      <c r="A597">
+        <v>595</v>
+      </c>
+      <c r="B597">
+        <v>0.0006664651446044445</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2">
+      <c r="A598">
+        <v>596</v>
+      </c>
+      <c r="B598">
+        <v>0.0005379565409384668</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2">
+      <c r="A599">
+        <v>597</v>
+      </c>
+      <c r="B599">
+        <v>-0.0001106445852201432</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2">
+      <c r="A600">
+        <v>598</v>
+      </c>
+      <c r="B600">
+        <v>0.0006114906864240766</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2">
+      <c r="A601">
+        <v>599</v>
+      </c>
+      <c r="B601">
+        <v>0.001623652875423431</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2">
+      <c r="A602">
+        <v>600</v>
+      </c>
+      <c r="B602">
+        <v>0.002376045798882842</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2">
+      <c r="A603">
+        <v>601</v>
+      </c>
+      <c r="B603">
+        <v>0.001905685989186168</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2">
+      <c r="A604">
+        <v>602</v>
+      </c>
+      <c r="B604">
+        <v>0.009197269566357136</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2">
+      <c r="A605">
+        <v>603</v>
+      </c>
+      <c r="B605">
+        <v>0.001239445642568171</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2">
+      <c r="A606">
+        <v>604</v>
+      </c>
+      <c r="B606">
+        <v>-0.0003617238835431635</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2">
+      <c r="A607">
+        <v>605</v>
+      </c>
+      <c r="B607">
+        <v>0.00157943821977824</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2">
+      <c r="A608">
+        <v>606</v>
+      </c>
+      <c r="B608">
+        <v>0.00190709694288671</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2">
+      <c r="A609">
+        <v>607</v>
+      </c>
+      <c r="B609">
+        <v>0.000366486405255273</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2">
+      <c r="A610">
+        <v>608</v>
+      </c>
+      <c r="B610">
+        <v>0.0002760671195574105</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2">
+      <c r="A611">
+        <v>609</v>
+      </c>
+      <c r="B611">
+        <v>0.0003382190770935267</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2">
+      <c r="A612">
+        <v>610</v>
+      </c>
+      <c r="B612">
+        <v>0.0002634749689605087</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2">
+      <c r="A613">
+        <v>611</v>
+      </c>
+      <c r="B613">
+        <v>0.0008584464085288346</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2">
+      <c r="A614">
+        <v>612</v>
+      </c>
+      <c r="B614">
+        <v>8.714242721907794E-05</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2">
+      <c r="A615">
+        <v>613</v>
+      </c>
+      <c r="B615">
+        <v>0.0008856499916873872</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2">
+      <c r="A616">
+        <v>614</v>
+      </c>
+      <c r="B616">
+        <v>0.0007307230844162405</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2">
+      <c r="A617">
+        <v>615</v>
+      </c>
+      <c r="B617">
+        <v>-4.040624844492413E-05</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2">
+      <c r="A618">
+        <v>616</v>
+      </c>
+      <c r="B618">
+        <v>0.0008800218347460032</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2">
+      <c r="A619">
+        <v>617</v>
+      </c>
+      <c r="B619">
+        <v>3.408832344575785E-05</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2">
+      <c r="A620">
+        <v>618</v>
+      </c>
+      <c r="B620">
+        <v>0.0002121101570082828</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2">
+      <c r="A621">
+        <v>619</v>
+      </c>
+      <c r="B621">
+        <v>0.002166753401979804</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2">
+      <c r="A622">
+        <v>620</v>
+      </c>
+      <c r="B622">
+        <v>0.0003396563406568021</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2">
+      <c r="A623">
+        <v>621</v>
+      </c>
+      <c r="B623">
+        <v>0.0009691482409834862</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2">
+      <c r="A624">
+        <v>622</v>
+      </c>
+      <c r="B624">
+        <v>0.000503363786265254</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2">
+      <c r="A625">
+        <v>623</v>
+      </c>
+      <c r="B625">
+        <v>0.0007939793285913765</v>
+      </c>
+    </row>
+    <row r="626" spans="1:2">
+      <c r="A626">
+        <v>624</v>
+      </c>
+      <c r="B626">
+        <v>0.0006861888105049729</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2">
+      <c r="A627">
+        <v>625</v>
+      </c>
+      <c r="B627">
+        <v>0.0003928471123799682</v>
+      </c>
+    </row>
+    <row r="628" spans="1:2">
+      <c r="A628">
+        <v>626</v>
+      </c>
+      <c r="B628">
+        <v>0.0009980464819818735</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2">
+      <c r="A629">
+        <v>627</v>
+      </c>
+      <c r="B629">
+        <v>0.0005089436890557408</v>
+      </c>
+    </row>
+    <row r="630" spans="1:2">
+      <c r="A630">
+        <v>628</v>
+      </c>
+      <c r="B630">
+        <v>-0.005527419969439507</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2">
+      <c r="A631">
+        <v>629</v>
+      </c>
+      <c r="B631">
+        <v>0.0005760985659435391</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2">
+      <c r="A632">
+        <v>630</v>
+      </c>
+      <c r="B632">
+        <v>0.001165529945865273</v>
+      </c>
+    </row>
+    <row r="633" spans="1:2">
+      <c r="A633">
+        <v>631</v>
+      </c>
+      <c r="B633">
+        <v>0.0004783025360666215</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2">
+      <c r="A634">
+        <v>632</v>
+      </c>
+      <c r="B634">
+        <v>0.00128779630176723</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2">
+      <c r="A635">
+        <v>633</v>
+      </c>
+      <c r="B635">
+        <v>0.0005524986772798002</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2">
+      <c r="A636">
+        <v>634</v>
+      </c>
+      <c r="B636">
+        <v>0.0002123795420629904</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2">
+      <c r="A637">
+        <v>635</v>
+      </c>
+      <c r="B637">
+        <v>0.0005630829255096614</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2">
+      <c r="A638">
+        <v>636</v>
+      </c>
+      <c r="B638">
+        <v>0.000493742641992867</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2">
+      <c r="A639">
+        <v>637</v>
+      </c>
+      <c r="B639">
+        <v>0.0004627082089427859</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2">
+      <c r="A640">
+        <v>638</v>
+      </c>
+      <c r="B640">
+        <v>0.001220121863298118</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2">
+      <c r="A641">
+        <v>639</v>
+      </c>
+      <c r="B641">
+        <v>0.00190881488379091</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2">
+      <c r="A642">
+        <v>640</v>
+      </c>
+      <c r="B642">
+        <v>0.0004851618723478168</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2">
+      <c r="A643">
+        <v>641</v>
+      </c>
+      <c r="B643">
+        <v>4.349453956820071E-05</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2">
+      <c r="A644">
+        <v>642</v>
+      </c>
+      <c r="B644">
+        <v>0.0003177463368047029</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2">
+      <c r="A645">
+        <v>643</v>
+      </c>
+      <c r="B645">
+        <v>0.001369058387354016</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2">
+      <c r="A646">
+        <v>644</v>
+      </c>
+      <c r="B646">
+        <v>0.0007735503022558987</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2">
+      <c r="A647">
+        <v>645</v>
+      </c>
+      <c r="B647">
+        <v>-6.406033207895234E-05</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2">
+      <c r="A648">
+        <v>646</v>
+      </c>
+      <c r="B648">
+        <v>0.0009189457050524652</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2">
+      <c r="A649">
+        <v>647</v>
+      </c>
+      <c r="B649">
+        <v>-0.0006378627149388194</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2">
+      <c r="A650">
+        <v>648</v>
+      </c>
+      <c r="B650">
+        <v>0.001051951898261905</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2">
+      <c r="A651">
+        <v>649</v>
+      </c>
+      <c r="B651">
+        <v>0.0001854016300057992</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2">
+      <c r="A652">
+        <v>650</v>
+      </c>
+      <c r="B652">
+        <v>0.0003131220582872629</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2">
+      <c r="A653">
+        <v>651</v>
+      </c>
+      <c r="B653">
+        <v>0.0002516653330530971</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2">
+      <c r="A654">
+        <v>652</v>
+      </c>
+      <c r="B654">
+        <v>0.001057810848578811</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2">
+      <c r="A655">
+        <v>653</v>
+      </c>
+      <c r="B655">
+        <v>-0.001263821846805513</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2">
+      <c r="A656">
+        <v>654</v>
+      </c>
+      <c r="B656">
+        <v>-0.001976236933842301</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2">
+      <c r="A657">
+        <v>655</v>
+      </c>
+      <c r="B657">
+        <v>-0.0007729507051408291</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2">
+      <c r="A658">
+        <v>656</v>
+      </c>
+      <c r="B658">
+        <v>0.0008705734508112073</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2">
+      <c r="A659">
+        <v>657</v>
+      </c>
+      <c r="B659">
+        <v>0.0003489619994070381</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2">
+      <c r="A660">
+        <v>658</v>
+      </c>
+      <c r="B660">
+        <v>-0.0002806693955790251</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2">
+      <c r="A661">
+        <v>659</v>
+      </c>
+      <c r="B661">
+        <v>0.004450162872672081</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2">
+      <c r="A662">
+        <v>660</v>
+      </c>
+      <c r="B662">
+        <v>0.0006137159653007984</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2">
+      <c r="A663">
+        <v>661</v>
+      </c>
+      <c r="B663">
+        <v>0.0003174337325617671</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2">
+      <c r="A664">
+        <v>662</v>
+      </c>
+      <c r="B664">
+        <v>0.0006730026798322797</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2">
+      <c r="A665">
+        <v>663</v>
+      </c>
+      <c r="B665">
+        <v>0.001661989954300225</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2">
+      <c r="A666">
+        <v>664</v>
+      </c>
+      <c r="B666">
+        <v>0.0008309926488436759</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2">
+      <c r="A667">
+        <v>665</v>
+      </c>
+      <c r="B667">
+        <v>0.0009032892994582653</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2">
+      <c r="A668">
+        <v>666</v>
+      </c>
+      <c r="B668">
+        <v>0.002707500476390123</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2">
+      <c r="A669">
+        <v>667</v>
+      </c>
+      <c r="B669">
+        <v>-0.005187458358705044</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2">
+      <c r="A670">
+        <v>668</v>
+      </c>
+      <c r="B670">
+        <v>0.0007938688504509628</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2">
+      <c r="A671">
+        <v>669</v>
+      </c>
+      <c r="B671">
+        <v>0.0003764972789213061</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2">
+      <c r="A672">
+        <v>670</v>
+      </c>
+      <c r="B672">
+        <v>0.0003847540647257119</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2">
+      <c r="A673">
+        <v>671</v>
+      </c>
+      <c r="B673">
+        <v>9.639548807172105E-05</v>
+      </c>
+    </row>
+    <row r="674" spans="1:2">
+      <c r="A674">
+        <v>672</v>
+      </c>
+      <c r="B674">
+        <v>0.0005066801095381379</v>
+      </c>
+    </row>
+    <row r="675" spans="1:2">
+      <c r="A675">
+        <v>673</v>
+      </c>
+      <c r="B675">
+        <v>0.0009453534730710089</v>
+      </c>
+    </row>
+    <row r="676" spans="1:2">
+      <c r="A676">
+        <v>674</v>
+      </c>
+      <c r="B676">
+        <v>0.0009175332961603999</v>
+      </c>
+    </row>
+    <row r="677" spans="1:2">
+      <c r="A677">
+        <v>675</v>
+      </c>
+      <c r="B677">
+        <v>0.0006364817963913083</v>
+      </c>
+    </row>
+    <row r="678" spans="1:2">
+      <c r="A678">
+        <v>676</v>
+      </c>
+      <c r="B678">
+        <v>9.587169188307598E-05</v>
+      </c>
+    </row>
+    <row r="679" spans="1:2">
+      <c r="A679">
+        <v>677</v>
+      </c>
+      <c r="B679">
+        <v>0.0003464239998720586</v>
+      </c>
+    </row>
+    <row r="680" spans="1:2">
+      <c r="A680">
+        <v>678</v>
+      </c>
+      <c r="B680">
+        <v>0.0003094801213592291</v>
+      </c>
+    </row>
+    <row r="681" spans="1:2">
+      <c r="A681">
+        <v>679</v>
+      </c>
+      <c r="B681">
+        <v>0.0002925035078078508</v>
+      </c>
+    </row>
+    <row r="682" spans="1:2">
+      <c r="A682">
+        <v>680</v>
+      </c>
+      <c r="B682">
+        <v>0.006839069537818432</v>
+      </c>
+    </row>
+    <row r="683" spans="1:2">
+      <c r="A683">
+        <v>681</v>
+      </c>
+      <c r="B683">
+        <v>0.001207182416692376</v>
+      </c>
+    </row>
+    <row r="684" spans="1:2">
+      <c r="A684">
+        <v>682</v>
+      </c>
+      <c r="B684">
+        <v>-0.001062378636561334</v>
+      </c>
+    </row>
+    <row r="685" spans="1:2">
+      <c r="A685">
+        <v>683</v>
+      </c>
+      <c r="B685">
+        <v>0.0002707154781091958</v>
+      </c>
+    </row>
+    <row r="686" spans="1:2">
+      <c r="A686">
+        <v>684</v>
+      </c>
+      <c r="B686">
+        <v>0.0003160393971484154</v>
+      </c>
+    </row>
+    <row r="687" spans="1:2">
+      <c r="A687">
+        <v>685</v>
+      </c>
+      <c r="B687">
+        <v>0.0006298805237747729</v>
+      </c>
+    </row>
+    <row r="688" spans="1:2">
+      <c r="A688">
+        <v>686</v>
+      </c>
+      <c r="B688">
+        <v>0.0007423669449053705</v>
+      </c>
+    </row>
+    <row r="689" spans="1:2">
+      <c r="A689">
+        <v>687</v>
+      </c>
+      <c r="B689">
+        <v>0.0002547944022808224</v>
+      </c>
+    </row>
+    <row r="690" spans="1:2">
+      <c r="A690">
+        <v>688</v>
+      </c>
+      <c r="B690">
+        <v>0.000414893584093079</v>
+      </c>
+    </row>
+    <row r="691" spans="1:2">
+      <c r="A691">
+        <v>689</v>
+      </c>
+      <c r="B691">
+        <v>0.001771635259501636</v>
+      </c>
+    </row>
+    <row r="692" spans="1:2">
+      <c r="A692">
+        <v>690</v>
+      </c>
+      <c r="B692">
+        <v>-0.0004964088439010084</v>
+      </c>
+    </row>
+    <row r="693" spans="1:2">
+      <c r="A693">
+        <v>691</v>
+      </c>
+      <c r="B693">
+        <v>0.001192706637084484</v>
+      </c>
+    </row>
+    <row r="694" spans="1:2">
+      <c r="A694">
+        <v>692</v>
+      </c>
+      <c r="B694">
+        <v>0.001149274525232613</v>
+      </c>
+    </row>
+    <row r="695" spans="1:2">
+      <c r="A695">
+        <v>693</v>
+      </c>
+      <c r="B695">
+        <v>0.001356306718662381</v>
+      </c>
+    </row>
+    <row r="696" spans="1:2">
+      <c r="A696">
+        <v>694</v>
+      </c>
+      <c r="B696">
+        <v>-0.0001050882565323263</v>
+      </c>
+    </row>
+    <row r="697" spans="1:2">
+      <c r="A697">
+        <v>695</v>
+      </c>
+      <c r="B697">
+        <v>0.0002282373607158661</v>
+      </c>
+    </row>
+    <row r="698" spans="1:2">
+      <c r="A698">
+        <v>696</v>
+      </c>
+      <c r="B698">
+        <v>0.0007315591792576015</v>
+      </c>
+    </row>
+    <row r="699" spans="1:2">
+      <c r="A699">
+        <v>697</v>
+      </c>
+      <c r="B699">
+        <v>-0.0004844831710215658</v>
+      </c>
+    </row>
+    <row r="700" spans="1:2">
+      <c r="A700">
+        <v>698</v>
+      </c>
+      <c r="B700">
+        <v>0.0007410880643874407</v>
+      </c>
+    </row>
+    <row r="701" spans="1:2">
+      <c r="A701">
+        <v>699</v>
+      </c>
+      <c r="B701">
+        <v>-4.708858250523917E-05</v>
+      </c>
+    </row>
+    <row r="702" spans="1:2">
+      <c r="A702">
+        <v>700</v>
+      </c>
+      <c r="B702">
+        <v>-0.0001202441999339499</v>
+      </c>
+    </row>
+    <row r="703" spans="1:2">
+      <c r="A703">
+        <v>701</v>
+      </c>
+      <c r="B703">
+        <v>0.001282822573557496</v>
+      </c>
+    </row>
+    <row r="704" spans="1:2">
+      <c r="A704">
+        <v>702</v>
+      </c>
+      <c r="B704">
+        <v>0.0003027299826499075</v>
+      </c>
+    </row>
+    <row r="705" spans="1:2">
+      <c r="A705">
+        <v>703</v>
+      </c>
+      <c r="B705">
+        <v>0.0006356962257996202</v>
+      </c>
+    </row>
+    <row r="706" spans="1:2">
+      <c r="A706">
+        <v>704</v>
+      </c>
+      <c r="B706">
+        <v>0.0004407722735777497</v>
+      </c>
+    </row>
+    <row r="707" spans="1:2">
+      <c r="A707">
+        <v>705</v>
+      </c>
+      <c r="B707">
+        <v>0.0001841248158598319</v>
+      </c>
+    </row>
+    <row r="708" spans="1:2">
+      <c r="A708">
+        <v>706</v>
+      </c>
+      <c r="B708">
+        <v>-0.001922554452903569</v>
+      </c>
+    </row>
+    <row r="709" spans="1:2">
+      <c r="A709">
+        <v>707</v>
+      </c>
+      <c r="B709">
+        <v>-0.000291887583443895</v>
+      </c>
+    </row>
+    <row r="710" spans="1:2">
+      <c r="A710">
+        <v>708</v>
+      </c>
+      <c r="B710">
+        <v>0.001058311085216701</v>
+      </c>
+    </row>
+    <row r="711" spans="1:2">
+      <c r="A711">
+        <v>709</v>
+      </c>
+      <c r="B711">
+        <v>0.0004489242564886808</v>
+      </c>
+    </row>
+    <row r="712" spans="1:2">
+      <c r="A712">
+        <v>710</v>
+      </c>
+      <c r="B712">
+        <v>-0.0001186742083518766</v>
+      </c>
+    </row>
+    <row r="713" spans="1:2">
+      <c r="A713">
+        <v>711</v>
+      </c>
+      <c r="B713">
+        <v>0.000329782662447542</v>
+      </c>
+    </row>
+    <row r="714" spans="1:2">
+      <c r="A714">
+        <v>712</v>
+      </c>
+      <c r="B714">
+        <v>-1.681829235167243E-05</v>
+      </c>
+    </row>
+    <row r="715" spans="1:2">
+      <c r="A715">
+        <v>713</v>
+      </c>
+      <c r="B715">
+        <v>0.0006153836147859693</v>
+      </c>
+    </row>
+    <row r="716" spans="1:2">
+      <c r="A716">
+        <v>714</v>
+      </c>
+      <c r="B716">
+        <v>0.0005336705362424254</v>
+      </c>
+    </row>
+    <row r="717" spans="1:2">
+      <c r="A717">
+        <v>715</v>
+      </c>
+      <c r="B717">
+        <v>1.000622614810709E-05</v>
+      </c>
+    </row>
+    <row r="718" spans="1:2">
+      <c r="A718">
+        <v>716</v>
+      </c>
+      <c r="B718">
+        <v>0.0002539997512940317</v>
+      </c>
+    </row>
+    <row r="719" spans="1:2">
+      <c r="A719">
+        <v>717</v>
+      </c>
+      <c r="B719">
+        <v>0.000289002520730719</v>
+      </c>
+    </row>
+    <row r="720" spans="1:2">
+      <c r="A720">
+        <v>718</v>
+      </c>
+      <c r="B720">
+        <v>-7.869082037359476E-05</v>
+      </c>
+    </row>
+    <row r="721" spans="1:2">
+      <c r="A721">
+        <v>719</v>
+      </c>
+      <c r="B721">
+        <v>0.006050015334039927</v>
+      </c>
+    </row>
+    <row r="722" spans="1:2">
+      <c r="A722">
+        <v>720</v>
+      </c>
+      <c r="B722">
+        <v>3.445004404056817E-05</v>
+      </c>
+    </row>
+    <row r="723" spans="1:2">
+      <c r="A723">
+        <v>721</v>
+      </c>
+      <c r="B723">
+        <v>0.0002566078037489206</v>
+      </c>
+    </row>
+    <row r="724" spans="1:2">
+      <c r="A724">
+        <v>722</v>
+      </c>
+      <c r="B724">
+        <v>0.0006702404352836311</v>
+      </c>
+    </row>
+    <row r="725" spans="1:2">
+      <c r="A725">
+        <v>723</v>
+      </c>
+      <c r="B725">
+        <v>0.0006936992285773158</v>
+      </c>
+    </row>
+    <row r="726" spans="1:2">
+      <c r="A726">
+        <v>724</v>
+      </c>
+      <c r="B726">
+        <v>0.0002558323612902313</v>
+      </c>
+    </row>
+    <row r="727" spans="1:2">
+      <c r="A727">
+        <v>725</v>
+      </c>
+      <c r="B727">
+        <v>0.0009292093454860151</v>
+      </c>
+    </row>
+    <row r="728" spans="1:2">
+      <c r="A728">
+        <v>726</v>
+      </c>
+      <c r="B728">
+        <v>0.0004154966154601425</v>
+      </c>
+    </row>
+    <row r="729" spans="1:2">
+      <c r="A729">
+        <v>727</v>
+      </c>
+      <c r="B729">
+        <v>0.0006990541005507112</v>
+      </c>
+    </row>
+    <row r="730" spans="1:2">
+      <c r="A730">
+        <v>728</v>
+      </c>
+      <c r="B730">
+        <v>0.0002207049546996132</v>
+      </c>
+    </row>
+    <row r="731" spans="1:2">
+      <c r="A731">
+        <v>729</v>
+      </c>
+      <c r="B731">
+        <v>0.0003747069858945906</v>
+      </c>
+    </row>
+    <row r="732" spans="1:2">
+      <c r="A732">
+        <v>730</v>
+      </c>
+      <c r="B732">
+        <v>0.0003744900168385357</v>
+      </c>
+    </row>
+    <row r="733" spans="1:2">
+      <c r="A733">
+        <v>731</v>
+      </c>
+      <c r="B733">
+        <v>-0.0002917129604611546</v>
+      </c>
+    </row>
+    <row r="734" spans="1:2">
+      <c r="A734">
+        <v>732</v>
+      </c>
+      <c r="B734">
+        <v>0.005210591480135918</v>
+      </c>
+    </row>
+    <row r="735" spans="1:2">
+      <c r="A735">
+        <v>733</v>
+      </c>
+      <c r="B735">
+        <v>0.00111568090505898</v>
+      </c>
+    </row>
+    <row r="736" spans="1:2">
+      <c r="A736">
+        <v>734</v>
+      </c>
+      <c r="B736">
+        <v>0.0003654288884717971</v>
+      </c>
+    </row>
+    <row r="737" spans="1:2">
+      <c r="A737">
+        <v>735</v>
+      </c>
+      <c r="B737">
+        <v>0.0003472387325018644</v>
+      </c>
+    </row>
+    <row r="738" spans="1:2">
+      <c r="A738">
+        <v>736</v>
+      </c>
+      <c r="B738">
+        <v>0.0001574078196426854</v>
+      </c>
+    </row>
+    <row r="739" spans="1:2">
+      <c r="A739">
+        <v>737</v>
+      </c>
+      <c r="B739">
+        <v>0.0004010040429420769</v>
+      </c>
+    </row>
+    <row r="740" spans="1:2">
+      <c r="A740">
+        <v>738</v>
+      </c>
+      <c r="B740">
+        <v>2.297476203239057E-05</v>
+      </c>
+    </row>
+    <row r="741" spans="1:2">
+      <c r="A741">
+        <v>739</v>
+      </c>
+      <c r="B741">
+        <v>0.0001799688616301864</v>
+      </c>
+    </row>
+    <row r="742" spans="1:2">
+      <c r="A742">
+        <v>740</v>
+      </c>
+      <c r="B742">
+        <v>0.000215811567613855</v>
+      </c>
+    </row>
+    <row r="743" spans="1:2">
+      <c r="A743">
+        <v>741</v>
+      </c>
+      <c r="B743">
+        <v>0.0004266223695594817</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2">
+      <c r="A744">
+        <v>742</v>
+      </c>
+      <c r="B744">
+        <v>-1.767078401826438E-06</v>
+      </c>
+    </row>
+    <row r="745" spans="1:2">
+      <c r="A745">
+        <v>743</v>
+      </c>
+      <c r="B745">
+        <v>0.001118923653848469</v>
+      </c>
+    </row>
+    <row r="746" spans="1:2">
+      <c r="A746">
+        <v>744</v>
+      </c>
+      <c r="B746">
+        <v>0.0001576888607814908</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2">
+      <c r="A747">
+        <v>745</v>
+      </c>
+      <c r="B747">
+        <v>0.002380455611273646</v>
+      </c>
+    </row>
+    <row r="748" spans="1:2">
+      <c r="A748">
+        <v>746</v>
+      </c>
+      <c r="B748">
+        <v>0.002448854967951775</v>
+      </c>
+    </row>
+    <row r="749" spans="1:2">
+      <c r="A749">
+        <v>747</v>
+      </c>
+      <c r="B749">
+        <v>0.001602961798198521</v>
+      </c>
+    </row>
+    <row r="750" spans="1:2">
+      <c r="A750">
+        <v>748</v>
+      </c>
+      <c r="B750">
+        <v>0.0007382429321296513</v>
+      </c>
+    </row>
+    <row r="751" spans="1:2">
+      <c r="A751">
+        <v>749</v>
+      </c>
+      <c r="B751">
+        <v>0.0004052480217069387</v>
+      </c>
+    </row>
+    <row r="752" spans="1:2">
+      <c r="A752">
+        <v>750</v>
+      </c>
+      <c r="B752">
+        <v>0.0001716995029710233</v>
+      </c>
+    </row>
+    <row r="753" spans="1:2">
+      <c r="A753">
+        <v>751</v>
+      </c>
+      <c r="B753">
+        <v>0.0004192079941276461</v>
+      </c>
+    </row>
+    <row r="754" spans="1:2">
+      <c r="A754">
+        <v>752</v>
+      </c>
+      <c r="B754">
+        <v>0.0006815408123657107</v>
+      </c>
+    </row>
+    <row r="755" spans="1:2">
+      <c r="A755">
+        <v>753</v>
+      </c>
+      <c r="B755">
+        <v>0.0002132830413756892</v>
+      </c>
+    </row>
+    <row r="756" spans="1:2">
+      <c r="A756">
+        <v>754</v>
+      </c>
+      <c r="B756">
+        <v>0.0002515695232432336</v>
+      </c>
+    </row>
+    <row r="757" spans="1:2">
+      <c r="A757">
+        <v>755</v>
+      </c>
+      <c r="B757">
+        <v>0.0006405942840501666</v>
+      </c>
+    </row>
+    <row r="758" spans="1:2">
+      <c r="A758">
+        <v>756</v>
+      </c>
+      <c r="B758">
+        <v>0.000296891201287508</v>
+      </c>
+    </row>
+    <row r="759" spans="1:2">
+      <c r="A759">
+        <v>757</v>
+      </c>
+      <c r="B759">
+        <v>0.0008362677181139588</v>
+      </c>
+    </row>
+    <row r="760" spans="1:2">
+      <c r="A760">
+        <v>758</v>
+      </c>
+      <c r="B760">
+        <v>-0.003242684062570333</v>
+      </c>
+    </row>
+    <row r="761" spans="1:2">
+      <c r="A761">
+        <v>759</v>
+      </c>
+      <c r="B761">
+        <v>0.0003312352346256375</v>
+      </c>
+    </row>
+    <row r="762" spans="1:2">
+      <c r="A762">
+        <v>760</v>
+      </c>
+      <c r="B762">
+        <v>9.662524098530412E-05</v>
+      </c>
+    </row>
+    <row r="763" spans="1:2">
+      <c r="A763">
+        <v>761</v>
+      </c>
+      <c r="B763">
+        <v>-1.79152557393536E-05</v>
+      </c>
+    </row>
+    <row r="764" spans="1:2">
+      <c r="A764">
+        <v>762</v>
+      </c>
+      <c r="B764">
+        <v>0.0003197341284248978</v>
+      </c>
+    </row>
+    <row r="765" spans="1:2">
+      <c r="A765">
+        <v>763</v>
+      </c>
+      <c r="B765">
+        <v>-9.789630712475628E-05</v>
+      </c>
+    </row>
+    <row r="766" spans="1:2">
+      <c r="A766">
+        <v>764</v>
+      </c>
+      <c r="B766">
+        <v>0.0004665871383622289</v>
+      </c>
+    </row>
+    <row r="767" spans="1:2">
+      <c r="A767">
+        <v>765</v>
+      </c>
+      <c r="B767">
+        <v>0.002176421927288175</v>
+      </c>
+    </row>
+    <row r="768" spans="1:2">
+      <c r="A768">
+        <v>766</v>
+      </c>
+      <c r="B768">
+        <v>0.0003017909766640514</v>
+      </c>
+    </row>
+    <row r="769" spans="1:2">
+      <c r="A769">
+        <v>767</v>
+      </c>
+      <c r="B769">
+        <v>-3.154846490360796E-05</v>
+      </c>
+    </row>
+    <row r="770" spans="1:2">
+      <c r="A770">
+        <v>768</v>
+      </c>
+      <c r="B770">
+        <v>0.0002809887228067964</v>
+      </c>
+    </row>
+    <row r="771" spans="1:2">
+      <c r="A771">
+        <v>769</v>
+      </c>
+      <c r="B771">
+        <v>0.0006142128841020167</v>
+      </c>
+    </row>
+    <row r="772" spans="1:2">
+      <c r="A772">
+        <v>770</v>
+      </c>
+      <c r="B772">
+        <v>0.0002001759567065164</v>
+      </c>
+    </row>
+    <row r="773" spans="1:2">
+      <c r="A773">
+        <v>771</v>
+      </c>
+      <c r="B773">
+        <v>0.0004985854611732066</v>
+      </c>
+    </row>
+    <row r="774" spans="1:2">
+      <c r="A774">
+        <v>772</v>
+      </c>
+      <c r="B774">
+        <v>0.0007492914446629584</v>
+      </c>
+    </row>
+    <row r="775" spans="1:2">
+      <c r="A775">
+        <v>773</v>
+      </c>
+      <c r="B775">
+        <v>0.001566710183396935</v>
+      </c>
+    </row>
+    <row r="776" spans="1:2">
+      <c r="A776">
+        <v>774</v>
+      </c>
+      <c r="B776">
+        <v>0.0004868138639722019</v>
+      </c>
+    </row>
+    <row r="777" spans="1:2">
+      <c r="A777">
+        <v>775</v>
+      </c>
+      <c r="B777">
+        <v>-9.280091762775555E-05</v>
+      </c>
+    </row>
+    <row r="778" spans="1:2">
+      <c r="A778">
+        <v>776</v>
+      </c>
+      <c r="B778">
+        <v>0.0001833806600188836</v>
+      </c>
+    </row>
+    <row r="779" spans="1:2">
+      <c r="A779">
+        <v>777</v>
+      </c>
+      <c r="B779">
+        <v>0.0001528974389657378</v>
+      </c>
+    </row>
+    <row r="780" spans="1:2">
+      <c r="A780">
+        <v>778</v>
+      </c>
+      <c r="B780">
+        <v>0.002586161019280553</v>
+      </c>
+    </row>
+    <row r="781" spans="1:2">
+      <c r="A781">
+        <v>779</v>
+      </c>
+      <c r="B781">
+        <v>0.0004963488318026066</v>
+      </c>
+    </row>
+    <row r="782" spans="1:2">
+      <c r="A782">
+        <v>780</v>
+      </c>
+      <c r="B782">
+        <v>0.0005843722028657794</v>
+      </c>
+    </row>
+    <row r="783" spans="1:2">
+      <c r="A783">
+        <v>781</v>
+      </c>
+      <c r="B783">
+        <v>0.000778948946390301</v>
+      </c>
+    </row>
+    <row r="784" spans="1:2">
+      <c r="A784">
+        <v>782</v>
+      </c>
+      <c r="B784">
+        <v>0.0003815908567048609</v>
+      </c>
+    </row>
+    <row r="785" spans="1:2">
+      <c r="A785">
+        <v>783</v>
+      </c>
+      <c r="B785">
+        <v>-0.0001503878156654537</v>
+      </c>
+    </row>
+    <row r="786" spans="1:2">
+      <c r="A786">
+        <v>784</v>
+      </c>
+      <c r="B786">
+        <v>0.0003420766734052449</v>
+      </c>
+    </row>
+    <row r="787" spans="1:2">
+      <c r="A787">
+        <v>785</v>
+      </c>
+      <c r="B787">
+        <v>0.0002978861739393324</v>
+      </c>
+    </row>
+    <row r="788" spans="1:2">
+      <c r="A788">
+        <v>786</v>
+      </c>
+      <c r="B788">
+        <v>0.0004532817692961544</v>
+      </c>
+    </row>
+    <row r="789" spans="1:2">
+      <c r="A789">
+        <v>787</v>
+      </c>
+      <c r="B789">
+        <v>0.0002536321699153632</v>
+      </c>
+    </row>
+    <row r="790" spans="1:2">
+      <c r="A790">
+        <v>788</v>
+      </c>
+      <c r="B790">
+        <v>0.0001175055949715897</v>
+      </c>
+    </row>
+    <row r="791" spans="1:2">
+      <c r="A791">
+        <v>789</v>
+      </c>
+      <c r="B791">
+        <v>0.0007406233344227076</v>
+      </c>
+    </row>
+    <row r="792" spans="1:2">
+      <c r="A792">
+        <v>790</v>
+      </c>
+      <c r="B792">
+        <v>0.0003231577575206757</v>
+      </c>
+    </row>
+    <row r="793" spans="1:2">
+      <c r="A793">
+        <v>791</v>
+      </c>
+      <c r="B793">
+        <v>0.004157807677984238</v>
+      </c>
+    </row>
+    <row r="794" spans="1:2">
+      <c r="A794">
+        <v>792</v>
+      </c>
+      <c r="B794">
+        <v>0.0001250374771188945</v>
+      </c>
+    </row>
+    <row r="795" spans="1:2">
+      <c r="A795">
+        <v>793</v>
+      </c>
+      <c r="B795">
+        <v>0.0005048286984674633</v>
+      </c>
+    </row>
+    <row r="796" spans="1:2">
+      <c r="A796">
+        <v>794</v>
+      </c>
+      <c r="B796">
+        <v>7.488667324651033E-05</v>
+      </c>
+    </row>
+    <row r="797" spans="1:2">
+      <c r="A797">
+        <v>795</v>
+      </c>
+      <c r="B797">
+        <v>3.930416642106138E-05</v>
+      </c>
+    </row>
+    <row r="798" spans="1:2">
+      <c r="A798">
+        <v>796</v>
+      </c>
+      <c r="B798">
+        <v>0.0001565564598422498</v>
+      </c>
+    </row>
+    <row r="799" spans="1:2">
+      <c r="A799">
+        <v>797</v>
+      </c>
+      <c r="B799">
+        <v>9.833331569097936E-05</v>
+      </c>
+    </row>
+    <row r="800" spans="1:2">
+      <c r="A800">
+        <v>798</v>
+      </c>
+      <c r="B800">
+        <v>-0.0002220636088168249</v>
+      </c>
+    </row>
+    <row r="801" spans="1:2">
+      <c r="A801">
+        <v>799</v>
+      </c>
+      <c r="B801">
+        <v>0.0007562041282653809</v>
+      </c>
+    </row>
+    <row r="802" spans="1:2">
+      <c r="A802">
+        <v>800</v>
+      </c>
+      <c r="B802">
+        <v>0.0001120060114772059</v>
+      </c>
+    </row>
+    <row r="803" spans="1:2">
+      <c r="A803">
+        <v>801</v>
+      </c>
+      <c r="B803">
+        <v>-8.584476017858833E-05</v>
+      </c>
+    </row>
+    <row r="804" spans="1:2">
+      <c r="A804">
+        <v>802</v>
+      </c>
+      <c r="B804">
+        <v>-0.0001395647414028645</v>
+      </c>
+    </row>
+    <row r="805" spans="1:2">
+      <c r="A805">
+        <v>803</v>
+      </c>
+      <c r="B805">
+        <v>0.0009070045198313892</v>
+      </c>
+    </row>
+    <row r="806" spans="1:2">
+      <c r="A806">
+        <v>804</v>
+      </c>
+      <c r="B806">
+        <v>0.0007173824124038219</v>
+      </c>
+    </row>
+    <row r="807" spans="1:2">
+      <c r="A807">
+        <v>805</v>
+      </c>
+      <c r="B807">
+        <v>-0.0001777592988219112</v>
+      </c>
+    </row>
+    <row r="808" spans="1:2">
+      <c r="A808">
+        <v>806</v>
+      </c>
+      <c r="B808">
+        <v>0.000112367735709995</v>
+      </c>
+    </row>
+    <row r="809" spans="1:2">
+      <c r="A809">
+        <v>807</v>
+      </c>
+      <c r="B809">
+        <v>0.0006904587498866022</v>
+      </c>
+    </row>
+    <row r="810" spans="1:2">
+      <c r="A810">
+        <v>808</v>
+      </c>
+      <c r="B810">
+        <v>0.0005024610436521471</v>
+      </c>
+    </row>
+    <row r="811" spans="1:2">
+      <c r="A811">
+        <v>809</v>
+      </c>
+      <c r="B811">
+        <v>0.0004398038727231324</v>
+      </c>
+    </row>
+    <row r="812" spans="1:2">
+      <c r="A812">
+        <v>810</v>
+      </c>
+      <c r="B812">
+        <v>0.001232495647855103</v>
+      </c>
+    </row>
+    <row r="813" spans="1:2">
+      <c r="A813">
+        <v>811</v>
+      </c>
+      <c r="B813">
+        <v>0.0005876764189451933</v>
+      </c>
+    </row>
+    <row r="814" spans="1:2">
+      <c r="A814">
+        <v>812</v>
+      </c>
+      <c r="B814">
+        <v>0.0002586544142104685</v>
+      </c>
+    </row>
+    <row r="815" spans="1:2">
+      <c r="A815">
+        <v>813</v>
+      </c>
+      <c r="B815">
+        <v>0.001144141191616654</v>
+      </c>
+    </row>
+    <row r="816" spans="1:2">
+      <c r="A816">
+        <v>814</v>
+      </c>
+      <c r="B816">
+        <v>0.0004699891433119774</v>
+      </c>
+    </row>
+    <row r="817" spans="1:2">
+      <c r="A817">
+        <v>815</v>
+      </c>
+      <c r="B817">
+        <v>0.0005611137603409588</v>
+      </c>
+    </row>
+    <row r="818" spans="1:2">
+      <c r="A818">
+        <v>816</v>
+      </c>
+      <c r="B818">
+        <v>-5.016505383537151E-05</v>
+      </c>
+    </row>
+    <row r="819" spans="1:2">
+      <c r="A819">
+        <v>817</v>
+      </c>
+      <c r="B819">
+        <v>0.001026895712129772</v>
       </c>
     </row>
   </sheetData>
@@ -9125,12 +15669,508 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
         <v>489</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.008072733879089355</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0.008639216423034668</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.002448320388793945</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0.003761172294616699</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.008451461791992188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0.01116335391998291</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.004939675331115723</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.008472681045532227</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.007416248321533203</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.008014798164367676</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.01049351692199707</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0.01458644866943359</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>0.01178514957427979</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>0.00229644775390625</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>0.005844593048095703</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>0.00178229808807373</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>0.003985285758972168</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>0.007596135139465332</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>0.008611321449279785</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>0.00476682186126709</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>0.007997632026672363</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>0.006519675254821777</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>0.004564762115478516</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>0.004073262214660645</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>0.004170894622802734</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>0.01130330562591553</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>0.009017586708068848</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>0.006282925605773926</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>0.01064407825469971</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>0.009979844093322754</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>0.006899595260620117</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <v>0.007202744483947754</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>0.01050162315368652</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <v>0.01332581043243408</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36">
+        <v>0.00238800048828125</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>0.0101698637008667</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>0.01390886306762695</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>0.008612394332885742</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>0.009015083312988281</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>0.006609678268432617</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>0.008764982223510742</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>0.009654641151428223</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>0.01302993297576904</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>0.004000067710876465</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>0.01109409332275391</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>0.007359147071838379</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>0.02149820327758789</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>0.008451342582702637</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>0.002372264862060547</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>0.008061766624450684</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>0.00459897518157959</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <v>0.005568265914916992</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>0.01068806648254395</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>0.007220983505249023</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <v>0.002198576927185059</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <v>0.01051437854766846</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58">
+        <v>0.008717536926269531</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59">
+        <v>0.01081240177154541</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60">
+        <v>0.002353549003601074</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61">
+        <v>0.007715225219726562</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62">
+        <v>0.008431315422058105</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63">
+        <v>0.002743959426879883</v>
       </c>
     </row>
   </sheetData>
@@ -9140,12 +16180,108 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
         <v>489</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.03175115585327148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0.0406416654586792</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.04577434062957764</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0.02701389789581299</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.02762079238891602</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0.04812073707580566</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.04093873500823975</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.04924356937408447</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.04739522933959961</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.04855942726135254</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.03062355518341064</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0.04073798656463623</v>
       </c>
     </row>
   </sheetData>
